--- a/Studniówka 2027_I LO.xlsx
+++ b/Studniówka 2027_I LO.xlsx
@@ -3,22 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="2799" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B88286-D523-43CB-A78C-C2C16D2C24F9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46E1500D-7D9F-468D-A177-ECB72B4B9896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista uczniów_składki" sheetId="1" r:id="rId1"/>
-    <sheet name="Wydatki" sheetId="2" r:id="rId2"/>
-    <sheet name="Podsumowanie" sheetId="3" r:id="rId3"/>
-    <sheet name="Do wiadomości rodziców" sheetId="6" r:id="rId4"/>
-    <sheet name="Zadania" sheetId="8" r:id="rId5"/>
-    <sheet name="Notes" sheetId="7" state="hidden" r:id="rId6"/>
-    <sheet name="Ankieta#1_13.04.26" sheetId="5" state="hidden" r:id="rId7"/>
-    <sheet name="Dashboard" sheetId="9" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId2"/>
+    <sheet name="Wydatki" sheetId="2" r:id="rId3"/>
+    <sheet name="Podsumowanie" sheetId="3" r:id="rId4"/>
+    <sheet name="Do wiadomości rodziców" sheetId="6" r:id="rId5"/>
+    <sheet name="Zadania" sheetId="8" r:id="rId6"/>
+    <sheet name="Notes" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="Ankieta#1_13.04.26" sheetId="5" r:id="rId8"/>
+    <sheet name="Dashboard" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ankieta#1_13.04.26'!$K$1:$M$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ankieta#1_13.04.26'!$K$1:$M$168</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista uczniów_składki'!$Z$2:$AA$2</definedName>
     <definedName name="Fragmentator_Status">#N/A</definedName>
     <definedName name="Slicer_Klasa">#N/A</definedName>
@@ -30,8 +31,8 @@
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
       <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicerCache r:id="rId9"/>
         <x14:slicerCache r:id="rId10"/>
+        <x14:slicerCache r:id="rId11"/>
       </x15:slicerCaches>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2717" uniqueCount="462">
   <si>
     <t>Nazwisko</t>
   </si>
@@ -521,6 +522,9 @@
   </si>
   <si>
     <t>Klaudia</t>
+  </si>
+  <si>
+    <t>zrezygnowała z Os. Tow. 22.09</t>
   </si>
   <si>
     <t>Pasak</t>
@@ -1609,10 +1613,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -1881,25 +1885,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1911,11 +1915,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1940,28 +1944,28 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1997,10 +2001,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2012,31 +2016,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2058,7 +2062,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2067,36 +2071,36 @@
     <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2116,21 +2120,21 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2143,7 +2147,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2152,11 +2156,11 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2168,16 +2172,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2191,41 +2195,41 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="96">
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -2381,7 +2385,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <numFmt numFmtId="168" formatCode="dd/mm/yyyy\ hh:mm"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9E1F2"/>
@@ -2405,7 +2409,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <numFmt numFmtId="168" formatCode="dd/mm/yyyy\ hh:mm"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9E1F2"/>
@@ -2488,7 +2492,7 @@
       <font>
         <name val="Aptos"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="169" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
@@ -2525,7 +2529,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2544,7 +2548,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2563,7 +2567,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2600,7 +2604,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2769,7 +2773,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" relativeIndent="1"/>
     </dxf>
     <dxf>
@@ -2806,7 +2810,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" relativeIndent="1"/>
     </dxf>
     <dxf>
@@ -2825,7 +2829,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2844,7 +2848,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" relativeIndent="1"/>
     </dxf>
     <dxf>
@@ -2863,7 +2867,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2882,7 +2886,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2901,7 +2905,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2920,7 +2924,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" relativeIndent="1"/>
     </dxf>
     <dxf>
@@ -2957,7 +2961,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="center" vertical="center" relativeIndent="1"/>
     </dxf>
     <dxf>
@@ -3123,7 +3127,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
@@ -3142,7 +3146,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3180,7 +3184,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3199,7 +3203,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3218,7 +3222,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3237,7 +3241,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3256,7 +3260,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3275,7 +3279,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3294,7 +3298,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3313,7 +3317,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3332,7 +3336,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3351,7 +3355,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3370,7 +3374,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3389,7 +3393,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3408,7 +3412,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3427,7 +3431,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3446,7 +3450,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3465,7 +3469,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3559,7 +3563,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3578,7 +3582,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3615,7 +3619,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4597,11 +4601,11 @@
       </c>
       <c r="U1" s="4">
         <f>SUBTOTAL(9,U3:U614)</f>
-        <v>137790</v>
+        <v>137250</v>
       </c>
       <c r="V1" s="4">
         <f>SUBTOTAL(9,V3:V614)</f>
-        <v>-116490</v>
+        <v>-115950</v>
       </c>
     </row>
     <row r="2" spans="1:27" s="3" customFormat="1" ht="36.75" customHeight="1">
@@ -8207,7 +8211,10 @@
         <v>27</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="G81" s="4">
         <v>50</v>
@@ -8218,11 +8225,11 @@
       </c>
       <c r="U81" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D81="Nie",E81="Nie"),0,IF(AND(D81="Tak",E81="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
-        <v>700</v>
+        <v>430</v>
       </c>
       <c r="V81" s="4">
         <f t="shared" si="4"/>
-        <v>-650</v>
+        <v>-380</v>
       </c>
       <c r="W81" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8240,10 +8247,10 @@
     </row>
     <row r="82" spans="1:27">
       <c r="A82" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>87</v>
@@ -8285,7 +8292,7 @@
     </row>
     <row r="83" spans="1:27">
       <c r="A83" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>59</v>
@@ -8330,7 +8337,7 @@
     </row>
     <row r="84" spans="1:27">
       <c r="A84" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>65</v>
@@ -8420,13 +8427,13 @@
     </row>
     <row r="86" spans="1:27">
       <c r="A86" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>27</v>
@@ -8477,7 +8484,7 @@
     </row>
     <row r="87" spans="1:27">
       <c r="A87" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>76</v>
@@ -8522,10 +8529,10 @@
     </row>
     <row r="88" spans="1:27">
       <c r="A88" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>32</v>
@@ -8567,7 +8574,7 @@
     </row>
     <row r="89" spans="1:27">
       <c r="A89" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>59</v>
@@ -8612,10 +8619,10 @@
     </row>
     <row r="90" spans="1:27">
       <c r="A90" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>53</v>
@@ -8657,7 +8664,7 @@
     </row>
     <row r="91" spans="1:27">
       <c r="A91" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>155</v>
@@ -8702,13 +8709,13 @@
     </row>
     <row r="92" spans="1:27">
       <c r="A92" s="117" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>27</v>
@@ -8756,7 +8763,7 @@
         <v>59</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>27</v>
@@ -8795,13 +8802,13 @@
     </row>
     <row r="94" spans="1:27">
       <c r="A94" s="117" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>27</v>
@@ -8840,13 +8847,13 @@
     </row>
     <row r="95" spans="1:27">
       <c r="A95" s="117" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>27</v>
@@ -8882,13 +8889,13 @@
     </row>
     <row r="96" spans="1:27">
       <c r="A96" s="117" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>27</v>
@@ -8933,10 +8940,10 @@
         <v>140</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>27</v>
@@ -8978,13 +8985,13 @@
     </row>
     <row r="98" spans="1:27">
       <c r="A98" s="117" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>27</v>
@@ -9026,13 +9033,13 @@
     </row>
     <row r="99" spans="1:27">
       <c r="A99" s="117" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>27</v>
@@ -9071,13 +9078,13 @@
     </row>
     <row r="100" spans="1:27">
       <c r="A100" s="117" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>27</v>
@@ -9119,13 +9126,13 @@
     </row>
     <row r="101" spans="1:27">
       <c r="A101" s="117" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>27</v>
@@ -9167,13 +9174,13 @@
     </row>
     <row r="102" spans="1:27">
       <c r="A102" s="117" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>27</v>
@@ -9212,13 +9219,13 @@
     </row>
     <row r="103" spans="1:27">
       <c r="A103" s="117" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>27</v>
@@ -9260,13 +9267,13 @@
     </row>
     <row r="104" spans="1:27">
       <c r="A104" s="117" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>27</v>
@@ -9311,13 +9318,13 @@
     </row>
     <row r="105" spans="1:27">
       <c r="A105" s="117" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>27</v>
@@ -9359,13 +9366,13 @@
     </row>
     <row r="106" spans="1:27">
       <c r="A106" s="117" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>27</v>
@@ -9407,13 +9414,13 @@
     </row>
     <row r="107" spans="1:27">
       <c r="A107" s="117" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>27</v>
@@ -9449,13 +9456,13 @@
     </row>
     <row r="108" spans="1:27">
       <c r="A108" s="117" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>27</v>
@@ -9494,13 +9501,13 @@
     </row>
     <row r="109" spans="1:27">
       <c r="A109" s="117" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>27</v>
@@ -9542,13 +9549,13 @@
     </row>
     <row r="110" spans="1:27">
       <c r="A110" s="117" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>27</v>
@@ -9590,10 +9597,10 @@
     </row>
     <row r="111" spans="1:27">
       <c r="A111" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>53</v>
@@ -9635,13 +9642,13 @@
     </row>
     <row r="112" spans="1:27">
       <c r="A112" s="117" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>27</v>
@@ -9683,13 +9690,13 @@
     </row>
     <row r="113" spans="1:27">
       <c r="A113" s="117" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>27</v>
@@ -9731,13 +9738,13 @@
     </row>
     <row r="114" spans="1:27">
       <c r="A114" s="117" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>27</v>
@@ -9779,10 +9786,10 @@
     </row>
     <row r="115" spans="1:27">
       <c r="A115" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>32</v>
@@ -9824,10 +9831,10 @@
     </row>
     <row r="116" spans="1:27">
       <c r="A116" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>87</v>
@@ -9869,7 +9876,7 @@
     </row>
     <row r="117" spans="1:27">
       <c r="A117" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>44</v>
@@ -9914,10 +9921,10 @@
     </row>
     <row r="118" spans="1:27">
       <c r="A118" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>87</v>
@@ -9959,10 +9966,10 @@
     </row>
     <row r="119" spans="1:27">
       <c r="A119" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>87</v>
@@ -10004,7 +10011,7 @@
     </row>
     <row r="120" spans="1:27">
       <c r="A120" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>73</v>
@@ -10049,10 +10056,10 @@
     </row>
     <row r="121" spans="1:27">
       <c r="A121" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>113</v>
@@ -10094,7 +10101,7 @@
     </row>
     <row r="122" spans="1:27">
       <c r="A122" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>57</v>
@@ -10184,7 +10191,7 @@
     </row>
     <row r="124" spans="1:27">
       <c r="A124" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>59</v>
@@ -10229,7 +10236,7 @@
     </row>
     <row r="125" spans="1:27">
       <c r="A125" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>124</v>
@@ -10274,10 +10281,10 @@
     </row>
     <row r="126" spans="1:27">
       <c r="A126" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>32</v>
@@ -10319,13 +10326,13 @@
     </row>
     <row r="127" spans="1:27">
       <c r="A127" s="117" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>27</v>
@@ -10367,13 +10374,13 @@
     </row>
     <row r="128" spans="1:27">
       <c r="A128" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>27</v>
@@ -10418,13 +10425,13 @@
     </row>
     <row r="129" spans="1:27">
       <c r="A129" s="117" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>27</v>
@@ -10466,13 +10473,13 @@
     </row>
     <row r="130" spans="1:27">
       <c r="A130" s="117" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>27</v>
@@ -10523,7 +10530,7 @@
         <v>73</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>27</v>
@@ -10565,7 +10572,7 @@
     </row>
     <row r="132" spans="1:27">
       <c r="A132" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>46</v>
@@ -10610,13 +10617,13 @@
     </row>
     <row r="133" spans="1:27">
       <c r="A133" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>27</v>
@@ -10661,13 +10668,13 @@
     </row>
     <row r="134" spans="1:27">
       <c r="A134" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>27</v>
@@ -10709,13 +10716,13 @@
     </row>
     <row r="135" spans="1:27">
       <c r="A135" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>27</v>
@@ -10760,13 +10767,13 @@
     </row>
     <row r="136" spans="1:27">
       <c r="A136" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>27</v>
@@ -10808,13 +10815,13 @@
     </row>
     <row r="137" spans="1:27">
       <c r="A137" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>27</v>
@@ -10856,13 +10863,13 @@
     </row>
     <row r="138" spans="1:27">
       <c r="A138" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>27</v>
@@ -10904,13 +10911,13 @@
     </row>
     <row r="139" spans="1:27">
       <c r="A139" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>27</v>
@@ -10955,13 +10962,13 @@
     </row>
     <row r="140" spans="1:27">
       <c r="A140" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>27</v>
@@ -11006,13 +11013,13 @@
     </row>
     <row r="141" spans="1:27">
       <c r="A141" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>27</v>
@@ -11054,13 +11061,13 @@
     </row>
     <row r="142" spans="1:27">
       <c r="A142" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>27</v>
@@ -11102,13 +11109,13 @@
     </row>
     <row r="143" spans="1:27">
       <c r="A143" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>27</v>
@@ -11153,7 +11160,7 @@
     </row>
     <row r="144" spans="1:27">
       <c r="A144" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>31</v>
@@ -11198,13 +11205,13 @@
     </row>
     <row r="145" spans="1:27">
       <c r="A145" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>27</v>
@@ -11246,13 +11253,13 @@
     </row>
     <row r="146" spans="1:27">
       <c r="A146" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>27</v>
@@ -11297,13 +11304,13 @@
     </row>
     <row r="147" spans="1:27">
       <c r="A147" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>27</v>
@@ -11348,13 +11355,13 @@
     </row>
     <row r="148" spans="1:27">
       <c r="A148" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>27</v>
@@ -11399,10 +11406,10 @@
         <v>72</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>27</v>
@@ -11438,7 +11445,7 @@
     </row>
     <row r="150" spans="1:27">
       <c r="A150" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>29</v>
@@ -11483,13 +11490,13 @@
     </row>
     <row r="151" spans="1:27">
       <c r="A151" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>27</v>
@@ -11537,7 +11544,7 @@
         <v>86</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>87</v>
@@ -11582,7 +11589,7 @@
         <v>145</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>53</v>
@@ -11624,13 +11631,13 @@
     </row>
     <row r="154" spans="1:27">
       <c r="A154" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>27</v>
@@ -11675,10 +11682,10 @@
     </row>
     <row r="155" spans="1:27">
       <c r="A155" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>32</v>
@@ -11720,13 +11727,13 @@
     </row>
     <row r="156" spans="1:27">
       <c r="A156" s="117" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>146</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>27</v>
@@ -11768,13 +11775,13 @@
     </row>
     <row r="157" spans="1:27">
       <c r="A157" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>33</v>
@@ -11810,13 +11817,13 @@
     </row>
     <row r="158" spans="1:27">
       <c r="A158" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>27</v>
@@ -11858,10 +11865,10 @@
     </row>
     <row r="159" spans="1:27">
       <c r="A159" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>87</v>
@@ -11903,7 +11910,7 @@
     </row>
     <row r="160" spans="1:27">
       <c r="A160" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>80</v>
@@ -11996,7 +12003,7 @@
         <v>86</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>87</v>
@@ -12038,7 +12045,7 @@
     </row>
     <row r="163" spans="1:27">
       <c r="A163" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>73</v>
@@ -12083,7 +12090,7 @@
     </row>
     <row r="164" spans="1:27">
       <c r="A164" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>44</v>
@@ -12128,7 +12135,7 @@
     </row>
     <row r="165" spans="1:27">
       <c r="A165" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>29</v>
@@ -12173,10 +12180,10 @@
     </row>
     <row r="166" spans="1:27">
       <c r="A166" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>53</v>
@@ -12218,7 +12225,7 @@
     </row>
     <row r="167" spans="1:27">
       <c r="A167" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>73</v>
@@ -12263,13 +12270,13 @@
     </row>
     <row r="168" spans="1:27">
       <c r="A168" s="117" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>27</v>
@@ -12305,7 +12312,7 @@
     </row>
     <row r="169" spans="1:27">
       <c r="A169" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>63</v>
@@ -12350,10 +12357,10 @@
     </row>
     <row r="170" spans="1:27">
       <c r="A170" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>26</v>
@@ -12392,10 +12399,10 @@
     </row>
     <row r="171" spans="1:27">
       <c r="A171" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>26</v>
@@ -12437,7 +12444,7 @@
     </row>
     <row r="172" spans="1:27">
       <c r="A172" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>57</v>
@@ -12482,13 +12489,13 @@
     </row>
     <row r="173" spans="1:27">
       <c r="A173" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>27</v>
@@ -12536,10 +12543,10 @@
     </row>
     <row r="174" spans="1:27">
       <c r="A174" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>53</v>
@@ -12581,7 +12588,7 @@
     </row>
     <row r="175" spans="1:27">
       <c r="A175" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>107</v>
@@ -12626,7 +12633,7 @@
     </row>
     <row r="176" spans="1:27">
       <c r="A176" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>107</v>
@@ -12671,10 +12678,10 @@
     </row>
     <row r="177" spans="1:27">
       <c r="A177" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>87</v>
@@ -12716,7 +12723,7 @@
     </row>
     <row r="178" spans="1:27">
       <c r="A178" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>65</v>
@@ -12761,7 +12768,7 @@
     </row>
     <row r="179" spans="1:27">
       <c r="A179" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>78</v>
@@ -12806,10 +12813,10 @@
     </row>
     <row r="180" spans="1:27">
       <c r="A180" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>26</v>
@@ -12854,7 +12861,7 @@
         <v>91</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>26</v>
@@ -12896,13 +12903,13 @@
     </row>
     <row r="182" spans="1:27">
       <c r="A182" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>27</v>
@@ -12947,13 +12954,13 @@
     </row>
     <row r="183" spans="1:27">
       <c r="A183" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>33</v>
@@ -12989,13 +12996,13 @@
     </row>
     <row r="184" spans="1:27">
       <c r="A184" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>27</v>
@@ -13040,13 +13047,13 @@
     </row>
     <row r="185" spans="1:27">
       <c r="A185" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>27</v>
@@ -13091,7 +13098,7 @@
         <v>112</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>26</v>
@@ -13133,7 +13140,7 @@
     </row>
     <row r="187" spans="1:27">
       <c r="A187" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>73</v>
@@ -13178,10 +13185,10 @@
     </row>
     <row r="188" spans="1:27">
       <c r="A188" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>26</v>
@@ -13223,7 +13230,7 @@
     </row>
     <row r="189" spans="1:27">
       <c r="A189" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>35</v>
@@ -13268,7 +13275,7 @@
     </row>
     <row r="190" spans="1:27">
       <c r="A190" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>46</v>
@@ -13313,10 +13320,10 @@
     </row>
     <row r="191" spans="1:27">
       <c r="A191" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>26</v>
@@ -13358,7 +13365,7 @@
     </row>
     <row r="192" spans="1:27">
       <c r="A192" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>52</v>
@@ -13403,13 +13410,13 @@
     </row>
     <row r="193" spans="1:27">
       <c r="A193" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>27</v>
@@ -13454,10 +13461,10 @@
     </row>
     <row r="194" spans="1:27">
       <c r="A194" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>26</v>
@@ -13499,10 +13506,10 @@
     </row>
     <row r="195" spans="1:27">
       <c r="A195" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>26</v>
@@ -13544,13 +13551,13 @@
     </row>
     <row r="196" spans="1:27">
       <c r="A196" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>27</v>
@@ -13592,13 +13599,13 @@
     </row>
     <row r="197" spans="1:27">
       <c r="A197" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>27</v>
@@ -13643,7 +13650,7 @@
     </row>
     <row r="198" spans="1:27">
       <c r="A198" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>67</v>
@@ -13688,10 +13695,10 @@
     </row>
     <row r="199" spans="1:27">
       <c r="A199" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>26</v>
@@ -13733,13 +13740,13 @@
     </row>
     <row r="200" spans="1:27">
       <c r="A200" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>27</v>
@@ -13790,7 +13797,7 @@
         <v>78</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>27</v>
@@ -13832,10 +13839,10 @@
     </row>
     <row r="202" spans="1:27">
       <c r="A202" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>32</v>
@@ -13877,10 +13884,10 @@
     </row>
     <row r="203" spans="1:27">
       <c r="A203" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>32</v>
@@ -13922,10 +13929,10 @@
     </row>
     <row r="204" spans="1:27">
       <c r="A204" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>32</v>
@@ -13967,10 +13974,10 @@
     </row>
     <row r="205" spans="1:27">
       <c r="A205" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>32</v>
@@ -14012,7 +14019,7 @@
     </row>
     <row r="206" spans="1:27">
       <c r="A206" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>122</v>
@@ -14057,7 +14064,7 @@
     </row>
     <row r="207" spans="1:27">
       <c r="A207" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>78</v>
@@ -14102,7 +14109,7 @@
     </row>
     <row r="208" spans="1:27">
       <c r="A208" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>78</v>
@@ -14114,7 +14121,10 @@
         <v>27</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="G208" s="4">
         <v>50</v>
@@ -14125,11 +14135,11 @@
       </c>
       <c r="U208" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D208="Nie",E208="Nie"),0,IF(AND(D208="Tak",E208="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
-        <v>700</v>
+        <v>430</v>
       </c>
       <c r="V208" s="4">
         <f t="shared" si="11"/>
-        <v>-650</v>
+        <v>-380</v>
       </c>
       <c r="W208" s="55" t="str">
         <f t="shared" si="12"/>
@@ -14147,10 +14157,10 @@
     </row>
     <row r="209" spans="1:27">
       <c r="A209" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>32</v>
@@ -14192,7 +14202,7 @@
     </row>
     <row r="210" spans="1:27">
       <c r="A210" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>35</v>
@@ -14237,10 +14247,10 @@
     </row>
     <row r="211" spans="1:27">
       <c r="A211" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>113</v>
@@ -14282,13 +14292,13 @@
     </row>
     <row r="212" spans="1:27">
       <c r="A212" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>27</v>
@@ -14327,13 +14337,13 @@
     </row>
     <row r="213" spans="1:27">
       <c r="A213" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B213" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>27</v>
@@ -14378,13 +14388,13 @@
     </row>
     <row r="214" spans="1:27">
       <c r="A214" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>27</v>
@@ -14429,7 +14439,7 @@
     </row>
     <row r="215" spans="1:27">
       <c r="A215" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>57</v>
@@ -14474,7 +14484,7 @@
     </row>
     <row r="216" spans="1:27">
       <c r="A216" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>31</v>
@@ -14519,7 +14529,7 @@
     </row>
     <row r="217" spans="1:27">
       <c r="A217" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>80</v>
@@ -14564,13 +14574,13 @@
     </row>
     <row r="218" spans="1:27">
       <c r="A218" s="117" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>27</v>
@@ -14612,13 +14622,13 @@
     </row>
     <row r="219" spans="1:27">
       <c r="A219" s="117" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>27</v>
@@ -14660,10 +14670,10 @@
     </row>
     <row r="220" spans="1:27">
       <c r="A220" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>87</v>
@@ -14705,7 +14715,7 @@
     </row>
     <row r="221" spans="1:27">
       <c r="A221" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>153</v>
@@ -14750,13 +14760,13 @@
     </row>
     <row r="222" spans="1:27">
       <c r="A222" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B222" s="4" t="s">
         <v>100</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>27</v>
@@ -14801,10 +14811,10 @@
     </row>
     <row r="223" spans="1:27">
       <c r="A223" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>87</v>
@@ -14846,13 +14856,13 @@
     </row>
     <row r="224" spans="1:27">
       <c r="A224" s="117" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>27</v>
@@ -14894,10 +14904,10 @@
     </row>
     <row r="225" spans="1:27">
       <c r="A225" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>87</v>
@@ -18842,6 +18852,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB506CE-4D21-45F1-8FE8-8B46E7F378F7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{659C87BF-BB22-4652-A1F0-1E2B8A6DA034}">
   <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -18866,28 +18885,28 @@
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="29.25">
       <c r="A2" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>23</v>
@@ -18895,7 +18914,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="58" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B3" s="32" t="b">
         <v>1</v>
@@ -18905,29 +18924,29 @@
       </c>
       <c r="D3" s="33">
         <f>Podsumowanie!C12</f>
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E3" s="88">
         <v>270</v>
       </c>
       <c r="F3" s="88">
         <f>Table1[[#This Row],[Ilość]]*Table1[[#This Row],[Cena]]</f>
-        <v>101790</v>
+        <v>101250</v>
       </c>
       <c r="G3" s="88">
         <v>2000</v>
       </c>
       <c r="H3" s="88">
         <f>Table1[[#This Row],[Koszt]]-Table1[[#This Row],[Zaliczka]]</f>
-        <v>99790</v>
+        <v>99250</v>
       </c>
       <c r="I3" s="122" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="43.5">
       <c r="A4" s="44" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B4" s="43" t="b">
         <v>1</v>
@@ -18954,7 +18973,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="58" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B5" s="32" t="b">
         <v>1</v>
@@ -18980,12 +18999,12 @@
         <v>7600</v>
       </c>
       <c r="I5" s="122" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="58" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B6" s="32" t="b">
         <v>1</v>
@@ -19011,12 +19030,12 @@
         <v>10000</v>
       </c>
       <c r="I6" s="122" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="58" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B7" s="32" t="b">
         <v>1</v>
@@ -19042,12 +19061,12 @@
         <v>1300</v>
       </c>
       <c r="I7" s="122" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B8" s="32" t="b">
         <v>0</v>
@@ -19072,7 +19091,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B9" s="32" t="b">
         <v>0</v>
@@ -19097,7 +19116,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B10" s="32" t="b">
         <v>0</v>
@@ -19105,25 +19124,25 @@
       <c r="C10" s="32"/>
       <c r="D10" s="33">
         <f>(D3+D4)*1.1</f>
-        <v>447.70000000000005</v>
+        <v>445.50000000000006</v>
       </c>
       <c r="E10" s="88">
         <v>7.5</v>
       </c>
       <c r="F10" s="88">
         <f>Table1[[#This Row],[Ilość]]*Table1[[#This Row],[Cena]]</f>
-        <v>3357.7500000000005</v>
+        <v>3341.2500000000005</v>
       </c>
       <c r="G10" s="88"/>
       <c r="H10" s="88">
         <f>Table1[[#This Row],[Koszt]]-Table1[[#This Row],[Zaliczka]]</f>
-        <v>3357.7500000000005</v>
+        <v>3341.2500000000005</v>
       </c>
       <c r="I10" s="122"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B11" s="32" t="b">
         <v>0</v>
@@ -19148,7 +19167,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B12" s="32" t="b">
         <v>1</v>
@@ -19174,12 +19193,12 @@
         <v>1620</v>
       </c>
       <c r="I12" s="122" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B13" s="32" t="b">
         <v>0</v>
@@ -19207,7 +19226,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -19215,7 +19234,7 @@
       <c r="E14" s="35"/>
       <c r="F14" s="34">
         <f>SUBTOTAL(109,F3:F13)</f>
-        <v>133737.75</v>
+        <v>133181.25</v>
       </c>
       <c r="G14" s="34">
         <f>SUBTOTAL(109,G3:G13)</f>
@@ -19223,7 +19242,7 @@
       </c>
       <c r="H14" s="34">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>129057.75</v>
+        <v>128501.25</v>
       </c>
       <c r="I14" s="35"/>
     </row>
@@ -19244,7 +19263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4C4521-749B-409C-BE5E-248315EEF2F8}">
   <dimension ref="A1:V34"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19265,35 +19284,35 @@
   <sheetData>
     <row r="1" spans="1:22" ht="33" customHeight="1">
       <c r="A1" s="22" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B1" s="65" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1" s="92" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F1" s="92" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G1" s="92" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1" s="92" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I1" s="92"/>
       <c r="J1" s="93" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K1" s="93" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L1" s="93" t="s">
         <v>21</v>
@@ -19304,7 +19323,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B2" s="38">
         <f>COUNTIFS('Lista uczniów_składki'!D:D,"Tak",'Lista uczniów_składki'!C:C,Podsumowanie!A2)</f>
@@ -19408,11 +19427,11 @@
       </c>
       <c r="C4" s="40">
         <f>COUNTIFS('Lista uczniów_składki'!E:E,"Tak",'Lista uczniów_składki'!C:C,Podsumowanie!A4)</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="38">
         <f t="shared" ref="D4:D8" si="3">SUM(B4:C4)</f>
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4" s="124">
         <v>36</v>
@@ -19432,7 +19451,7 @@
       <c r="I4" s="60"/>
       <c r="J4" s="91">
         <f>SUMIFS('Lista uczniów_składki'!U:U,'Lista uczniów_składki'!C:C,Podsumowanie!A4)</f>
-        <v>20990</v>
+        <v>20450</v>
       </c>
       <c r="K4" s="91">
         <f>SUMIFS('Lista uczniów_składki'!T:T,'Lista uczniów_składki'!C:C,Podsumowanie!A4)</f>
@@ -19440,7 +19459,7 @@
       </c>
       <c r="L4" s="91">
         <f t="shared" si="2"/>
-        <v>-19190</v>
+        <v>-18650</v>
       </c>
       <c r="T4" s="63"/>
       <c r="U4" s="90"/>
@@ -19448,7 +19467,7 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B5" s="38">
         <f>COUNTIFS('Lista uczniów_składki'!D:D,"Tak",'Lista uczniów_składki'!C:C,Podsumowanie!A5)</f>
@@ -19642,7 +19661,7 @@
       <c r="E9" s="63"/>
       <c r="J9" s="91">
         <f>SUM(J2:J8)</f>
-        <v>137790</v>
+        <v>137250</v>
       </c>
       <c r="K9" s="91">
         <f t="shared" ref="K9:L9" si="4">SUM(K2:K8)</f>
@@ -19650,19 +19669,19 @@
       </c>
       <c r="L9" s="91">
         <f t="shared" si="4"/>
-        <v>-116490</v>
+        <v>-115950</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="125" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B11" s="125"/>
       <c r="E11" s="63"/>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B12" s="16">
         <f>SUM(B2:B8)</f>
@@ -19670,17 +19689,17 @@
       </c>
       <c r="C12" s="126">
         <f>SUM(B12:B13)</f>
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E12" s="63"/>
     </row>
     <row r="13" spans="1:22" s="8" customFormat="1">
       <c r="A13" s="29" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B13" s="17">
         <f>SUM(C2:C8)</f>
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C13" s="127"/>
       <c r="E13" s="63"/>
@@ -19689,14 +19708,14 @@
     </row>
     <row r="14" spans="1:22" s="27" customFormat="1" ht="27.75">
       <c r="A14" s="30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B14" s="87">
         <f>Wydatki!D4</f>
         <v>30</v>
       </c>
       <c r="C14" s="124" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D14" s="63"/>
       <c r="E14" s="63"/>
@@ -19720,21 +19739,21 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B15" s="12">
         <f>SUM(Wydatki!F3:F4)</f>
-        <v>101790</v>
+        <v>101250</v>
       </c>
       <c r="E15" s="63"/>
     </row>
     <row r="16" spans="1:22" s="8" customFormat="1">
       <c r="A16" s="29" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B16" s="13">
         <f>SUM(Wydatki!F5:F13)</f>
-        <v>31947.75</v>
+        <v>31931.25</v>
       </c>
       <c r="E16" s="63"/>
       <c r="H16" s="61"/>
@@ -19742,11 +19761,11 @@
     </row>
     <row r="17" spans="1:9" s="8" customFormat="1">
       <c r="A17" s="31" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B17" s="14">
         <f>SUM(B15:B16)</f>
-        <v>133737.75</v>
+        <v>133181.25</v>
       </c>
       <c r="E17" s="63"/>
       <c r="H17" s="61"/>
@@ -19761,7 +19780,7 @@
     </row>
     <row r="19" spans="1:9" s="8" customFormat="1">
       <c r="A19" s="109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B19" s="64">
         <v>430</v>
@@ -19776,7 +19795,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="59" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B20" s="110">
         <f>Wydatki!E3</f>
@@ -19790,50 +19809,50 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B22" s="11">
         <f>B19*B12+B20*B13</f>
-        <v>137790</v>
+        <v>137250</v>
       </c>
       <c r="E22" s="108"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B23" s="12">
         <f>SUM(Table1[Koszt])</f>
-        <v>133737.75</v>
+        <v>133181.25</v>
       </c>
       <c r="E23" s="63"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="21" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B24" s="15">
         <f>B22-B23</f>
-        <v>4052.25</v>
+        <v>4068.75</v>
       </c>
       <c r="E24" s="63"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="22" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E26" s="63"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B27" s="18">
         <f>IF(B2=0,"",B$24/SUM($B$3:$B$8)*B2)</f>
-        <v>696.48046875</v>
+        <v>699.31640625</v>
       </c>
       <c r="E27" s="63"/>
     </row>
@@ -19843,7 +19862,7 @@
       </c>
       <c r="B28" s="18">
         <f>IF(B3=0,"",B$24/SUM($B$3:$B$8)*B3)</f>
-        <v>506.53125</v>
+        <v>508.59375</v>
       </c>
       <c r="E28" s="45"/>
       <c r="H28" s="62"/>
@@ -19855,17 +19874,17 @@
       </c>
       <c r="B29" s="18">
         <f>IF(B4=0,"",B$24/SUM($B$3:$B$8)*B4)</f>
-        <v>738.69140625</v>
+        <v>741.69921875</v>
       </c>
       <c r="E29" s="63"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B30" s="18">
         <f>IF(B5=0,"",B$24/SUM($B$3:$B$8)*B5)</f>
-        <v>738.69140625</v>
+        <v>741.69921875</v>
       </c>
       <c r="E30" s="63"/>
     </row>
@@ -19875,7 +19894,7 @@
       </c>
       <c r="B31" s="18">
         <f>IF(B6=0,"",B$24/SUM($B$3:$B$8)*B6)</f>
-        <v>738.69140625</v>
+        <v>741.69921875</v>
       </c>
       <c r="E31" s="63"/>
     </row>
@@ -19885,7 +19904,7 @@
       </c>
       <c r="B32" s="18">
         <f>IF(B7=0,"",B$24/SUM($B$3:$B$8)*B7)</f>
-        <v>717.5859375</v>
+        <v>720.5078125</v>
       </c>
       <c r="E32" s="63"/>
     </row>
@@ -19895,7 +19914,7 @@
       </c>
       <c r="B33" s="18">
         <f>IF(B8=0,"",B$24/SUM($B$3:$B$8)*B8)</f>
-        <v>612.05859375</v>
+        <v>614.55078125</v>
       </c>
       <c r="E33" s="63"/>
     </row>
@@ -19928,7 +19947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E235FE4-7C05-4EE5-B6BD-B7E167384F75}">
   <dimension ref="A4:F51"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -19948,13 +19967,13 @@
   <sheetData>
     <row r="4" spans="1:5">
       <c r="C4" s="85" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D4" s="67"/>
     </row>
     <row r="5" spans="1:5">
       <c r="C5" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D5" s="68">
         <f>SUM(Podsumowanie!E2:E8)</f>
@@ -19963,7 +19982,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="C6" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D6" s="68">
         <f>SUM(Podsumowanie!B2:B8)</f>
@@ -19972,38 +19991,38 @@
     </row>
     <row r="7" spans="1:5">
       <c r="C7" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D7" s="68">
         <f>SUM(Podsumowanie!C2:C8)</f>
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="C8" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D8" s="68">
         <f>D6+D7</f>
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" customHeight="1">
       <c r="A9" s="130" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B9" s="131" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D9" s="106">
         <f>Podsumowanie!B14</f>
         <v>30</v>
       </c>
       <c r="E9" s="105" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
@@ -20014,7 +20033,7 @@
       <c r="A11" s="130"/>
       <c r="B11" s="131"/>
       <c r="C11" s="85" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D11" s="67"/>
     </row>
@@ -20026,14 +20045,14 @@
         <v>1</v>
       </c>
       <c r="C12" s="70" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D12" s="71">
         <f>Wydatki!F3</f>
-        <v>101790</v>
+        <v>101250</v>
       </c>
       <c r="E12" s="115" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.5">
@@ -20044,7 +20063,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="72" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D13" s="76">
         <f>Wydatki!F4</f>
@@ -20060,14 +20079,14 @@
         <v>1</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D14" s="71">
         <f>Wydatki!F5</f>
         <v>8000</v>
       </c>
       <c r="E14" s="115" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -20078,14 +20097,14 @@
         <v>1</v>
       </c>
       <c r="C15" s="70" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D15" s="71">
         <f>Wydatki!F6</f>
         <v>12000</v>
       </c>
       <c r="E15" s="105" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -20096,14 +20115,14 @@
         <v>1</v>
       </c>
       <c r="C16" s="70" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D16" s="71">
         <f>Wydatki!F7</f>
         <v>1400</v>
       </c>
       <c r="E16" s="115" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20114,7 +20133,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D17" s="71">
         <f>Wydatki!F8</f>
@@ -20130,7 +20149,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D18" s="71">
         <f>Wydatki!F9</f>
@@ -20146,11 +20165,11 @@
         <v>0</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D19" s="71">
         <f>Wydatki!F10</f>
-        <v>3357.7500000000005</v>
+        <v>3341.2500000000005</v>
       </c>
       <c r="E19" s="115"/>
     </row>
@@ -20162,7 +20181,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="73" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D20" s="71">
         <f>Wydatki!F11</f>
@@ -20178,14 +20197,14 @@
         <v>1</v>
       </c>
       <c r="C21" s="73" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D21" s="71">
         <f>Wydatki!F12</f>
         <v>1800</v>
       </c>
       <c r="E21" s="115" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="26.25">
@@ -20196,7 +20215,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="104" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D22" s="107">
         <f>Wydatki!F13</f>
@@ -20206,22 +20225,22 @@
     </row>
     <row r="23" spans="1:6" ht="18.75">
       <c r="C23" s="74" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D23" s="75">
         <f>Wydatki!F14</f>
-        <v>133737.75</v>
+        <v>133181.25</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="C26" s="66" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D26" s="67"/>
     </row>
     <row r="27" spans="1:6" ht="16.5">
       <c r="C27" s="79" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D27" s="78">
         <f>Podsumowanie!B19</f>
@@ -20234,7 +20253,7 @@
     </row>
     <row r="28" spans="1:6" ht="16.5">
       <c r="C28" s="79" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D28" s="78">
         <f>Podsumowanie!B20</f>
@@ -20247,7 +20266,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="C31" s="102" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D31" s="67"/>
       <c r="E31" s="67"/>
@@ -20258,10 +20277,10 @@
         <v>2</v>
       </c>
       <c r="D32" s="97" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E32" s="97" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F32" s="97" t="s">
         <v>21</v>
@@ -20269,7 +20288,7 @@
     </row>
     <row r="33" spans="3:6">
       <c r="C33" s="99" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D33" s="95">
         <f>SUMIFS('Lista uczniów_składki'!U:U,'Lista uczniów_składki'!C:C,'Do wiadomości rodziców'!C33)</f>
@@ -20307,7 +20326,7 @@
       </c>
       <c r="D35" s="95">
         <f>SUMIFS('Lista uczniów_składki'!U:U,'Lista uczniów_składki'!C:C,'Do wiadomości rodziców'!C35)</f>
-        <v>20990</v>
+        <v>20450</v>
       </c>
       <c r="E35" s="96">
         <f>SUMIFS('Lista uczniów_składki'!T:T,'Lista uczniów_składki'!C:C,'Do wiadomości rodziców'!C35)</f>
@@ -20315,12 +20334,12 @@
       </c>
       <c r="F35" s="91">
         <f t="shared" si="0"/>
-        <v>-19190</v>
+        <v>-18650</v>
       </c>
     </row>
     <row r="36" spans="3:6">
       <c r="C36" s="101" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D36" s="95">
         <f>SUMIFS('Lista uczniów_składki'!U:U,'Lista uczniów_składki'!C:C,'Do wiadomości rodziców'!C36)</f>
@@ -20388,11 +20407,11 @@
     </row>
     <row r="40" spans="3:6">
       <c r="C40" s="103" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D40" s="121">
         <f>SUBTOTAL(109,D33:D39)</f>
-        <v>137790</v>
+        <v>137250</v>
       </c>
       <c r="E40" s="121">
         <f>SUBTOTAL(109,E33:E39)</f>
@@ -20400,7 +20419,7 @@
       </c>
       <c r="F40" s="121">
         <f>SUBTOTAL(109,Table5[Delta])</f>
-        <v>-116490</v>
+        <v>-115950</v>
       </c>
     </row>
     <row r="41" spans="3:6">
@@ -20417,7 +20436,7 @@
     </row>
     <row r="44" spans="3:6">
       <c r="C44" s="132" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D44" s="132"/>
       <c r="E44" s="132"/>
@@ -20428,21 +20447,21 @@
     </row>
     <row r="45" spans="3:6">
       <c r="C45" s="118" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D45" s="119" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E45" s="119" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F45" s="119" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46" spans="3:6">
       <c r="C46" s="123" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D46" s="71">
         <v>5750</v>
@@ -20457,7 +20476,7 @@
     </row>
     <row r="47" spans="3:6">
       <c r="C47" s="123" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D47" s="71">
         <v>7350</v>
@@ -20472,7 +20491,7 @@
     </row>
     <row r="48" spans="3:6">
       <c r="C48" s="123" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D48" s="71">
         <v>6000</v>
@@ -20530,7 +20549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FAEACC5-CE8D-41C2-A817-9575DF4970B6}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -20544,27 +20563,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B2" s="114">
         <v>46275</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D2" s="43" t="b">
         <v>1</v>
@@ -20572,13 +20591,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B3" s="114">
         <v>46401</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D3" s="43" t="b">
         <v>0</v>
@@ -20586,13 +20605,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B4" s="114">
         <v>46395</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D4" s="43" t="b">
         <v>0</v>
@@ -20600,13 +20619,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B5" s="114">
         <v>46254</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D5" s="43" t="b">
         <v>0</v>
@@ -20614,13 +20633,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B6" s="114">
         <v>46412</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D6" s="43" t="b">
         <v>0</v>
@@ -20628,13 +20647,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B7" s="114">
         <v>46185</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D7" s="43" t="b">
         <v>1</v>
@@ -20642,13 +20661,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B8" s="114">
         <v>46192</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D8" s="43" t="b">
         <v>1</v>
@@ -20656,13 +20675,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B9" s="114">
         <v>46192</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D9" s="43" t="b">
         <v>0</v>
@@ -20670,13 +20689,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B10" s="114">
         <v>46267</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D10" s="43" t="b">
         <v>0</v>
@@ -20684,13 +20703,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B11" s="114">
         <v>46356</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D11" s="43" t="b">
         <v>0</v>
@@ -20758,7 +20777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B90623C-A02B-45BC-8CCB-535472D2A61A}">
   <dimension ref="B3:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20769,24 +20788,24 @@
   <sheetData>
     <row r="3" spans="2:4">
       <c r="B3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C3">
         <v>5750</v>
       </c>
       <c r="D3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C4">
         <v>500</v>
       </c>
       <c r="D4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -20794,7 +20813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8936F2-E3A6-406E-9341-D29A69F6583E}">
   <dimension ref="A1:M277"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -20808,16 +20827,16 @@
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="65.25" customHeight="1">
       <c r="A1" s="55" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B1" s="86" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C1" s="86" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D1" s="55" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E1" s="55" t="s">
         <v>1</v>
@@ -20829,10 +20848,10 @@
         <v>2</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -20846,7 +20865,7 @@
         <v>46125.645833333336</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>25</v>
@@ -20884,7 +20903,7 @@
         <v>46125.647222222222</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>29</v>
@@ -20922,7 +20941,7 @@
         <v>46125.648611111108</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E4" s="47" t="s">
         <v>31</v>
@@ -20960,7 +20979,7 @@
         <v>46125.65</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E5" s="47" t="s">
         <v>35</v>
@@ -20998,7 +21017,7 @@
         <v>46125.652777777781</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E6" s="47" t="s">
         <v>37</v>
@@ -21036,7 +21055,7 @@
         <v>46125.658333333333</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E7" s="47" t="s">
         <v>39</v>
@@ -21074,7 +21093,7 @@
         <v>46125.67083333333</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E8" s="47" t="s">
         <v>35</v>
@@ -21112,7 +21131,7 @@
         <v>46125.677083333336</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E9" s="47" t="s">
         <v>42</v>
@@ -21150,7 +21169,7 @@
         <v>46125.682638888888</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E10" s="47" t="s">
         <v>44</v>
@@ -21188,7 +21207,7 @@
         <v>46125.697222222225</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E11" s="47" t="s">
         <v>46</v>
@@ -21226,7 +21245,7 @@
         <v>46125.70208333333</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E12" s="47" t="s">
         <v>48</v>
@@ -21264,7 +21283,7 @@
         <v>46125.72152777778</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E13" s="47" t="s">
         <v>50</v>
@@ -21302,7 +21321,7 @@
         <v>46125.762499999997</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E14" s="47" t="s">
         <v>52</v>
@@ -21340,7 +21359,7 @@
         <v>46125.763888888891</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E15" s="47" t="s">
         <v>55</v>
@@ -21378,7 +21397,7 @@
         <v>46125.765277777777</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E16" s="47" t="s">
         <v>57</v>
@@ -21416,7 +21435,7 @@
         <v>46125.767361111109</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E17" s="47" t="s">
         <v>59</v>
@@ -21454,7 +21473,7 @@
         <v>46125.768750000003</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E18" s="47" t="s">
         <v>61</v>
@@ -21492,7 +21511,7 @@
         <v>46125.770138888889</v>
       </c>
       <c r="D19" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E19" s="47" t="s">
         <v>63</v>
@@ -21530,7 +21549,7 @@
         <v>46125.774305555555</v>
       </c>
       <c r="D20" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E20" s="47" t="s">
         <v>65</v>
@@ -21568,7 +21587,7 @@
         <v>46125.777777777781</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E21" s="47" t="s">
         <v>67</v>
@@ -21606,7 +21625,7 @@
         <v>46125.790972222225</v>
       </c>
       <c r="D22" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E22" s="47" t="s">
         <v>25</v>
@@ -21644,7 +21663,7 @@
         <v>46125.84375</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E23" s="47" t="s">
         <v>70</v>
@@ -21682,7 +21701,7 @@
         <v>46125.845138888886</v>
       </c>
       <c r="D24" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E24" s="47" t="s">
         <v>63</v>
@@ -21720,7 +21739,7 @@
         <v>46125.84652777778</v>
       </c>
       <c r="D25" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E25" s="47" t="s">
         <v>73</v>
@@ -21758,7 +21777,7 @@
         <v>46125.866666666669</v>
       </c>
       <c r="D26" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E26" s="47" t="s">
         <v>63</v>
@@ -21796,7 +21815,7 @@
         <v>46125.892361111109</v>
       </c>
       <c r="D27" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E27" s="47" t="s">
         <v>76</v>
@@ -21834,7 +21853,7 @@
         <v>46125.897222222222</v>
       </c>
       <c r="D28" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E28" s="47" t="s">
         <v>78</v>
@@ -21872,7 +21891,7 @@
         <v>46126.37777777778</v>
       </c>
       <c r="D29" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E29" s="47" t="s">
         <v>80</v>
@@ -21910,7 +21929,7 @@
         <v>46126.384027777778</v>
       </c>
       <c r="D30" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E30" s="47" t="s">
         <v>65</v>
@@ -21948,7 +21967,7 @@
         <v>46126.384027777778</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E31" s="47" t="s">
         <v>83</v>
@@ -21986,7 +22005,7 @@
         <v>46126.405555555553</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E32" s="47" t="s">
         <v>85</v>
@@ -22024,7 +22043,7 @@
         <v>46126.522916666669</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E33" s="47" t="s">
         <v>73</v>
@@ -22062,7 +22081,7 @@
         <v>46126.522916666669</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E34" s="47" t="s">
         <v>89</v>
@@ -22100,7 +22119,7 @@
         <v>46126.523611111108</v>
       </c>
       <c r="D35" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E35" s="47" t="s">
         <v>89</v>
@@ -22138,13 +22157,13 @@
         <v>46126.523611111108</v>
       </c>
       <c r="D36" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F36" s="47" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G36" s="47" t="s">
         <v>87</v>
@@ -22176,7 +22195,7 @@
         <v>46126.523611111108</v>
       </c>
       <c r="D37" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E37" s="47" t="s">
         <v>67</v>
@@ -22214,7 +22233,7 @@
         <v>46126.525000000001</v>
       </c>
       <c r="D38" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E38" s="47" t="s">
         <v>95</v>
@@ -22252,7 +22271,7 @@
         <v>46126.525000000001</v>
       </c>
       <c r="D39" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E39" s="47" t="s">
         <v>73</v>
@@ -22290,7 +22309,7 @@
         <v>46126.525000000001</v>
       </c>
       <c r="D40" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E40" s="47" t="s">
         <v>98</v>
@@ -22328,7 +22347,7 @@
         <v>46126.525694444441</v>
       </c>
       <c r="D41" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E41" s="47" t="s">
         <v>100</v>
@@ -22366,7 +22385,7 @@
         <v>46126.525694444441</v>
       </c>
       <c r="D42" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E42" s="47" t="s">
         <v>59</v>
@@ -22404,7 +22423,7 @@
         <v>46126.526388888888</v>
       </c>
       <c r="D43" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>46</v>
@@ -22442,7 +22461,7 @@
         <v>46126.706944444442</v>
       </c>
       <c r="D44" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E44" s="47" t="s">
         <v>73</v>
@@ -22480,7 +22499,7 @@
         <v>46126.915277777778</v>
       </c>
       <c r="D45" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E45" s="47" t="s">
         <v>105</v>
@@ -22518,7 +22537,7 @@
         <v>46127.85</v>
       </c>
       <c r="D46" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E46" s="47" t="s">
         <v>107</v>
@@ -22556,7 +22575,7 @@
         <v>46127.866666666669</v>
       </c>
       <c r="D47" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E47" s="47" t="s">
         <v>109</v>
@@ -22594,7 +22613,7 @@
         <v>46127.992361111108</v>
       </c>
       <c r="D48" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E48" s="47" t="s">
         <v>111</v>
@@ -22632,7 +22651,7 @@
         <v>46128.43472222222</v>
       </c>
       <c r="D49" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E49" s="47" t="s">
         <v>59</v>
@@ -22670,7 +22689,7 @@
         <v>46128.43472222222</v>
       </c>
       <c r="D50" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E50" s="47" t="s">
         <v>115</v>
@@ -22708,7 +22727,7 @@
         <v>46128.43472222222</v>
       </c>
       <c r="D51" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E51" s="47" t="s">
         <v>73</v>
@@ -22746,7 +22765,7 @@
         <v>46128.436805555553</v>
       </c>
       <c r="D52" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E52" s="47" t="s">
         <v>118</v>
@@ -22784,7 +22803,7 @@
         <v>46128.436805555553</v>
       </c>
       <c r="D53" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E53" s="47" t="s">
         <v>37</v>
@@ -22822,7 +22841,7 @@
         <v>46128.436805555553</v>
       </c>
       <c r="D54" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E54" s="47" t="s">
         <v>73</v>
@@ -22860,7 +22879,7 @@
         <v>46128.4375</v>
       </c>
       <c r="D55" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E55" s="47" t="s">
         <v>122</v>
@@ -22898,7 +22917,7 @@
         <v>46128.4375</v>
       </c>
       <c r="D56" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E56" s="47" t="s">
         <v>63</v>
@@ -22936,7 +22955,7 @@
         <v>46128.439583333333</v>
       </c>
       <c r="D57" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E57" s="47" t="s">
         <v>124</v>
@@ -22974,7 +22993,7 @@
         <v>46128.439583333333</v>
       </c>
       <c r="D58" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E58" s="47" t="s">
         <v>46</v>
@@ -23012,7 +23031,7 @@
         <v>46128.439583333333</v>
       </c>
       <c r="D59" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E59" s="47" t="s">
         <v>127</v>
@@ -23050,7 +23069,7 @@
         <v>46128.44027777778</v>
       </c>
       <c r="D60" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E60" s="47" t="s">
         <v>92</v>
@@ -23088,7 +23107,7 @@
         <v>46128.440972222219</v>
       </c>
       <c r="D61" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E61" s="47" t="s">
         <v>130</v>
@@ -23126,13 +23145,13 @@
         <v>46128.440972222219</v>
       </c>
       <c r="D62" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F62" s="47" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G62" s="47" t="s">
         <v>113</v>
@@ -23164,7 +23183,7 @@
         <v>46128.440972222219</v>
       </c>
       <c r="D63" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E63" s="47" t="s">
         <v>52</v>
@@ -23202,7 +23221,7 @@
         <v>46128.440972222219</v>
       </c>
       <c r="D64" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E64" s="47" t="s">
         <v>135</v>
@@ -23240,7 +23259,7 @@
         <v>46128.442361111112</v>
       </c>
       <c r="D65" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E65" s="47" t="s">
         <v>65</v>
@@ -23278,7 +23297,7 @@
         <v>46128.479166666664</v>
       </c>
       <c r="D66" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E66" s="47" t="s">
         <v>29</v>
@@ -23316,7 +23335,7 @@
         <v>46128.693055555559</v>
       </c>
       <c r="D67" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E67" s="47" t="s">
         <v>139</v>
@@ -23354,7 +23373,7 @@
         <v>46128.724305555559</v>
       </c>
       <c r="D68" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E68" s="47" t="s">
         <v>63</v>
@@ -23392,7 +23411,7 @@
         <v>46128.788888888892</v>
       </c>
       <c r="D69" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E69" s="47" t="s">
         <v>63</v>
@@ -23430,7 +23449,7 @@
         <v>46128.838194444441</v>
       </c>
       <c r="D70" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>25</v>
@@ -23468,7 +23487,7 @@
         <v>46128.85</v>
       </c>
       <c r="D71" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E71" s="47" t="s">
         <v>100</v>
@@ -23506,7 +23525,7 @@
         <v>46128.925000000003</v>
       </c>
       <c r="D72" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E72" s="47" t="s">
         <v>29</v>
@@ -23544,7 +23563,7 @@
         <v>46129.521527777775</v>
       </c>
       <c r="D73" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E73" s="47" t="s">
         <v>146</v>
@@ -23582,7 +23601,7 @@
         <v>46129.619444444441</v>
       </c>
       <c r="D74" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E74" s="47" t="s">
         <v>63</v>
@@ -23620,7 +23639,7 @@
         <v>46129.661111111112</v>
       </c>
       <c r="D75" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E75" s="47" t="s">
         <v>63</v>
@@ -23658,7 +23677,7 @@
         <v>46129.880555555559</v>
       </c>
       <c r="D76" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E76" s="47" t="s">
         <v>59</v>
@@ -23696,7 +23715,7 @@
         <v>46129.929861111108</v>
       </c>
       <c r="D77" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E77" s="47" t="s">
         <v>150</v>
@@ -23734,7 +23753,7 @@
         <v>46130.60833333333</v>
       </c>
       <c r="D78" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E78" s="47" t="s">
         <v>151</v>
@@ -23772,7 +23791,7 @@
         <v>46130.65</v>
       </c>
       <c r="D79" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E79" s="47" t="s">
         <v>153</v>
@@ -23810,7 +23829,7 @@
         <v>46130.883333333331</v>
       </c>
       <c r="D80" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E80" s="47" t="s">
         <v>155</v>
@@ -23848,13 +23867,13 @@
         <v>46131.617361111108</v>
       </c>
       <c r="D81" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E81" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="F81" s="47" t="s">
         <v>157</v>
-      </c>
-      <c r="F81" s="47" t="s">
-        <v>156</v>
       </c>
       <c r="G81" s="47" t="s">
         <v>87</v>
@@ -23886,13 +23905,13 @@
         <v>46131.762499999997</v>
       </c>
       <c r="D82" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E82" s="47" t="s">
         <v>59</v>
       </c>
       <c r="F82" s="47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G82" s="47" t="s">
         <v>26</v>
@@ -23924,13 +23943,13 @@
         <v>46131.979861111111</v>
       </c>
       <c r="D83" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E83" s="47" t="s">
         <v>65</v>
       </c>
       <c r="F83" s="47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G83" s="47" t="s">
         <v>113</v>
@@ -23962,7 +23981,7 @@
         <v>46131.979861111111</v>
       </c>
       <c r="D84" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E84" s="47" t="s">
         <v>78</v>
@@ -24000,16 +24019,16 @@
         <v>46133.536111111112</v>
       </c>
       <c r="D85" s="47" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E85" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="F85" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="F85" s="47" t="s">
-        <v>160</v>
-      </c>
       <c r="G85" s="47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H85" s="47" t="s">
         <v>27</v>
@@ -24038,13 +24057,13 @@
         <v>46134.777083333334</v>
       </c>
       <c r="D86" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E86" s="49" t="s">
         <v>76</v>
       </c>
       <c r="F86" s="49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G86" s="49" t="s">
         <v>113</v>
@@ -24076,13 +24095,13 @@
         <v>46134.780555555553</v>
       </c>
       <c r="D87" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E87" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="F87" s="51" t="s">
         <v>165</v>
-      </c>
-      <c r="F87" s="51" t="s">
-        <v>164</v>
       </c>
       <c r="G87" s="51" t="s">
         <v>32</v>
@@ -24114,13 +24133,13 @@
         <v>46134.780555555553</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E88" s="49" t="s">
         <v>59</v>
       </c>
       <c r="F88" s="49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G88" s="49" t="s">
         <v>53</v>
@@ -24152,13 +24171,13 @@
         <v>46135.796527777777</v>
       </c>
       <c r="D89" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E89" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="F89" s="51" t="s">
         <v>168</v>
-      </c>
-      <c r="F89" s="51" t="s">
-        <v>167</v>
       </c>
       <c r="G89" s="51" t="s">
         <v>53</v>
@@ -24190,13 +24209,13 @@
         <v>46135.796527777777</v>
       </c>
       <c r="D90" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E90" s="49" t="s">
         <v>155</v>
       </c>
       <c r="F90" s="49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G90" s="49" t="s">
         <v>53</v>
@@ -24228,16 +24247,16 @@
         <v>46139.715277777781</v>
       </c>
       <c r="D91" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E91" s="49" t="s">
         <v>122</v>
       </c>
       <c r="F91" s="49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G91" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H91" s="49" t="s">
         <v>27</v>
@@ -24266,7 +24285,7 @@
         <v>46139.715277777781</v>
       </c>
       <c r="D92" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E92" s="51" t="s">
         <v>59</v>
@@ -24275,7 +24294,7 @@
         <v>110</v>
       </c>
       <c r="G92" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H92" s="51" t="s">
         <v>27</v>
@@ -24304,16 +24323,16 @@
         <v>46139.715277777781</v>
       </c>
       <c r="D93" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E93" s="49" t="s">
         <v>80</v>
       </c>
       <c r="F93" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="G93" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="G93" s="49" t="s">
-        <v>171</v>
       </c>
       <c r="H93" s="49" t="s">
         <v>27</v>
@@ -24342,16 +24361,16 @@
         <v>46139.715277777781</v>
       </c>
       <c r="D94" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E94" s="51" t="s">
         <v>42</v>
       </c>
       <c r="F94" s="51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G94" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H94" s="51" t="s">
         <v>27</v>
@@ -24380,16 +24399,16 @@
         <v>46139.715277777781</v>
       </c>
       <c r="D95" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E95" s="49" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F95" s="49" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G95" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H95" s="49" t="s">
         <v>27</v>
@@ -24418,16 +24437,16 @@
         <v>46139.716666666667</v>
       </c>
       <c r="D96" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E96" s="51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F96" s="51" t="s">
         <v>140</v>
       </c>
       <c r="G96" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H96" s="51" t="s">
         <v>27</v>
@@ -24456,16 +24475,16 @@
         <v>46139.722916666666</v>
       </c>
       <c r="D97" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E97" s="51" t="s">
         <v>39</v>
       </c>
       <c r="F97" s="51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G97" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H97" s="51" t="s">
         <v>27</v>
@@ -24494,16 +24513,16 @@
         <v>46139.753472222219</v>
       </c>
       <c r="D98" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E98" s="49" t="s">
+        <v>179</v>
+      </c>
+      <c r="F98" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="F98" s="49" t="s">
-        <v>177</v>
-      </c>
       <c r="G98" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H98" s="49" t="s">
         <v>27</v>
@@ -24532,16 +24551,16 @@
         <v>46139.759027777778</v>
       </c>
       <c r="D99" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E99" s="51" t="s">
+        <v>181</v>
+      </c>
+      <c r="F99" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="F99" s="51" t="s">
-        <v>179</v>
-      </c>
       <c r="G99" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H99" s="51" t="s">
         <v>27</v>
@@ -24570,16 +24589,16 @@
         <v>46139.760416666664</v>
       </c>
       <c r="D100" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E100" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="F100" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="F100" s="49" t="s">
-        <v>181</v>
-      </c>
       <c r="G100" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H100" s="49" t="s">
         <v>27</v>
@@ -24608,16 +24627,16 @@
         <v>46139.803472222222</v>
       </c>
       <c r="D101" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E101" s="51" t="s">
         <v>57</v>
       </c>
       <c r="F101" s="51" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G101" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H101" s="51" t="s">
         <v>27</v>
@@ -24646,16 +24665,16 @@
         <v>46139.808333333334</v>
       </c>
       <c r="D102" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E102" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="F102" s="49" t="s">
         <v>185</v>
       </c>
-      <c r="F102" s="49" t="s">
-        <v>184</v>
-      </c>
       <c r="G102" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H102" s="49" t="s">
         <v>27</v>
@@ -24684,16 +24703,16 @@
         <v>46139.888888888891</v>
       </c>
       <c r="D103" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E103" s="51" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F103" s="51" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G103" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H103" s="51" t="s">
         <v>27</v>
@@ -24722,16 +24741,16 @@
         <v>46140.425000000003</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E104" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="F104" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="F104" s="49" t="s">
-        <v>188</v>
-      </c>
       <c r="G104" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H104" s="49" t="s">
         <v>27</v>
@@ -24760,16 +24779,16 @@
         <v>46140.604861111111</v>
       </c>
       <c r="D105" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E105" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="F105" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="F105" s="49" t="s">
-        <v>190</v>
-      </c>
       <c r="G105" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H105" s="49" t="s">
         <v>27</v>
@@ -24798,16 +24817,16 @@
         <v>46140.616666666669</v>
       </c>
       <c r="D106" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E106" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F106" s="51" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G106" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H106" s="51" t="s">
         <v>27</v>
@@ -24836,16 +24855,16 @@
         <v>46140.972222222219</v>
       </c>
       <c r="D107" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E107" s="49" t="s">
         <v>73</v>
       </c>
       <c r="F107" s="49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G107" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H107" s="49" t="s">
         <v>27</v>
@@ -24874,16 +24893,16 @@
         <v>46140.972222222219</v>
       </c>
       <c r="D108" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E108" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="F108" s="49" t="s">
         <v>195</v>
       </c>
-      <c r="F108" s="49" t="s">
-        <v>194</v>
-      </c>
       <c r="G108" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H108" s="49" t="s">
         <v>27</v>
@@ -24912,16 +24931,16 @@
         <v>46142.597222222219</v>
       </c>
       <c r="D109" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E109" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="F109" s="51" t="s">
         <v>197</v>
       </c>
-      <c r="F109" s="51" t="s">
-        <v>196</v>
-      </c>
       <c r="G109" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H109" s="51" t="s">
         <v>27</v>
@@ -24950,13 +24969,13 @@
         <v>46153.702777777777</v>
       </c>
       <c r="D110" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E110" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="F110" s="49" t="s">
         <v>199</v>
-      </c>
-      <c r="F110" s="49" t="s">
-        <v>198</v>
       </c>
       <c r="G110" s="49" t="s">
         <v>53</v>
@@ -24988,16 +25007,16 @@
         <v>46164.888194444444</v>
       </c>
       <c r="D111" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E111" s="51" t="s">
         <v>63</v>
       </c>
       <c r="F111" s="51" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G111" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H111" s="51" t="s">
         <v>27</v>
@@ -25026,16 +25045,16 @@
         <v>46165.59375</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E112" s="49" t="s">
+        <v>203</v>
+      </c>
+      <c r="F112" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="F112" s="49" t="s">
-        <v>201</v>
-      </c>
       <c r="G112" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H112" s="49" t="s">
         <v>27</v>
@@ -25064,16 +25083,16 @@
         <v>46165.59375</v>
       </c>
       <c r="D113" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E113" s="51" t="s">
         <v>127</v>
       </c>
       <c r="F113" s="51" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G113" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H113" s="51" t="s">
         <v>27</v>
@@ -25102,13 +25121,13 @@
         <v>46167.594444444447</v>
       </c>
       <c r="D114" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E114" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="F114" s="49" t="s">
         <v>204</v>
-      </c>
-      <c r="F114" s="49" t="s">
-        <v>203</v>
       </c>
       <c r="G114" s="49" t="s">
         <v>32</v>
@@ -25140,13 +25159,13 @@
         <v>46167.85</v>
       </c>
       <c r="D115" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E115" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="F115" s="51" t="s">
         <v>206</v>
-      </c>
-      <c r="F115" s="51" t="s">
-        <v>205</v>
       </c>
       <c r="G115" s="51" t="s">
         <v>87</v>
@@ -25178,13 +25197,13 @@
         <v>46167.854861111111</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E116" s="49" t="s">
         <v>44</v>
       </c>
       <c r="F116" s="49" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G116" s="49" t="s">
         <v>87</v>
@@ -25216,13 +25235,13 @@
         <v>46167.890972222223</v>
       </c>
       <c r="D117" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E117" s="51" t="s">
+        <v>210</v>
+      </c>
+      <c r="F117" s="51" t="s">
         <v>209</v>
-      </c>
-      <c r="F117" s="51" t="s">
-        <v>208</v>
       </c>
       <c r="G117" s="51" t="s">
         <v>87</v>
@@ -25254,13 +25273,13 @@
         <v>46167.92291666667</v>
       </c>
       <c r="D118" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E118" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="F118" s="49" t="s">
         <v>211</v>
-      </c>
-      <c r="F118" s="49" t="s">
-        <v>210</v>
       </c>
       <c r="G118" s="49" t="s">
         <v>87</v>
@@ -25292,13 +25311,13 @@
         <v>46167.929166666669</v>
       </c>
       <c r="D119" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E119" s="51" t="s">
         <v>73</v>
       </c>
       <c r="F119" s="51" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G119" s="51" t="s">
         <v>32</v>
@@ -25330,13 +25349,13 @@
         <v>46167.933333333334</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E120" s="49" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F120" s="49" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G120" s="49" t="s">
         <v>113</v>
@@ -25368,13 +25387,13 @@
         <v>46168.370833333334</v>
       </c>
       <c r="D121" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E121" s="51" t="s">
         <v>57</v>
       </c>
       <c r="F121" s="51" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G121" s="51" t="s">
         <v>32</v>
@@ -25406,7 +25425,7 @@
         <v>46168.401388888888</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E122" s="49" t="s">
         <v>46</v>
@@ -25444,13 +25463,13 @@
         <v>46168.402118055601</v>
       </c>
       <c r="D123" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E123" s="49" t="s">
         <v>59</v>
       </c>
       <c r="F123" s="49" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G123" s="49" t="s">
         <v>32</v>
@@ -25482,13 +25501,13 @@
         <v>46168.406145833302</v>
       </c>
       <c r="D124" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E124" s="51" t="s">
         <v>124</v>
       </c>
       <c r="F124" s="51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G124" s="51" t="s">
         <v>32</v>
@@ -25520,13 +25539,13 @@
         <v>46168.429502314801</v>
       </c>
       <c r="D125" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E125" s="49" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F125" s="49" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G125" s="49" t="s">
         <v>32</v>
@@ -25558,16 +25577,16 @@
         <v>46168.470891203702</v>
       </c>
       <c r="D126" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E126" s="51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F126" s="51" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G126" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H126" s="51" t="s">
         <v>27</v>
@@ -25596,16 +25615,16 @@
         <v>46168.472280092603</v>
       </c>
       <c r="D127" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E127" s="51" t="s">
         <v>83</v>
       </c>
       <c r="F127" s="51" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G127" s="51" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H127" s="51" t="s">
         <v>27</v>
@@ -25634,16 +25653,16 @@
         <v>46168.472476851799</v>
       </c>
       <c r="D128" s="51" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E128" s="51" t="s">
         <v>63</v>
       </c>
       <c r="F128" s="51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G128" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H128" s="51" t="s">
         <v>27</v>
@@ -25672,16 +25691,16 @@
         <v>46168.477511574099</v>
       </c>
       <c r="D129" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E129" s="49" t="s">
         <v>73</v>
       </c>
       <c r="F129" s="49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G129" s="49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H129" s="49" t="s">
         <v>27</v>
@@ -25710,7 +25729,7 @@
         <v>46168.484293981499</v>
       </c>
       <c r="D130" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E130" s="53" t="s">
         <v>73</v>
@@ -25719,7 +25738,7 @@
         <v>34</v>
       </c>
       <c r="G130" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H130" s="53" t="s">
         <v>27</v>
@@ -25748,13 +25767,13 @@
         <v>46168.519641203697</v>
       </c>
       <c r="D131" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E131" s="53" t="s">
         <v>46</v>
       </c>
       <c r="F131" s="53" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G131" s="53" t="s">
         <v>87</v>
@@ -25786,16 +25805,16 @@
         <v>46168.583449074104</v>
       </c>
       <c r="D132" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E132" s="53" t="s">
         <v>37</v>
       </c>
       <c r="F132" s="53" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G132" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H132" s="53" t="s">
         <v>27</v>
@@ -25824,16 +25843,16 @@
         <v>46168.583541666703</v>
       </c>
       <c r="D133" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E133" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="F133" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="F133" s="53" t="s">
-        <v>224</v>
-      </c>
       <c r="G133" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H133" s="53" t="s">
         <v>27</v>
@@ -25862,16 +25881,16 @@
         <v>46168.5835532407</v>
       </c>
       <c r="D134" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E134" s="53" t="s">
         <v>46</v>
       </c>
       <c r="F134" s="53" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G134" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H134" s="53" t="s">
         <v>27</v>
@@ -25900,16 +25919,16 @@
         <v>46168.583564814799</v>
       </c>
       <c r="D135" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E135" s="53" t="s">
         <v>29</v>
       </c>
       <c r="F135" s="53" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G135" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H135" s="53" t="s">
         <v>27</v>
@@ -25938,16 +25957,16 @@
         <v>46168.583634259303</v>
       </c>
       <c r="D136" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E136" s="53" t="s">
         <v>65</v>
       </c>
       <c r="F136" s="53" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G136" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H136" s="53" t="s">
         <v>27</v>
@@ -25976,16 +25995,16 @@
         <v>46168.584340277797</v>
       </c>
       <c r="D137" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E137" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="F137" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="F137" s="53" t="s">
-        <v>228</v>
-      </c>
       <c r="G137" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H137" s="53" t="s">
         <v>27</v>
@@ -26014,16 +26033,16 @@
         <v>46168.5844560185</v>
       </c>
       <c r="D138" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E138" s="53" t="s">
         <v>63</v>
       </c>
       <c r="F138" s="53" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G138" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H138" s="53" t="s">
         <v>27</v>
@@ -26052,16 +26071,16 @@
         <v>46168.586053240702</v>
       </c>
       <c r="D139" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E139" s="53" t="s">
         <v>59</v>
       </c>
       <c r="F139" s="53" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G139" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H139" s="53" t="s">
         <v>27</v>
@@ -26090,16 +26109,16 @@
         <v>46168.586192129602</v>
       </c>
       <c r="D140" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E140" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F140" s="53" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G140" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H140" s="53" t="s">
         <v>27</v>
@@ -26128,16 +26147,16 @@
         <v>46168.588125000002</v>
       </c>
       <c r="D141" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E141" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F141" s="53" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G141" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H141" s="53" t="s">
         <v>27</v>
@@ -26166,16 +26185,16 @@
         <v>46168.589942129598</v>
       </c>
       <c r="D142" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E142" s="53" t="s">
         <v>35</v>
       </c>
       <c r="F142" s="53" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G142" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H142" s="53" t="s">
         <v>27</v>
@@ -26204,13 +26223,13 @@
         <v>46168.593043981498</v>
       </c>
       <c r="D143" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E143" s="53" t="s">
         <v>31</v>
       </c>
       <c r="F143" s="53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G143" s="53" t="s">
         <v>32</v>
@@ -26242,16 +26261,16 @@
         <v>46168.595381944397</v>
       </c>
       <c r="D144" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E144" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F144" s="53" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G144" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H144" s="53" t="s">
         <v>27</v>
@@ -26280,16 +26299,16 @@
         <v>46168.607453703698</v>
       </c>
       <c r="D145" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E145" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="F145" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="F145" s="53" t="s">
-        <v>237</v>
-      </c>
       <c r="G145" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H145" s="53" t="s">
         <v>27</v>
@@ -26318,16 +26337,16 @@
         <v>46168.629259259302</v>
       </c>
       <c r="D146" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E146" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F146" s="53" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G146" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H146" s="53" t="s">
         <v>27</v>
@@ -26356,16 +26375,16 @@
         <v>46168.648854166699</v>
       </c>
       <c r="D147" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E147" s="53" t="s">
         <v>35</v>
       </c>
       <c r="F147" s="53" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G147" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H147" s="53" t="s">
         <v>27</v>
@@ -26394,16 +26413,16 @@
         <v>46168.650486111103</v>
       </c>
       <c r="D148" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E148" s="53" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F148" s="53" t="s">
         <v>72</v>
       </c>
       <c r="G148" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H148" s="53" t="s">
         <v>27</v>
@@ -26432,13 +26451,13 @@
         <v>46168.655462962997</v>
       </c>
       <c r="D149" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E149" s="53" t="s">
         <v>29</v>
       </c>
       <c r="F149" s="53" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G149" s="53" t="s">
         <v>32</v>
@@ -26470,16 +26489,16 @@
         <v>46168.668182870402</v>
       </c>
       <c r="D150" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E150" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="F150" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="F150" s="53" t="s">
-        <v>242</v>
-      </c>
       <c r="G150" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H150" s="53" t="s">
         <v>27</v>
@@ -26508,10 +26527,10 @@
         <v>46168.689687500002</v>
       </c>
       <c r="D151" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E151" s="53" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F151" s="53" t="s">
         <v>86</v>
@@ -26546,10 +26565,10 @@
         <v>46168.709189814799</v>
       </c>
       <c r="D152" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E152" s="53" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F152" s="53" t="s">
         <v>145</v>
@@ -26584,16 +26603,16 @@
         <v>46168.742303240702</v>
       </c>
       <c r="D153" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E153" s="53" t="s">
+        <v>248</v>
+      </c>
+      <c r="F153" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="F153" s="53" t="s">
-        <v>246</v>
-      </c>
       <c r="G153" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H153" s="53" t="s">
         <v>27</v>
@@ -26622,13 +26641,13 @@
         <v>46168.772951388899</v>
       </c>
       <c r="D154" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E154" s="53" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F154" s="53" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G154" s="53" t="s">
         <v>32</v>
@@ -26660,16 +26679,16 @@
         <v>46168.792337963001</v>
       </c>
       <c r="D155" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E155" s="53" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F155" s="53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G155" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H155" s="53" t="s">
         <v>27</v>
@@ -26698,16 +26717,16 @@
         <v>46168.795405092598</v>
       </c>
       <c r="D156" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E156" s="53" t="s">
         <v>67</v>
       </c>
       <c r="F156" s="53" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G156" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H156" s="53" t="s">
         <v>33</v>
@@ -26736,16 +26755,16 @@
         <v>46168.804918981499</v>
       </c>
       <c r="D157" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E157" s="53" t="s">
         <v>29</v>
       </c>
       <c r="F157" s="53" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G157" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H157" s="53" t="s">
         <v>27</v>
@@ -26774,13 +26793,13 @@
         <v>46169.368923611102</v>
       </c>
       <c r="D158" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E158" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="F158" s="53" t="s">
         <v>253</v>
-      </c>
-      <c r="F158" s="53" t="s">
-        <v>252</v>
       </c>
       <c r="G158" s="53" t="s">
         <v>87</v>
@@ -26812,13 +26831,13 @@
         <v>46169.369375000002</v>
       </c>
       <c r="D159" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E159" s="53" t="s">
         <v>80</v>
       </c>
       <c r="F159" s="53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G159" s="53" t="s">
         <v>113</v>
@@ -26850,7 +26869,7 @@
         <v>46169.369444444397</v>
       </c>
       <c r="D160" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E160" s="53" t="s">
         <v>37</v>
@@ -26888,10 +26907,10 @@
         <v>46169.371342592603</v>
       </c>
       <c r="D161" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E161" s="53" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F161" s="53" t="s">
         <v>86</v>
@@ -26926,13 +26945,13 @@
         <v>46169.3975347222</v>
       </c>
       <c r="D162" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E162" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F162" s="53" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G162" s="53" t="s">
         <v>113</v>
@@ -26964,13 +26983,13 @@
         <v>46169.402523148201</v>
       </c>
       <c r="D163" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E163" s="53" t="s">
         <v>44</v>
       </c>
       <c r="F163" s="53" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G163" s="53" t="s">
         <v>113</v>
@@ -27002,13 +27021,13 @@
         <v>46169.409618055601</v>
       </c>
       <c r="D164" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E164" s="53" t="s">
         <v>29</v>
       </c>
       <c r="F164" s="53" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G164" s="53" t="s">
         <v>53</v>
@@ -27040,13 +27059,13 @@
         <v>46169.410289351901</v>
       </c>
       <c r="D165" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E165" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="F165" s="53" t="s">
         <v>259</v>
-      </c>
-      <c r="F165" s="53" t="s">
-        <v>258</v>
       </c>
       <c r="G165" s="53" t="s">
         <v>53</v>
@@ -27078,13 +27097,13 @@
         <v>46169.499108796299</v>
       </c>
       <c r="D166" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E166" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F166" s="53" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G166" s="53" t="s">
         <v>53</v>
@@ -27116,16 +27135,16 @@
         <v>46169.5080787037</v>
       </c>
       <c r="D167" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E167" s="53" t="s">
         <v>39</v>
       </c>
       <c r="F167" s="53" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G167" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H167" s="53" t="s">
         <v>27</v>
@@ -27154,13 +27173,13 @@
         <v>46169.574502314797</v>
       </c>
       <c r="D168" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E168" s="53" t="s">
         <v>63</v>
       </c>
       <c r="F168" s="53" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G168" s="53" t="s">
         <v>113</v>
@@ -27192,13 +27211,13 @@
         <v>46169.6722800926</v>
       </c>
       <c r="D169" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E169" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="F169" s="53" t="s">
         <v>264</v>
-      </c>
-      <c r="F169" s="53" t="s">
-        <v>263</v>
       </c>
       <c r="G169" s="53" t="s">
         <v>26</v>
@@ -27230,13 +27249,13 @@
         <v>46169.674780092602</v>
       </c>
       <c r="D170" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E170" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="F170" s="53" t="s">
         <v>266</v>
-      </c>
-      <c r="F170" s="53" t="s">
-        <v>265</v>
       </c>
       <c r="G170" s="53" t="s">
         <v>26</v>
@@ -27268,13 +27287,13 @@
         <v>46169.682210648098</v>
       </c>
       <c r="D171" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E171" s="53" t="s">
         <v>57</v>
       </c>
       <c r="F171" s="53" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G171" s="53" t="s">
         <v>26</v>
@@ -27306,16 +27325,16 @@
         <v>46169.924351851798</v>
       </c>
       <c r="D172" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E172" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="F172" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="F172" s="53" t="s">
-        <v>268</v>
-      </c>
       <c r="G172" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H172" s="53" t="s">
         <v>27</v>
@@ -27344,13 +27363,13 @@
         <v>46169.931226851899</v>
       </c>
       <c r="D173" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E173" s="53" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F173" s="53" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G173" s="53" t="s">
         <v>53</v>
@@ -27382,13 +27401,13 @@
         <v>46169.945590277799</v>
       </c>
       <c r="D174" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E174" s="53" t="s">
         <v>107</v>
       </c>
       <c r="F174" s="53" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G174" s="53" t="s">
         <v>87</v>
@@ -27420,13 +27439,13 @@
         <v>46170.293969907398</v>
       </c>
       <c r="D175" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E175" s="53" t="s">
         <v>107</v>
       </c>
       <c r="F175" s="53" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G175" s="53" t="s">
         <v>26</v>
@@ -27458,13 +27477,13 @@
         <v>46170.312013888899</v>
       </c>
       <c r="D176" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E176" s="53" t="s">
+        <v>275</v>
+      </c>
+      <c r="F176" s="53" t="s">
         <v>274</v>
-      </c>
-      <c r="F176" s="53" t="s">
-        <v>273</v>
       </c>
       <c r="G176" s="53" t="s">
         <v>87</v>
@@ -27496,13 +27515,13 @@
         <v>46170.318321759303</v>
       </c>
       <c r="D177" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E177" s="53" t="s">
         <v>65</v>
       </c>
       <c r="F177" s="53" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G177" s="53" t="s">
         <v>26</v>
@@ -27534,13 +27553,13 @@
         <v>46170.320960648103</v>
       </c>
       <c r="D178" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E178" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F178" s="53" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G178" s="53" t="s">
         <v>26</v>
@@ -27572,13 +27591,13 @@
         <v>46170.3214814815</v>
       </c>
       <c r="D179" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E179" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="F179" s="53" t="s">
         <v>277</v>
-      </c>
-      <c r="F179" s="53" t="s">
-        <v>276</v>
       </c>
       <c r="G179" s="53" t="s">
         <v>26</v>
@@ -27610,10 +27629,10 @@
         <v>46170.334490740701</v>
       </c>
       <c r="D180" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E180" s="53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F180" s="53" t="s">
         <v>91</v>
@@ -27648,16 +27667,16 @@
         <v>46170.343738425901</v>
       </c>
       <c r="D181" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E181" s="53" t="s">
         <v>46</v>
       </c>
       <c r="F181" s="53" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G181" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H181" s="53" t="s">
         <v>27</v>
@@ -27686,16 +27705,16 @@
         <v>46170.344351851803</v>
       </c>
       <c r="D182" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E182" s="53" t="s">
+        <v>282</v>
+      </c>
+      <c r="F182" s="53" t="s">
         <v>281</v>
       </c>
-      <c r="F182" s="53" t="s">
-        <v>280</v>
-      </c>
       <c r="G182" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H182" s="53" t="s">
         <v>33</v>
@@ -27724,16 +27743,16 @@
         <v>46170.350277777798</v>
       </c>
       <c r="D183" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E183" s="53" t="s">
         <v>35</v>
       </c>
       <c r="F183" s="53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G183" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H183" s="53" t="s">
         <v>27</v>
@@ -27762,16 +27781,16 @@
         <v>46170.362974536998</v>
       </c>
       <c r="D184" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E184" s="53" t="s">
         <v>52</v>
       </c>
       <c r="F184" s="53" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G184" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H184" s="53" t="s">
         <v>27</v>
@@ -27800,10 +27819,10 @@
         <v>46170.3669212963</v>
       </c>
       <c r="D185" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E185" s="53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F185" s="53" t="s">
         <v>112</v>
@@ -27838,13 +27857,13 @@
         <v>46170.367071759298</v>
       </c>
       <c r="D186" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E186" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F186" s="53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G186" s="53" t="s">
         <v>26</v>
@@ -27876,13 +27895,13 @@
         <v>46170.3670949074</v>
       </c>
       <c r="D187" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E187" s="53" t="s">
+        <v>288</v>
+      </c>
+      <c r="F187" s="53" t="s">
         <v>287</v>
-      </c>
-      <c r="F187" s="53" t="s">
-        <v>286</v>
       </c>
       <c r="G187" s="53" t="s">
         <v>26</v>
@@ -27914,13 +27933,13 @@
         <v>46170.367152777799</v>
       </c>
       <c r="D188" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E188" s="53" t="s">
         <v>35</v>
       </c>
       <c r="F188" s="53" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G188" s="53" t="s">
         <v>26</v>
@@ -27952,13 +27971,13 @@
         <v>46170.367199074099</v>
       </c>
       <c r="D189" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E189" s="53" t="s">
         <v>46</v>
       </c>
       <c r="F189" s="53" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G189" s="53" t="s">
         <v>26</v>
@@ -27990,13 +28009,13 @@
         <v>46170.3676388889</v>
       </c>
       <c r="D190" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E190" s="53" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F190" s="53" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G190" s="53" t="s">
         <v>26</v>
@@ -28028,13 +28047,13 @@
         <v>46170.3727546296</v>
       </c>
       <c r="D191" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E191" s="53" t="s">
         <v>52</v>
       </c>
       <c r="F191" s="53" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G191" s="53" t="s">
         <v>53</v>
@@ -28066,16 +28085,16 @@
         <v>46170.3760763889</v>
       </c>
       <c r="D192" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E192" s="53" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F192" s="53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G192" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H192" s="53" t="s">
         <v>27</v>
@@ -28104,13 +28123,13 @@
         <v>46170.382662037002</v>
       </c>
       <c r="D193" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E193" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="F193" s="53" t="s">
         <v>294</v>
-      </c>
-      <c r="F193" s="53" t="s">
-        <v>293</v>
       </c>
       <c r="G193" s="53" t="s">
         <v>26</v>
@@ -28142,13 +28161,13 @@
         <v>46170.410659722198</v>
       </c>
       <c r="D194" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E194" s="53" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F194" s="53" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G194" s="53" t="s">
         <v>26</v>
@@ -28180,16 +28199,16 @@
         <v>46170.426134259302</v>
       </c>
       <c r="D195" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E195" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F195" s="53" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G195" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H195" s="53" t="s">
         <v>27</v>
@@ -28218,16 +28237,16 @@
         <v>46170.4313078704</v>
       </c>
       <c r="D196" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E196" s="53" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F196" s="53" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G196" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H196" s="53" t="s">
         <v>27</v>
@@ -28256,13 +28275,13 @@
         <v>46170.440532407403</v>
       </c>
       <c r="D197" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E197" s="53" t="s">
         <v>67</v>
       </c>
       <c r="F197" s="53" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G197" s="53" t="s">
         <v>26</v>
@@ -28294,13 +28313,13 @@
         <v>46170.442349536999</v>
       </c>
       <c r="D198" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E198" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="F198" s="53" t="s">
         <v>301</v>
-      </c>
-      <c r="F198" s="53" t="s">
-        <v>300</v>
       </c>
       <c r="G198" s="53" t="s">
         <v>26</v>
@@ -28332,16 +28351,16 @@
         <v>46170.463715277801</v>
       </c>
       <c r="D199" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E199" s="53" t="s">
+        <v>304</v>
+      </c>
+      <c r="F199" s="53" t="s">
         <v>303</v>
       </c>
-      <c r="F199" s="53" t="s">
-        <v>302</v>
-      </c>
       <c r="G199" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H199" s="53" t="s">
         <v>27</v>
@@ -28370,7 +28389,7 @@
         <v>46170.494340277801</v>
       </c>
       <c r="D200" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E200" s="53" t="s">
         <v>78</v>
@@ -28379,7 +28398,7 @@
         <v>56</v>
       </c>
       <c r="G200" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H200" s="53" t="s">
         <v>27</v>
@@ -28408,13 +28427,13 @@
         <v>46170.540069444403</v>
       </c>
       <c r="D201" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E201" s="53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F201" s="53" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G201" s="53" t="s">
         <v>32</v>
@@ -28446,13 +28465,13 @@
         <v>46170.540439814802</v>
       </c>
       <c r="D202" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E202" s="53" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F202" s="53" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G202" s="53" t="s">
         <v>32</v>
@@ -28484,13 +28503,13 @@
         <v>46170.5406365741</v>
       </c>
       <c r="D203" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E203" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="F203" s="53" t="s">
         <v>307</v>
-      </c>
-      <c r="F203" s="53" t="s">
-        <v>306</v>
       </c>
       <c r="G203" s="53" t="s">
         <v>32</v>
@@ -28522,13 +28541,13 @@
         <v>46170.541828703703</v>
       </c>
       <c r="D204" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E204" s="53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F204" s="53" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G204" s="53" t="s">
         <v>32</v>
@@ -28560,13 +28579,13 @@
         <v>46170.555706018502</v>
       </c>
       <c r="D205" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E205" s="53" t="s">
         <v>122</v>
       </c>
       <c r="F205" s="53" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G205" s="53" t="s">
         <v>32</v>
@@ -28598,13 +28617,13 @@
         <v>46170.5613310185</v>
       </c>
       <c r="D206" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E206" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F206" s="53" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G206" s="53" t="s">
         <v>32</v>
@@ -28636,13 +28655,13 @@
         <v>46170.6018287037</v>
       </c>
       <c r="D207" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E207" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F207" s="53" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G207" s="53" t="s">
         <v>87</v>
@@ -28674,13 +28693,13 @@
         <v>46170.6551736111</v>
       </c>
       <c r="D208" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E208" s="53" t="s">
+        <v>314</v>
+      </c>
+      <c r="F208" s="53" t="s">
         <v>313</v>
-      </c>
-      <c r="F208" s="53" t="s">
-        <v>312</v>
       </c>
       <c r="G208" s="53" t="s">
         <v>32</v>
@@ -28712,13 +28731,13 @@
         <v>46170.798148148097</v>
       </c>
       <c r="D209" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E209" s="53" t="s">
         <v>35</v>
       </c>
       <c r="F209" s="53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G209" s="53" t="s">
         <v>113</v>
@@ -28750,13 +28769,13 @@
         <v>46171.3684027778</v>
       </c>
       <c r="D210" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E210" s="53" t="s">
+        <v>317</v>
+      </c>
+      <c r="F210" s="53" t="s">
         <v>316</v>
-      </c>
-      <c r="F210" s="53" t="s">
-        <v>315</v>
       </c>
       <c r="G210" s="53" t="s">
         <v>113</v>
@@ -28788,16 +28807,16 @@
         <v>46171.409490740698</v>
       </c>
       <c r="D211" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E211" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F211" s="53" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G211" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H211" s="53" t="s">
         <v>27</v>
@@ -28826,16 +28845,16 @@
         <v>46171.410208333298</v>
       </c>
       <c r="D212" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E212" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F212" s="53" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G212" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H212" s="53" t="s">
         <v>27</v>
@@ -28864,16 +28883,16 @@
         <v>46171.411041666703</v>
       </c>
       <c r="D213" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E213" s="53" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F213" s="53" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G213" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H213" s="53" t="s">
         <v>27</v>
@@ -28902,13 +28921,13 @@
         <v>46171.423634259299</v>
       </c>
       <c r="D214" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E214" s="53" t="s">
         <v>57</v>
       </c>
       <c r="F214" s="53" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G214" s="53" t="s">
         <v>26</v>
@@ -28940,13 +28959,13 @@
         <v>46171.646597222199</v>
       </c>
       <c r="D215" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E215" s="53" t="s">
         <v>31</v>
       </c>
       <c r="F215" s="53" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G215" s="53" t="s">
         <v>32</v>
@@ -28978,13 +28997,13 @@
         <v>46171.646608796298</v>
       </c>
       <c r="D216" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E216" s="53" t="s">
         <v>80</v>
       </c>
       <c r="F216" s="53" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G216" s="53" t="s">
         <v>32</v>
@@ -29016,16 +29035,16 @@
         <v>46171.668287036999</v>
       </c>
       <c r="D217" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E217" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F217" s="53" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G217" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H217" s="53" t="s">
         <v>27</v>
@@ -29054,16 +29073,16 @@
         <v>46171.704421296301</v>
       </c>
       <c r="D218" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E218" s="53" t="s">
         <v>52</v>
       </c>
       <c r="F218" s="53" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G218" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H218" s="53" t="s">
         <v>27</v>
@@ -29092,13 +29111,13 @@
         <v>46171.726331018501</v>
       </c>
       <c r="D219" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E219" s="53" t="s">
+        <v>326</v>
+      </c>
+      <c r="F219" s="53" t="s">
         <v>325</v>
-      </c>
-      <c r="F219" s="53" t="s">
-        <v>324</v>
       </c>
       <c r="G219" s="53" t="s">
         <v>87</v>
@@ -29130,13 +29149,13 @@
         <v>46171.7492824074</v>
       </c>
       <c r="D220" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E220" s="53" t="s">
         <v>153</v>
       </c>
       <c r="F220" s="53" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G220" s="53" t="s">
         <v>32</v>
@@ -29168,16 +29187,16 @@
         <v>46171.882743055598</v>
       </c>
       <c r="D221" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E221" s="53" t="s">
         <v>100</v>
       </c>
       <c r="F221" s="53" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G221" s="53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H221" s="53" t="s">
         <v>27</v>
@@ -29206,13 +29225,13 @@
         <v>46172.437511574099</v>
       </c>
       <c r="D222" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E222" s="53" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F222" s="53" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G222" s="53" t="s">
         <v>87</v>
@@ -29244,16 +29263,16 @@
         <v>46172.486087963</v>
       </c>
       <c r="D223" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E223" s="53" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F223" s="53" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G223" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H223" s="53" t="s">
         <v>27</v>
@@ -29282,13 +29301,13 @@
         <v>46172.724467592598</v>
       </c>
       <c r="D224" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E224" s="53" t="s">
+        <v>332</v>
+      </c>
+      <c r="F224" s="53" t="s">
         <v>331</v>
-      </c>
-      <c r="F224" s="53" t="s">
-        <v>330</v>
       </c>
       <c r="G224" s="53" t="s">
         <v>87</v>
@@ -29320,13 +29339,13 @@
         <v>46174.4089930556</v>
       </c>
       <c r="D225" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E225" s="53" t="s">
         <v>57</v>
       </c>
       <c r="F225" s="53" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G225" s="53" t="s">
         <v>26</v>
@@ -29358,13 +29377,13 @@
         <v>46174.409849536998</v>
       </c>
       <c r="D226" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E226" s="53" t="s">
         <v>59</v>
       </c>
       <c r="F226" s="53" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G226" s="53" t="s">
         <v>26</v>
@@ -29396,13 +29415,13 @@
         <v>46174.452615740702</v>
       </c>
       <c r="D227" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E227" s="53" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F227" s="53" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G227" s="53" t="s">
         <v>26</v>
@@ -29434,13 +29453,13 @@
         <v>46174.645057870403</v>
       </c>
       <c r="D228" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E228" s="53" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F228" s="53" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G228" s="53" t="s">
         <v>26</v>
@@ -29472,16 +29491,16 @@
         <v>46174.820590277799</v>
       </c>
       <c r="D229" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E229" s="53" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F229" s="53" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G229" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H229" s="53" t="s">
         <v>27</v>
@@ -29510,16 +29529,16 @@
         <v>46174.909942129598</v>
       </c>
       <c r="D230" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E230" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F230" s="53" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G230" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H230" s="53" t="s">
         <v>27</v>
@@ -29548,16 +29567,16 @@
         <v>46174.910532407397</v>
       </c>
       <c r="D231" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E231" s="53" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F231" s="53" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G231" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H231" s="53" t="s">
         <v>27</v>
@@ -29586,7 +29605,7 @@
         <v>46175.453402777799</v>
       </c>
       <c r="D232" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E232" s="53" t="s">
         <v>73</v>
@@ -29624,13 +29643,13 @@
         <v>46175.4539814815</v>
       </c>
       <c r="D233" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E233" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F233" s="53" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G233" s="53" t="s">
         <v>26</v>
@@ -29662,13 +29681,13 @@
         <v>46175.876828703702</v>
       </c>
       <c r="D234" s="54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E234" s="53" t="s">
         <v>153</v>
       </c>
       <c r="F234" s="53" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G234" s="53" t="s">
         <v>26</v>
@@ -30170,7 +30189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F683D51-3249-402D-BC5B-49663797B112}">
   <dimension ref="A5:AO18"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -30197,53 +30216,53 @@
   <sheetData>
     <row r="5" spans="1:41">
       <c r="AC5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:41">
       <c r="AC6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AD6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AE6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AF6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG6" t="s">
         <v>23</v>
       </c>
       <c r="AN6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B7" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
@@ -30258,7 +30277,7 @@
       </c>
       <c r="AD7" s="91">
         <f>Wydatki!F3</f>
-        <v>101790</v>
+        <v>101250</v>
       </c>
       <c r="AE7" s="91">
         <f>Wydatki!G3</f>
@@ -30266,7 +30285,7 @@
       </c>
       <c r="AF7" s="91">
         <f>Wydatki!H3</f>
-        <v>99790</v>
+        <v>99250</v>
       </c>
       <c r="AG7" t="str">
         <f>Wydatki!I3</f>
@@ -30278,7 +30297,7 @@
       </c>
       <c r="AO7" s="91">
         <f>Podsumowanie!B27</f>
-        <v>696.48046875</v>
+        <v>699.31640625</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -30318,19 +30337,19 @@
         <v>2</v>
       </c>
       <c r="Q8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="S8" t="s">
         <v>21</v>
       </c>
       <c r="X8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Y8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AC8" t="str">
         <f>Wydatki!A4</f>
@@ -30358,7 +30377,7 @@
       </c>
       <c r="AO8" s="91">
         <f>Podsumowanie!B28</f>
-        <v>506.53125</v>
+        <v>508.59375</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -30444,7 +30463,7 @@
       </c>
       <c r="AO9" s="91">
         <f>Podsumowanie!B29</f>
-        <v>738.69140625</v>
+        <v>741.69921875</v>
       </c>
     </row>
     <row r="10" spans="1:41">
@@ -30458,11 +30477,11 @@
       </c>
       <c r="J10">
         <f>Podsumowanie!C4</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K10" s="91">
         <f>Podsumowanie!J4</f>
-        <v>20990</v>
+        <v>20450</v>
       </c>
       <c r="L10" s="91">
         <f>Podsumowanie!K4</f>
@@ -30470,7 +30489,7 @@
       </c>
       <c r="M10" s="91">
         <f>Podsumowanie!L4</f>
-        <v>-19190</v>
+        <v>-18650</v>
       </c>
       <c r="P10" t="str">
         <f>'Do wiadomości rodziców'!C34</f>
@@ -30494,7 +30513,7 @@
       </c>
       <c r="Y10">
         <f>'Do wiadomości rodziców'!D7</f>
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AC10" t="str">
         <f>Wydatki!A6</f>
@@ -30522,7 +30541,7 @@
       </c>
       <c r="AO10" s="91">
         <f>Podsumowanie!B30</f>
-        <v>738.69140625</v>
+        <v>741.69921875</v>
       </c>
     </row>
     <row r="11" spans="1:41">
@@ -30556,7 +30575,7 @@
       </c>
       <c r="Q11" s="91">
         <f>'Do wiadomości rodziców'!D35</f>
-        <v>20990</v>
+        <v>20450</v>
       </c>
       <c r="R11" s="91">
         <f>'Do wiadomości rodziców'!E35</f>
@@ -30564,7 +30583,7 @@
       </c>
       <c r="S11" s="91">
         <f>'Do wiadomości rodziców'!F35</f>
-        <v>-19190</v>
+        <v>-18650</v>
       </c>
       <c r="X11" t="str">
         <f>'Do wiadomości rodziców'!C9</f>
@@ -30600,7 +30619,7 @@
       </c>
       <c r="AO11" s="91">
         <f>Podsumowanie!B31</f>
-        <v>738.69140625</v>
+        <v>741.69921875</v>
       </c>
     </row>
     <row r="12" spans="1:41">
@@ -30670,7 +30689,7 @@
       </c>
       <c r="AO12" s="91">
         <f>Podsumowanie!B32</f>
-        <v>717.5859375</v>
+        <v>720.5078125</v>
       </c>
     </row>
     <row r="13" spans="1:41">
@@ -30740,7 +30759,7 @@
       </c>
       <c r="AO13" s="91">
         <f>Podsumowanie!B33</f>
-        <v>612.05859375</v>
+        <v>614.55078125</v>
       </c>
     </row>
     <row r="14" spans="1:41">
@@ -30790,7 +30809,7 @@
       </c>
       <c r="AD14" s="91">
         <f>Wydatki!F10</f>
-        <v>3357.7500000000005</v>
+        <v>3341.2500000000005</v>
       </c>
       <c r="AE14" s="91">
         <f>Wydatki!G10</f>
@@ -30798,7 +30817,7 @@
       </c>
       <c r="AF14" s="91">
         <f>Wydatki!H10</f>
-        <v>3357.7500000000005</v>
+        <v>3341.2500000000005</v>
       </c>
       <c r="AG14">
         <f>Wydatki!I10</f>
@@ -30850,7 +30869,7 @@
       </c>
       <c r="Q16" s="91">
         <f>'Do wiadomości rodziców'!D40</f>
-        <v>137790</v>
+        <v>137250</v>
       </c>
       <c r="R16" s="91">
         <f>'Do wiadomości rodziców'!E40</f>
@@ -30858,7 +30877,7 @@
       </c>
       <c r="S16" s="91">
         <f>'Do wiadomości rodziców'!F40</f>
-        <v>-116490</v>
+        <v>-115950</v>
       </c>
       <c r="AC16" t="str">
         <f>Wydatki!A12</f>
@@ -30906,7 +30925,7 @@
     <row r="18" spans="29:33">
       <c r="AD18" s="91">
         <f>Wydatki!F14</f>
-        <v>133737.75</v>
+        <v>133181.25</v>
       </c>
       <c r="AE18" s="91">
         <f>Wydatki!G14</f>
@@ -30914,7 +30933,7 @@
       </c>
       <c r="AF18" s="91">
         <f>Wydatki!H14</f>
-        <v>129057.75</v>
+        <v>128501.25</v>
       </c>
     </row>
   </sheetData>

--- a/Studniówka 2027_I LO.xlsx
+++ b/Studniówka 2027_I LO.xlsx
@@ -3,23 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46E1500D-7D9F-468D-A177-ECB72B4B9896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18B45ACF-D0EB-411E-ADD6-A742540B2905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista uczniów_składki" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId2"/>
-    <sheet name="Wydatki" sheetId="2" r:id="rId3"/>
-    <sheet name="Podsumowanie" sheetId="3" r:id="rId4"/>
-    <sheet name="Do wiadomości rodziców" sheetId="6" r:id="rId5"/>
-    <sheet name="Zadania" sheetId="8" r:id="rId6"/>
-    <sheet name="Notes" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet name="Ankieta#1_13.04.26" sheetId="5" r:id="rId8"/>
-    <sheet name="Dashboard" sheetId="9" r:id="rId9"/>
+    <sheet name="Wydatki" sheetId="2" r:id="rId2"/>
+    <sheet name="Podsumowanie" sheetId="3" r:id="rId3"/>
+    <sheet name="Do wiadomości rodziców" sheetId="6" r:id="rId4"/>
+    <sheet name="Zadania" sheetId="8" r:id="rId5"/>
+    <sheet name="Notes" sheetId="7" state="hidden" r:id="rId6"/>
+    <sheet name="Ankieta#1_13.04.26" sheetId="5" r:id="rId7"/>
+    <sheet name="Dashboard" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ankieta#1_13.04.26'!$K$1:$M$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ankieta#1_13.04.26'!$K$1:$M$168</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista uczniów_składki'!$Z$2:$AA$2</definedName>
     <definedName name="Fragmentator_Status">#N/A</definedName>
     <definedName name="Slicer_Klasa">#N/A</definedName>
@@ -31,8 +30,8 @@
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
       <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicerCache r:id="rId9"/>
         <x14:slicerCache r:id="rId10"/>
-        <x14:slicerCache r:id="rId11"/>
       </x15:slicerCaches>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -18852,15 +18851,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB506CE-4D21-45F1-8FE8-8B46E7F378F7}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{659C87BF-BB22-4652-A1F0-1E2B8A6DA034}">
   <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -19263,7 +19253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4C4521-749B-409C-BE5E-248315EEF2F8}">
   <dimension ref="A1:V34"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19947,7 +19937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E235FE4-7C05-4EE5-B6BD-B7E167384F75}">
   <dimension ref="A4:F51"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -20549,7 +20539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FAEACC5-CE8D-41C2-A817-9575DF4970B6}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -20777,7 +20767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B90623C-A02B-45BC-8CCB-535472D2A61A}">
   <dimension ref="B3:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20813,7 +20803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8936F2-E3A6-406E-9341-D29A69F6583E}">
   <dimension ref="A1:M277"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -30189,7 +30179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F683D51-3249-402D-BC5B-49663797B112}">
   <dimension ref="A5:AO18"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/Studniówka 2027_I LO.xlsx
+++ b/Studniówka 2027_I LO.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18B45ACF-D0EB-411E-ADD6-A742540B2905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2DC5501-9F2A-455A-BFB6-95BEF46E45EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista uczniów_składki" sheetId="1" r:id="rId1"/>
@@ -1612,10 +1612,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -1884,25 +1884,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1914,11 +1914,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1943,28 +1943,28 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2000,10 +2000,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2015,31 +2015,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2061,7 +2061,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2070,36 +2070,36 @@
     <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2119,21 +2119,21 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2146,7 +2146,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2155,11 +2155,11 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2171,16 +2171,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2194,41 +2194,41 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="96">
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -2384,7 +2384,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="168" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9E1F2"/>
@@ -2408,7 +2408,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="168" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9E1F2"/>
@@ -2491,7 +2491,7 @@
       <font>
         <name val="Aptos"/>
       </font>
-      <numFmt numFmtId="169" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
@@ -2528,7 +2528,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2547,7 +2547,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2566,7 +2566,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2603,7 +2603,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2772,7 +2772,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" relativeIndent="1"/>
     </dxf>
     <dxf>
@@ -2809,7 +2809,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" relativeIndent="1"/>
     </dxf>
     <dxf>
@@ -2828,7 +2828,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2847,7 +2847,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" relativeIndent="1"/>
     </dxf>
     <dxf>
@@ -2866,7 +2866,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2885,7 +2885,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2904,7 +2904,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2923,7 +2923,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" relativeIndent="1"/>
     </dxf>
     <dxf>
@@ -2960,7 +2960,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="center" vertical="center" relativeIndent="1"/>
     </dxf>
     <dxf>
@@ -3126,7 +3126,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
@@ -3145,7 +3145,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3183,7 +3183,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3202,7 +3202,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3221,7 +3221,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3240,7 +3240,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3259,7 +3259,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3278,7 +3278,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3297,7 +3297,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3316,7 +3316,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3335,7 +3335,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3354,7 +3354,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3373,7 +3373,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3392,7 +3392,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3411,7 +3411,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3430,7 +3430,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3449,7 +3449,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3468,7 +3468,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3562,7 +3562,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3581,7 +3581,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3618,7 +3618,7 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3685,8 +3685,8 @@
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main">
       <mc:Choice Requires="a15">
@@ -3753,14 +3753,14 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main">
       <mc:Choice Requires="a15">
@@ -3883,7 +3883,11 @@
   <autoFilter ref="A2:X235" xr:uid="{CFCB90EF-AA27-4917-A5A7-03A9090EB806}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1">
+      <filters>
+        <filter val="3D"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="3" hiddenButton="1"/>
     <filterColumn colId="4" hiddenButton="1"/>
     <filterColumn colId="5" hiddenButton="1"/>
@@ -4544,7 +4548,7 @@
     <row r="1" spans="1:27">
       <c r="G1" s="4">
         <f>SUBTOTAL(9,G3:G614)</f>
-        <v>9600</v>
+        <v>1750</v>
       </c>
       <c r="H1" s="4">
         <f t="shared" ref="H1:S1" si="0">SUBTOTAL(9,H3:H614)</f>
@@ -4560,15 +4564,15 @@
       </c>
       <c r="K1" s="4">
         <f t="shared" si="0"/>
-        <v>6500</v>
+        <v>3100</v>
       </c>
       <c r="L1" s="4">
         <f t="shared" si="0"/>
-        <v>4600</v>
+        <v>2600</v>
       </c>
       <c r="M1" s="4">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N1" s="4">
         <f t="shared" si="0"/>
@@ -4580,7 +4584,7 @@
       </c>
       <c r="P1" s="4">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q1" s="4">
         <f t="shared" si="0"/>
@@ -4596,15 +4600,15 @@
       </c>
       <c r="T1" s="4">
         <f>SUBTOTAL(9,T3:T614)</f>
-        <v>21300</v>
+        <v>7750</v>
       </c>
       <c r="U1" s="4">
         <f>SUBTOTAL(9,U3:U614)</f>
-        <v>137250</v>
+        <v>21530</v>
       </c>
       <c r="V1" s="4">
         <f>SUBTOTAL(9,V3:V614)</f>
-        <v>-115950</v>
+        <v>-13780</v>
       </c>
     </row>
     <row r="2" spans="1:27" s="3" customFormat="1" ht="36.75" customHeight="1">
@@ -4681,7 +4685,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="17.25" customHeight="1">
+    <row r="3" spans="1:27" ht="17.25" hidden="1" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
@@ -4726,7 +4730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" hidden="1">
       <c r="A4" s="4" t="s">
         <v>28</v>
       </c>
@@ -4771,7 +4775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" hidden="1">
       <c r="A5" s="4" t="s">
         <v>30</v>
       </c>
@@ -4816,7 +4820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" hidden="1">
       <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
@@ -4861,7 +4865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" hidden="1">
       <c r="A7" s="4" t="s">
         <v>36</v>
       </c>
@@ -4906,7 +4910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" hidden="1">
       <c r="A8" s="4" t="s">
         <v>38</v>
       </c>
@@ -4951,7 +4955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" hidden="1">
       <c r="A9" s="4" t="s">
         <v>40</v>
       </c>
@@ -4996,7 +5000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" hidden="1">
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
@@ -5041,7 +5045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" hidden="1">
       <c r="A11" s="4" t="s">
         <v>43</v>
       </c>
@@ -5086,7 +5090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" hidden="1">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
@@ -5131,7 +5135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" hidden="1">
       <c r="A13" s="4" t="s">
         <v>47</v>
       </c>
@@ -5176,7 +5180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" hidden="1">
       <c r="A14" s="4" t="s">
         <v>49</v>
       </c>
@@ -5221,7 +5225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" hidden="1">
       <c r="A15" s="4" t="s">
         <v>51</v>
       </c>
@@ -5266,7 +5270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" hidden="1">
       <c r="A16" s="4" t="s">
         <v>54</v>
       </c>
@@ -5311,7 +5315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" hidden="1">
       <c r="A17" s="4" t="s">
         <v>56</v>
       </c>
@@ -5356,7 +5360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" hidden="1">
       <c r="A18" s="4" t="s">
         <v>58</v>
       </c>
@@ -5401,7 +5405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" hidden="1">
       <c r="A19" s="4" t="s">
         <v>60</v>
       </c>
@@ -5446,7 +5450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" hidden="1">
       <c r="A20" s="4" t="s">
         <v>62</v>
       </c>
@@ -5491,7 +5495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" hidden="1">
       <c r="A21" s="4" t="s">
         <v>64</v>
       </c>
@@ -5536,7 +5540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" hidden="1">
       <c r="A22" s="4" t="s">
         <v>66</v>
       </c>
@@ -5581,7 +5585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" hidden="1">
       <c r="A23" s="4" t="s">
         <v>68</v>
       </c>
@@ -5626,7 +5630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" hidden="1">
       <c r="A24" s="4" t="s">
         <v>69</v>
       </c>
@@ -5671,7 +5675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" hidden="1">
       <c r="A25" s="4" t="s">
         <v>71</v>
       </c>
@@ -5716,7 +5720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" hidden="1">
       <c r="A26" s="4" t="s">
         <v>72</v>
       </c>
@@ -5761,7 +5765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" hidden="1">
       <c r="A27" s="4" t="s">
         <v>74</v>
       </c>
@@ -5806,7 +5810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" hidden="1">
       <c r="A28" s="4" t="s">
         <v>75</v>
       </c>
@@ -5851,7 +5855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" hidden="1">
       <c r="A29" s="4" t="s">
         <v>77</v>
       </c>
@@ -5896,7 +5900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" hidden="1">
       <c r="A30" s="4" t="s">
         <v>79</v>
       </c>
@@ -5941,7 +5945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" hidden="1">
       <c r="A31" s="4" t="s">
         <v>81</v>
       </c>
@@ -5986,7 +5990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" hidden="1">
       <c r="A32" s="4" t="s">
         <v>82</v>
       </c>
@@ -6031,7 +6035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" hidden="1">
       <c r="A33" s="4" t="s">
         <v>84</v>
       </c>
@@ -6076,7 +6080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" hidden="1">
       <c r="A34" s="4" t="s">
         <v>86</v>
       </c>
@@ -6121,7 +6125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" hidden="1">
       <c r="A35" s="4" t="s">
         <v>88</v>
       </c>
@@ -6166,7 +6170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" hidden="1">
       <c r="A36" s="4" t="s">
         <v>90</v>
       </c>
@@ -6211,7 +6215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" hidden="1">
       <c r="A37" s="4" t="s">
         <v>91</v>
       </c>
@@ -6256,7 +6260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:27">
+    <row r="38" spans="1:27" hidden="1">
       <c r="A38" s="4" t="s">
         <v>93</v>
       </c>
@@ -6301,7 +6305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" hidden="1">
       <c r="A39" s="4" t="s">
         <v>94</v>
       </c>
@@ -6346,7 +6350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" hidden="1">
       <c r="A40" s="4" t="s">
         <v>96</v>
       </c>
@@ -6391,7 +6395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" hidden="1">
       <c r="A41" s="4" t="s">
         <v>97</v>
       </c>
@@ -6436,7 +6440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" hidden="1">
       <c r="A42" s="4" t="s">
         <v>99</v>
       </c>
@@ -6481,7 +6485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="1:27" hidden="1">
       <c r="A43" s="4" t="s">
         <v>101</v>
       </c>
@@ -6526,7 +6530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" hidden="1">
       <c r="A44" s="4" t="s">
         <v>102</v>
       </c>
@@ -6571,7 +6575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:27">
+    <row r="45" spans="1:27" hidden="1">
       <c r="A45" s="4" t="s">
         <v>103</v>
       </c>
@@ -6619,7 +6623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:27" hidden="1">
       <c r="A46" s="4" t="s">
         <v>102</v>
       </c>
@@ -6664,7 +6668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:27" hidden="1">
       <c r="A47" s="4" t="s">
         <v>106</v>
       </c>
@@ -6709,7 +6713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:27" hidden="1">
       <c r="A48" s="4" t="s">
         <v>108</v>
       </c>
@@ -6754,7 +6758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:27" hidden="1">
       <c r="A49" s="4" t="s">
         <v>110</v>
       </c>
@@ -6799,7 +6803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:27">
+    <row r="50" spans="1:27" hidden="1">
       <c r="A50" s="4" t="s">
         <v>112</v>
       </c>
@@ -6844,7 +6848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:27">
+    <row r="51" spans="1:27" hidden="1">
       <c r="A51" s="4" t="s">
         <v>114</v>
       </c>
@@ -6889,7 +6893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:27">
+    <row r="52" spans="1:27" hidden="1">
       <c r="A52" s="4" t="s">
         <v>116</v>
       </c>
@@ -6934,7 +6938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:27">
+    <row r="53" spans="1:27" hidden="1">
       <c r="A53" s="4" t="s">
         <v>117</v>
       </c>
@@ -6979,7 +6983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:27">
+    <row r="54" spans="1:27" hidden="1">
       <c r="A54" s="4" t="s">
         <v>119</v>
       </c>
@@ -7024,7 +7028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:27" hidden="1">
       <c r="A55" s="4" t="s">
         <v>120</v>
       </c>
@@ -7069,7 +7073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:27">
+    <row r="56" spans="1:27" hidden="1">
       <c r="A56" s="4" t="s">
         <v>121</v>
       </c>
@@ -7114,7 +7118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:27">
+    <row r="57" spans="1:27" hidden="1">
       <c r="A57" s="4" t="s">
         <v>88</v>
       </c>
@@ -7159,7 +7163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:27">
+    <row r="58" spans="1:27" hidden="1">
       <c r="A58" s="4" t="s">
         <v>123</v>
       </c>
@@ -7204,7 +7208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:27">
+    <row r="59" spans="1:27" hidden="1">
       <c r="A59" s="4" t="s">
         <v>125</v>
       </c>
@@ -7249,7 +7253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:27" hidden="1">
       <c r="A60" s="4" t="s">
         <v>126</v>
       </c>
@@ -7294,7 +7298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:27">
+    <row r="61" spans="1:27" hidden="1">
       <c r="A61" s="4" t="s">
         <v>128</v>
       </c>
@@ -7339,7 +7343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:27">
+    <row r="62" spans="1:27" hidden="1">
       <c r="A62" s="4" t="s">
         <v>129</v>
       </c>
@@ -7384,7 +7388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:27">
+    <row r="63" spans="1:27" hidden="1">
       <c r="A63" s="4" t="s">
         <v>131</v>
       </c>
@@ -7431,7 +7435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:27">
+    <row r="64" spans="1:27" hidden="1">
       <c r="A64" s="4" t="s">
         <v>133</v>
       </c>
@@ -7476,7 +7480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:27">
+    <row r="65" spans="1:27" hidden="1">
       <c r="A65" s="4" t="s">
         <v>134</v>
       </c>
@@ -7521,7 +7525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:27">
+    <row r="66" spans="1:27" hidden="1">
       <c r="A66" s="4" t="s">
         <v>136</v>
       </c>
@@ -7566,7 +7570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:27">
+    <row r="67" spans="1:27" hidden="1">
       <c r="A67" s="4" t="s">
         <v>137</v>
       </c>
@@ -7611,7 +7615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:27">
+    <row r="68" spans="1:27" hidden="1">
       <c r="A68" s="4" t="s">
         <v>138</v>
       </c>
@@ -7656,7 +7660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:27">
+    <row r="69" spans="1:27" hidden="1">
       <c r="A69" s="4" t="s">
         <v>140</v>
       </c>
@@ -7701,7 +7705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:27">
+    <row r="70" spans="1:27" hidden="1">
       <c r="A70" s="4" t="s">
         <v>141</v>
       </c>
@@ -7746,7 +7750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:27">
+    <row r="71" spans="1:27" hidden="1">
       <c r="A71" s="4" t="s">
         <v>142</v>
       </c>
@@ -7791,7 +7795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:27">
+    <row r="72" spans="1:27" hidden="1">
       <c r="A72" s="4" t="s">
         <v>143</v>
       </c>
@@ -7836,7 +7840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:27">
+    <row r="73" spans="1:27" hidden="1">
       <c r="A73" s="4" t="s">
         <v>144</v>
       </c>
@@ -7881,7 +7885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:27">
+    <row r="74" spans="1:27" hidden="1">
       <c r="A74" s="4" t="s">
         <v>145</v>
       </c>
@@ -7926,7 +7930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:27">
+    <row r="75" spans="1:27" hidden="1">
       <c r="A75" s="4" t="s">
         <v>147</v>
       </c>
@@ -7971,7 +7975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:27">
+    <row r="76" spans="1:27" hidden="1">
       <c r="A76" s="4" t="s">
         <v>148</v>
       </c>
@@ -8016,7 +8020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:27">
+    <row r="77" spans="1:27" hidden="1">
       <c r="A77" s="4" t="s">
         <v>93</v>
       </c>
@@ -8061,7 +8065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:27">
+    <row r="78" spans="1:27" hidden="1">
       <c r="A78" s="4" t="s">
         <v>149</v>
       </c>
@@ -8106,7 +8110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:27">
+    <row r="79" spans="1:27" hidden="1">
       <c r="A79" s="4" t="s">
         <v>108</v>
       </c>
@@ -8151,7 +8155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:27">
+    <row r="80" spans="1:27" hidden="1">
       <c r="A80" s="4" t="s">
         <v>152</v>
       </c>
@@ -8196,7 +8200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:27">
+    <row r="81" spans="1:27" hidden="1">
       <c r="A81" s="4" t="s">
         <v>154</v>
       </c>
@@ -8244,7 +8248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:27">
+    <row r="82" spans="1:27" hidden="1">
       <c r="A82" s="4" t="s">
         <v>157</v>
       </c>
@@ -8289,7 +8293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:27">
+    <row r="83" spans="1:27" hidden="1">
       <c r="A83" s="4" t="s">
         <v>159</v>
       </c>
@@ -8334,7 +8338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:27">
+    <row r="84" spans="1:27" hidden="1">
       <c r="A84" s="4" t="s">
         <v>160</v>
       </c>
@@ -8379,7 +8383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:27">
+    <row r="85" spans="1:27" hidden="1">
       <c r="A85" s="4" t="s">
         <v>86</v>
       </c>
@@ -8424,7 +8428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:27">
+    <row r="86" spans="1:27" hidden="1">
       <c r="A86" s="4" t="s">
         <v>161</v>
       </c>
@@ -8481,7 +8485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:27">
+    <row r="87" spans="1:27" hidden="1">
       <c r="A87" s="4" t="s">
         <v>164</v>
       </c>
@@ -8526,7 +8530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:27">
+    <row r="88" spans="1:27" hidden="1">
       <c r="A88" s="4" t="s">
         <v>165</v>
       </c>
@@ -8571,7 +8575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:27">
+    <row r="89" spans="1:27" hidden="1">
       <c r="A89" s="4" t="s">
         <v>167</v>
       </c>
@@ -8616,7 +8620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:27">
+    <row r="90" spans="1:27" hidden="1">
       <c r="A90" s="4" t="s">
         <v>168</v>
       </c>
@@ -8661,7 +8665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:27">
+    <row r="91" spans="1:27" hidden="1">
       <c r="A91" s="4" t="s">
         <v>170</v>
       </c>
@@ -8722,6 +8726,9 @@
       <c r="E92" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G92" s="4">
+        <v>50</v>
+      </c>
       <c r="K92" s="4">
         <v>100</v>
       </c>
@@ -8730,7 +8737,7 @@
       </c>
       <c r="T92" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U92" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D92="Nie",E92="Nie"),0,IF(AND(D92="Tak",E92="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8738,7 +8745,7 @@
       </c>
       <c r="V92" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W92" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8770,12 +8777,15 @@
       <c r="E93" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G93" s="4">
+        <v>50</v>
+      </c>
       <c r="K93" s="4">
         <v>100</v>
       </c>
       <c r="T93" s="4">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="U93" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D93="Nie",E93="Nie"),0,IF(AND(D93="Tak",E93="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8783,7 +8793,7 @@
       </c>
       <c r="V93" s="4">
         <f t="shared" si="4"/>
-        <v>-600</v>
+        <v>-550</v>
       </c>
       <c r="W93" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8815,12 +8825,15 @@
       <c r="E94" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G94" s="4">
+        <v>50</v>
+      </c>
       <c r="K94" s="4">
         <v>100</v>
       </c>
       <c r="T94" s="4">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="U94" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D94="Nie",E94="Nie"),0,IF(AND(D94="Tak",E94="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8828,7 +8841,7 @@
       </c>
       <c r="V94" s="4">
         <f t="shared" si="4"/>
-        <v>-600</v>
+        <v>-550</v>
       </c>
       <c r="W94" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8860,9 +8873,12 @@
       <c r="E95" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G95" s="4">
+        <v>50</v>
+      </c>
       <c r="T95" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U95" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D95="Nie",E95="Nie"),0,IF(AND(D95="Tak",E95="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8870,7 +8886,7 @@
       </c>
       <c r="V95" s="4">
         <f t="shared" si="4"/>
-        <v>-700</v>
+        <v>-650</v>
       </c>
       <c r="W95" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8902,6 +8918,9 @@
       <c r="E96" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G96" s="4">
+        <v>50</v>
+      </c>
       <c r="K96" s="4">
         <v>100</v>
       </c>
@@ -8910,7 +8929,7 @@
       </c>
       <c r="T96" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U96" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D96="Nie",E96="Nie"),0,IF(AND(D96="Tak",E96="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8918,7 +8937,7 @@
       </c>
       <c r="V96" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W96" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8950,6 +8969,9 @@
       <c r="E97" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G97" s="4">
+        <v>50</v>
+      </c>
       <c r="K97" s="4">
         <v>100</v>
       </c>
@@ -8958,7 +8980,7 @@
       </c>
       <c r="T97" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U97" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D97="Nie",E97="Nie"),0,IF(AND(D97="Tak",E97="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8966,7 +8988,7 @@
       </c>
       <c r="V97" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W97" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8998,6 +9020,9 @@
       <c r="E98" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G98" s="4">
+        <v>50</v>
+      </c>
       <c r="K98" s="4">
         <v>100</v>
       </c>
@@ -9006,7 +9031,7 @@
       </c>
       <c r="T98" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U98" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D98="Nie",E98="Nie"),0,IF(AND(D98="Tak",E98="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9014,7 +9039,7 @@
       </c>
       <c r="V98" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W98" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9046,12 +9071,15 @@
       <c r="E99" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G99" s="4">
+        <v>50</v>
+      </c>
       <c r="K99" s="4">
         <v>100</v>
       </c>
       <c r="T99" s="4">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="U99" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D99="Nie",E99="Nie"),0,IF(AND(D99="Tak",E99="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9059,7 +9087,7 @@
       </c>
       <c r="V99" s="4">
         <f t="shared" si="4"/>
-        <v>-600</v>
+        <v>-550</v>
       </c>
       <c r="W99" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9091,6 +9119,9 @@
       <c r="E100" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G100" s="4">
+        <v>50</v>
+      </c>
       <c r="K100" s="4">
         <v>100</v>
       </c>
@@ -9099,7 +9130,7 @@
       </c>
       <c r="T100" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U100" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D100="Nie",E100="Nie"),0,IF(AND(D100="Tak",E100="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9107,7 +9138,7 @@
       </c>
       <c r="V100" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W100" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9139,6 +9170,9 @@
       <c r="E101" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G101" s="4">
+        <v>50</v>
+      </c>
       <c r="K101" s="4">
         <v>100</v>
       </c>
@@ -9147,7 +9181,7 @@
       </c>
       <c r="T101" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U101" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D101="Nie",E101="Nie"),0,IF(AND(D101="Tak",E101="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9155,7 +9189,7 @@
       </c>
       <c r="V101" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W101" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9187,12 +9221,15 @@
       <c r="E102" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G102" s="4">
+        <v>50</v>
+      </c>
       <c r="K102" s="4">
         <v>100</v>
       </c>
       <c r="T102" s="4">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="U102" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D102="Nie",E102="Nie"),0,IF(AND(D102="Tak",E102="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9200,7 +9237,7 @@
       </c>
       <c r="V102" s="4">
         <f t="shared" si="4"/>
-        <v>-600</v>
+        <v>-550</v>
       </c>
       <c r="W102" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9232,6 +9269,9 @@
       <c r="E103" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G103" s="4">
+        <v>50</v>
+      </c>
       <c r="K103" s="4">
         <v>100</v>
       </c>
@@ -9240,7 +9280,7 @@
       </c>
       <c r="T103" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U103" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D103="Nie",E103="Nie"),0,IF(AND(D103="Tak",E103="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9248,7 +9288,7 @@
       </c>
       <c r="V103" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W103" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9280,6 +9320,9 @@
       <c r="E104" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="G104" s="4">
+        <v>50</v>
+      </c>
       <c r="K104" s="4">
         <v>100</v>
       </c>
@@ -9291,7 +9334,7 @@
       </c>
       <c r="T104" s="4">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="U104" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D104="Nie",E104="Nie"),0,IF(AND(D104="Tak",E104="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9299,7 +9342,7 @@
       </c>
       <c r="V104" s="4">
         <f t="shared" si="4"/>
-        <v>-130</v>
+        <v>-80</v>
       </c>
       <c r="W104" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9331,6 +9374,9 @@
       <c r="E105" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G105" s="4">
+        <v>50</v>
+      </c>
       <c r="K105" s="4">
         <v>100</v>
       </c>
@@ -9339,7 +9385,7 @@
       </c>
       <c r="T105" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U105" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D105="Nie",E105="Nie"),0,IF(AND(D105="Tak",E105="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9347,7 +9393,7 @@
       </c>
       <c r="V105" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W105" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9379,6 +9425,9 @@
       <c r="E106" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="G106" s="4">
+        <v>50</v>
+      </c>
       <c r="K106" s="4">
         <v>100</v>
       </c>
@@ -9387,7 +9436,7 @@
       </c>
       <c r="T106" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U106" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D106="Nie",E106="Nie"),0,IF(AND(D106="Tak",E106="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9395,7 +9444,7 @@
       </c>
       <c r="V106" s="4">
         <f t="shared" si="4"/>
-        <v>-230</v>
+        <v>-180</v>
       </c>
       <c r="W106" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9427,9 +9476,12 @@
       <c r="E107" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G107" s="4">
+        <v>50</v>
+      </c>
       <c r="T107" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U107" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D107="Nie",E107="Nie"),0,IF(AND(D107="Tak",E107="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9437,7 +9489,7 @@
       </c>
       <c r="V107" s="4">
         <f t="shared" si="4"/>
-        <v>-700</v>
+        <v>-650</v>
       </c>
       <c r="W107" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9469,12 +9521,15 @@
       <c r="E108" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G108" s="4">
+        <v>50</v>
+      </c>
       <c r="K108" s="4">
         <v>100</v>
       </c>
       <c r="T108" s="4">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="U108" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D108="Nie",E108="Nie"),0,IF(AND(D108="Tak",E108="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9482,7 +9537,7 @@
       </c>
       <c r="V108" s="4">
         <f t="shared" si="4"/>
-        <v>-600</v>
+        <v>-550</v>
       </c>
       <c r="W108" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9514,6 +9569,9 @@
       <c r="E109" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G109" s="4">
+        <v>50</v>
+      </c>
       <c r="K109" s="4">
         <v>100</v>
       </c>
@@ -9522,7 +9580,7 @@
       </c>
       <c r="T109" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U109" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D109="Nie",E109="Nie"),0,IF(AND(D109="Tak",E109="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9530,7 +9588,7 @@
       </c>
       <c r="V109" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W109" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9562,6 +9620,9 @@
       <c r="E110" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="G110" s="4">
+        <v>50</v>
+      </c>
       <c r="K110" s="4">
         <v>100</v>
       </c>
@@ -9570,7 +9631,7 @@
       </c>
       <c r="T110" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U110" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D110="Nie",E110="Nie"),0,IF(AND(D110="Tak",E110="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9578,7 +9639,7 @@
       </c>
       <c r="V110" s="4">
         <f t="shared" si="4"/>
-        <v>-230</v>
+        <v>-180</v>
       </c>
       <c r="W110" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9594,7 +9655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:27">
+    <row r="111" spans="1:27" hidden="1">
       <c r="A111" s="4" t="s">
         <v>199</v>
       </c>
@@ -9655,6 +9716,9 @@
       <c r="E112" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="G112" s="4">
+        <v>50</v>
+      </c>
       <c r="K112" s="4">
         <v>100</v>
       </c>
@@ -9663,7 +9727,7 @@
       </c>
       <c r="T112" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U112" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D112="Nie",E112="Nie"),0,IF(AND(D112="Tak",E112="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9671,7 +9735,7 @@
       </c>
       <c r="V112" s="4">
         <f t="shared" si="4"/>
-        <v>-230</v>
+        <v>-180</v>
       </c>
       <c r="W112" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9703,6 +9767,9 @@
       <c r="E113" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="G113" s="4">
+        <v>50</v>
+      </c>
       <c r="K113" s="4">
         <v>100</v>
       </c>
@@ -9711,7 +9778,7 @@
       </c>
       <c r="T113" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U113" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D113="Nie",E113="Nie"),0,IF(AND(D113="Tak",E113="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9719,7 +9786,7 @@
       </c>
       <c r="V113" s="4">
         <f t="shared" si="4"/>
-        <v>-230</v>
+        <v>-180</v>
       </c>
       <c r="W113" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9751,6 +9818,9 @@
       <c r="E114" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G114" s="4">
+        <v>50</v>
+      </c>
       <c r="K114" s="4">
         <v>100</v>
       </c>
@@ -9759,7 +9829,7 @@
       </c>
       <c r="T114" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U114" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D114="Nie",E114="Nie"),0,IF(AND(D114="Tak",E114="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -9767,7 +9837,7 @@
       </c>
       <c r="V114" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W114" s="55" t="str">
         <f t="shared" si="5"/>
@@ -9783,7 +9853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:27">
+    <row r="115" spans="1:27" hidden="1">
       <c r="A115" s="4" t="s">
         <v>204</v>
       </c>
@@ -9828,7 +9898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:27">
+    <row r="116" spans="1:27" hidden="1">
       <c r="A116" s="4" t="s">
         <v>206</v>
       </c>
@@ -9873,7 +9943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:27">
+    <row r="117" spans="1:27" hidden="1">
       <c r="A117" s="4" t="s">
         <v>208</v>
       </c>
@@ -9918,7 +9988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:27">
+    <row r="118" spans="1:27" hidden="1">
       <c r="A118" s="4" t="s">
         <v>209</v>
       </c>
@@ -9963,7 +10033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:27">
+    <row r="119" spans="1:27" hidden="1">
       <c r="A119" s="4" t="s">
         <v>211</v>
       </c>
@@ -10008,7 +10078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:27">
+    <row r="120" spans="1:27" hidden="1">
       <c r="A120" s="4" t="s">
         <v>213</v>
       </c>
@@ -10053,7 +10123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:27">
+    <row r="121" spans="1:27" hidden="1">
       <c r="A121" s="4" t="s">
         <v>214</v>
       </c>
@@ -10098,7 +10168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:27">
+    <row r="122" spans="1:27" hidden="1">
       <c r="A122" s="4" t="s">
         <v>215</v>
       </c>
@@ -10143,7 +10213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:27">
+    <row r="123" spans="1:27" hidden="1">
       <c r="A123" s="4" t="s">
         <v>136</v>
       </c>
@@ -10188,7 +10258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:27">
+    <row r="124" spans="1:27" hidden="1">
       <c r="A124" s="4" t="s">
         <v>216</v>
       </c>
@@ -10233,7 +10303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:27">
+    <row r="125" spans="1:27" hidden="1">
       <c r="A125" s="4" t="s">
         <v>217</v>
       </c>
@@ -10278,7 +10348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:27">
+    <row r="126" spans="1:27" hidden="1">
       <c r="A126" s="4" t="s">
         <v>218</v>
       </c>
@@ -10339,6 +10409,9 @@
       <c r="E127" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G127" s="4">
+        <v>50</v>
+      </c>
       <c r="K127" s="4">
         <v>100</v>
       </c>
@@ -10347,7 +10420,7 @@
       </c>
       <c r="T127" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U127" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D127="Nie",E127="Nie"),0,IF(AND(D127="Tak",E127="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -10355,7 +10428,7 @@
       </c>
       <c r="V127" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W127" s="55" t="str">
         <f t="shared" si="5"/>
@@ -10371,7 +10444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
+    <row r="128" spans="1:27" hidden="1">
       <c r="A128" s="4" t="s">
         <v>220</v>
       </c>
@@ -10438,6 +10511,9 @@
       <c r="E129" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G129" s="4">
+        <v>50</v>
+      </c>
       <c r="K129" s="4">
         <v>100</v>
       </c>
@@ -10446,7 +10522,7 @@
       </c>
       <c r="T129" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U129" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D129="Nie",E129="Nie"),0,IF(AND(D129="Tak",E129="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -10454,7 +10530,7 @@
       </c>
       <c r="V129" s="4">
         <f t="shared" si="4"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W129" s="55" t="str">
         <f t="shared" si="5"/>
@@ -10486,6 +10562,9 @@
       <c r="E130" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G130" s="4">
+        <v>50</v>
+      </c>
       <c r="K130" s="4">
         <v>100</v>
       </c>
@@ -10497,7 +10576,7 @@
       </c>
       <c r="T130" s="4">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="U130" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D130="Nie",E130="Nie"),0,IF(AND(D130="Tak",E130="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -10505,7 +10584,7 @@
       </c>
       <c r="V130" s="4">
         <f t="shared" si="4"/>
-        <v>-400</v>
+        <v>-350</v>
       </c>
       <c r="W130" s="55" t="str">
         <f t="shared" si="5"/>
@@ -10537,6 +10616,9 @@
       <c r="E131" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="G131" s="4">
+        <v>50</v>
+      </c>
       <c r="K131" s="4">
         <v>100</v>
       </c>
@@ -10545,7 +10627,7 @@
       </c>
       <c r="T131" s="4">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U131" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D131="Nie",E131="Nie"),0,IF(AND(D131="Tak",E131="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -10553,7 +10635,7 @@
       </c>
       <c r="V131" s="4">
         <f t="shared" ref="V131:V194" si="7">IFERROR(T131-U131,"")</f>
-        <v>-230</v>
+        <v>-180</v>
       </c>
       <c r="W131" s="55" t="str">
         <f t="shared" ref="W131:W194" si="8">IF(OR(A131="",V131=0),"",IF(OR(V131&gt;-0.01,V131=0),"OK","NOK"))</f>
@@ -10569,7 +10651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:27">
+    <row r="132" spans="1:27" hidden="1">
       <c r="A132" s="4" t="s">
         <v>223</v>
       </c>
@@ -10614,7 +10696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:27">
+    <row r="133" spans="1:27" hidden="1">
       <c r="A133" s="4" t="s">
         <v>224</v>
       </c>
@@ -10665,7 +10747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:27">
+    <row r="134" spans="1:27" hidden="1">
       <c r="A134" s="4" t="s">
         <v>225</v>
       </c>
@@ -10713,7 +10795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:27">
+    <row r="135" spans="1:27" hidden="1">
       <c r="A135" s="4" t="s">
         <v>227</v>
       </c>
@@ -10764,7 +10846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:27">
+    <row r="136" spans="1:27" hidden="1">
       <c r="A136" s="4" t="s">
         <v>228</v>
       </c>
@@ -10812,7 +10894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:27">
+    <row r="137" spans="1:27" hidden="1">
       <c r="A137" s="4" t="s">
         <v>159</v>
       </c>
@@ -10860,7 +10942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:27">
+    <row r="138" spans="1:27" hidden="1">
       <c r="A138" s="4" t="s">
         <v>229</v>
       </c>
@@ -10908,7 +10990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:27">
+    <row r="139" spans="1:27" hidden="1">
       <c r="A139" s="4" t="s">
         <v>231</v>
       </c>
@@ -10959,7 +11041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:27">
+    <row r="140" spans="1:27" hidden="1">
       <c r="A140" s="4" t="s">
         <v>232</v>
       </c>
@@ -11010,7 +11092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:27">
+    <row r="141" spans="1:27" hidden="1">
       <c r="A141" s="4" t="s">
         <v>233</v>
       </c>
@@ -11058,7 +11140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:27">
+    <row r="142" spans="1:27" hidden="1">
       <c r="A142" s="4" t="s">
         <v>234</v>
       </c>
@@ -11106,7 +11188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:27">
+    <row r="143" spans="1:27" hidden="1">
       <c r="A143" s="4" t="s">
         <v>235</v>
       </c>
@@ -11157,7 +11239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:27">
+    <row r="144" spans="1:27" hidden="1">
       <c r="A144" s="4" t="s">
         <v>236</v>
       </c>
@@ -11202,7 +11284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:27">
+    <row r="145" spans="1:27" hidden="1">
       <c r="A145" s="4" t="s">
         <v>237</v>
       </c>
@@ -11250,7 +11332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:27">
+    <row r="146" spans="1:27" hidden="1">
       <c r="A146" s="4" t="s">
         <v>238</v>
       </c>
@@ -11301,7 +11383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:27">
+    <row r="147" spans="1:27" hidden="1">
       <c r="A147" s="4" t="s">
         <v>240</v>
       </c>
@@ -11352,7 +11434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:27">
+    <row r="148" spans="1:27" hidden="1">
       <c r="A148" s="4" t="s">
         <v>241</v>
       </c>
@@ -11416,9 +11498,12 @@
       <c r="E149" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="G149" s="4">
+        <v>50</v>
+      </c>
       <c r="T149" s="4">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U149" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D149="Nie",E149="Nie"),0,IF(AND(D149="Tak",E149="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -11426,7 +11511,7 @@
       </c>
       <c r="V149" s="4">
         <f t="shared" si="7"/>
-        <v>-430</v>
+        <v>-380</v>
       </c>
       <c r="W149" s="55" t="str">
         <f t="shared" si="8"/>
@@ -11442,7 +11527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:27">
+    <row r="150" spans="1:27" hidden="1">
       <c r="A150" s="4" t="s">
         <v>242</v>
       </c>
@@ -11487,7 +11572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:27">
+    <row r="151" spans="1:27" hidden="1">
       <c r="A151" s="4" t="s">
         <v>243</v>
       </c>
@@ -11538,7 +11623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:27">
+    <row r="152" spans="1:27" hidden="1">
       <c r="A152" s="4" t="s">
         <v>86</v>
       </c>
@@ -11583,7 +11668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:27">
+    <row r="153" spans="1:27" hidden="1">
       <c r="A153" s="4" t="s">
         <v>145</v>
       </c>
@@ -11628,7 +11713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:27">
+    <row r="154" spans="1:27" hidden="1">
       <c r="A154" s="4" t="s">
         <v>247</v>
       </c>
@@ -11679,7 +11764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:27">
+    <row r="155" spans="1:27" hidden="1">
       <c r="A155" s="4" t="s">
         <v>249</v>
       </c>
@@ -11738,7 +11823,10 @@
         <v>27</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="G156" s="4">
+        <v>50</v>
       </c>
       <c r="K156" s="4">
         <v>100</v>
@@ -11748,15 +11836,15 @@
       </c>
       <c r="T156" s="4">
         <f t="shared" si="9"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U156" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D156="Nie",E156="Nie"),0,IF(AND(D156="Tak",E156="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
-        <v>700</v>
+        <v>430</v>
       </c>
       <c r="V156" s="4">
         <f t="shared" si="7"/>
-        <v>-500</v>
+        <v>-180</v>
       </c>
       <c r="W156" s="55" t="str">
         <f t="shared" si="8"/>
@@ -11772,7 +11860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:27">
+    <row r="157" spans="1:27" hidden="1">
       <c r="A157" s="4" t="s">
         <v>251</v>
       </c>
@@ -11814,7 +11902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:27">
+    <row r="158" spans="1:27" hidden="1">
       <c r="A158" s="4" t="s">
         <v>252</v>
       </c>
@@ -11862,7 +11950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:27">
+    <row r="159" spans="1:27" hidden="1">
       <c r="A159" s="4" t="s">
         <v>253</v>
       </c>
@@ -11907,7 +11995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:27">
+    <row r="160" spans="1:27" hidden="1">
       <c r="A160" s="4" t="s">
         <v>255</v>
       </c>
@@ -11952,7 +12040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:27">
+    <row r="161" spans="1:27" hidden="1">
       <c r="A161" s="4" t="s">
         <v>140</v>
       </c>
@@ -11997,7 +12085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:27">
+    <row r="162" spans="1:27" hidden="1">
       <c r="A162" s="4" t="s">
         <v>86</v>
       </c>
@@ -12042,7 +12130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:27">
+    <row r="163" spans="1:27" hidden="1">
       <c r="A163" s="4" t="s">
         <v>256</v>
       </c>
@@ -12087,7 +12175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:27">
+    <row r="164" spans="1:27" hidden="1">
       <c r="A164" s="4" t="s">
         <v>257</v>
       </c>
@@ -12132,7 +12220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:27">
+    <row r="165" spans="1:27" hidden="1">
       <c r="A165" s="4" t="s">
         <v>258</v>
       </c>
@@ -12177,7 +12265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:27">
+    <row r="166" spans="1:27" hidden="1">
       <c r="A166" s="4" t="s">
         <v>259</v>
       </c>
@@ -12222,7 +12310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:27">
+    <row r="167" spans="1:27" hidden="1">
       <c r="A167" s="4" t="s">
         <v>261</v>
       </c>
@@ -12283,9 +12371,12 @@
       <c r="E168" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G168" s="4">
+        <v>50</v>
+      </c>
       <c r="T168" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U168" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D168="Nie",E168="Nie"),0,IF(AND(D168="Tak",E168="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -12293,7 +12384,7 @@
       </c>
       <c r="V168" s="4">
         <f t="shared" si="7"/>
-        <v>-700</v>
+        <v>-650</v>
       </c>
       <c r="W168" s="55" t="str">
         <f t="shared" si="8"/>
@@ -12309,7 +12400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:27">
+    <row r="169" spans="1:27" hidden="1">
       <c r="A169" s="4" t="s">
         <v>263</v>
       </c>
@@ -12354,7 +12445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:27">
+    <row r="170" spans="1:27" hidden="1">
       <c r="A170" s="4" t="s">
         <v>264</v>
       </c>
@@ -12396,7 +12487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:27">
+    <row r="171" spans="1:27" hidden="1">
       <c r="A171" s="4" t="s">
         <v>266</v>
       </c>
@@ -12441,7 +12532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:27">
+    <row r="172" spans="1:27" hidden="1">
       <c r="A172" s="4" t="s">
         <v>268</v>
       </c>
@@ -12486,7 +12577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:27">
+    <row r="173" spans="1:27" hidden="1">
       <c r="A173" s="4" t="s">
         <v>269</v>
       </c>
@@ -12540,7 +12631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:27">
+    <row r="174" spans="1:27" hidden="1">
       <c r="A174" s="4" t="s">
         <v>271</v>
       </c>
@@ -12585,7 +12676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:27">
+    <row r="175" spans="1:27" hidden="1">
       <c r="A175" s="4" t="s">
         <v>272</v>
       </c>
@@ -12630,7 +12721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:27">
+    <row r="176" spans="1:27" hidden="1">
       <c r="A176" s="4" t="s">
         <v>273</v>
       </c>
@@ -12675,7 +12766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:27">
+    <row r="177" spans="1:27" hidden="1">
       <c r="A177" s="4" t="s">
         <v>274</v>
       </c>
@@ -12720,7 +12811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:27">
+    <row r="178" spans="1:27" hidden="1">
       <c r="A178" s="4" t="s">
         <v>242</v>
       </c>
@@ -12765,7 +12856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:27">
+    <row r="179" spans="1:27" hidden="1">
       <c r="A179" s="4" t="s">
         <v>276</v>
       </c>
@@ -12810,7 +12901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:27">
+    <row r="180" spans="1:27" hidden="1">
       <c r="A180" s="4" t="s">
         <v>277</v>
       </c>
@@ -12855,7 +12946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:27">
+    <row r="181" spans="1:27" hidden="1">
       <c r="A181" s="4" t="s">
         <v>91</v>
       </c>
@@ -12900,7 +12991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:27">
+    <row r="182" spans="1:27" hidden="1">
       <c r="A182" s="4" t="s">
         <v>280</v>
       </c>
@@ -12951,7 +13042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:27">
+    <row r="183" spans="1:27" hidden="1">
       <c r="A183" s="4" t="s">
         <v>281</v>
       </c>
@@ -12993,7 +13084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:27">
+    <row r="184" spans="1:27" hidden="1">
       <c r="A184" s="4" t="s">
         <v>283</v>
       </c>
@@ -13044,7 +13135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:27">
+    <row r="185" spans="1:27" hidden="1">
       <c r="A185" s="4" t="s">
         <v>284</v>
       </c>
@@ -13092,7 +13183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:27">
+    <row r="186" spans="1:27" hidden="1">
       <c r="A186" s="4" t="s">
         <v>112</v>
       </c>
@@ -13137,7 +13228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:27">
+    <row r="187" spans="1:27" hidden="1">
       <c r="A187" s="4" t="s">
         <v>286</v>
       </c>
@@ -13182,7 +13273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:27">
+    <row r="188" spans="1:27" hidden="1">
       <c r="A188" s="4" t="s">
         <v>287</v>
       </c>
@@ -13227,7 +13318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:27">
+    <row r="189" spans="1:27" hidden="1">
       <c r="A189" s="4" t="s">
         <v>289</v>
       </c>
@@ -13272,7 +13363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:27">
+    <row r="190" spans="1:27" hidden="1">
       <c r="A190" s="4" t="s">
         <v>290</v>
       </c>
@@ -13317,7 +13408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:27">
+    <row r="191" spans="1:27" hidden="1">
       <c r="A191" s="4" t="s">
         <v>291</v>
       </c>
@@ -13362,7 +13453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:27">
+    <row r="192" spans="1:27" hidden="1">
       <c r="A192" s="4" t="s">
         <v>292</v>
       </c>
@@ -13407,7 +13498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:27">
+    <row r="193" spans="1:27" hidden="1">
       <c r="A193" s="4" t="s">
         <v>293</v>
       </c>
@@ -13458,7 +13549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:27">
+    <row r="194" spans="1:27" hidden="1">
       <c r="A194" s="4" t="s">
         <v>294</v>
       </c>
@@ -13503,7 +13594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:27">
+    <row r="195" spans="1:27" hidden="1">
       <c r="A195" s="4" t="s">
         <v>296</v>
       </c>
@@ -13548,7 +13639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:27">
+    <row r="196" spans="1:27" hidden="1">
       <c r="A196" s="4" t="s">
         <v>298</v>
       </c>
@@ -13596,7 +13687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:27">
+    <row r="197" spans="1:27" hidden="1">
       <c r="A197" s="4" t="s">
         <v>299</v>
       </c>
@@ -13647,7 +13738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:27">
+    <row r="198" spans="1:27" hidden="1">
       <c r="A198" s="4" t="s">
         <v>300</v>
       </c>
@@ -13692,7 +13783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:27">
+    <row r="199" spans="1:27" hidden="1">
       <c r="A199" s="4" t="s">
         <v>301</v>
       </c>
@@ -13737,7 +13828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:27">
+    <row r="200" spans="1:27" hidden="1">
       <c r="A200" s="4" t="s">
         <v>303</v>
       </c>
@@ -13788,7 +13879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:27">
+    <row r="201" spans="1:27" hidden="1">
       <c r="A201" s="4" t="s">
         <v>56</v>
       </c>
@@ -13836,7 +13927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:27">
+    <row r="202" spans="1:27" hidden="1">
       <c r="A202" s="4" t="s">
         <v>305</v>
       </c>
@@ -13881,7 +13972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:27">
+    <row r="203" spans="1:27" hidden="1">
       <c r="A203" s="4" t="s">
         <v>306</v>
       </c>
@@ -13926,7 +14017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:27">
+    <row r="204" spans="1:27" hidden="1">
       <c r="A204" s="4" t="s">
         <v>307</v>
       </c>
@@ -13971,7 +14062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:27">
+    <row r="205" spans="1:27" hidden="1">
       <c r="A205" s="4" t="s">
         <v>309</v>
       </c>
@@ -14016,7 +14107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:27">
+    <row r="206" spans="1:27" hidden="1">
       <c r="A206" s="4" t="s">
         <v>310</v>
       </c>
@@ -14061,7 +14152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:27">
+    <row r="207" spans="1:27" hidden="1">
       <c r="A207" s="4" t="s">
         <v>311</v>
       </c>
@@ -14106,7 +14197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:27">
+    <row r="208" spans="1:27" hidden="1">
       <c r="A208" s="4" t="s">
         <v>312</v>
       </c>
@@ -14154,7 +14245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:27">
+    <row r="209" spans="1:27" hidden="1">
       <c r="A209" s="4" t="s">
         <v>313</v>
       </c>
@@ -14199,7 +14290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:27">
+    <row r="210" spans="1:27" hidden="1">
       <c r="A210" s="4" t="s">
         <v>315</v>
       </c>
@@ -14244,7 +14335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:27">
+    <row r="211" spans="1:27" hidden="1">
       <c r="A211" s="4" t="s">
         <v>316</v>
       </c>
@@ -14289,7 +14380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:27">
+    <row r="212" spans="1:27" hidden="1">
       <c r="A212" s="4" t="s">
         <v>318</v>
       </c>
@@ -14334,7 +14425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:27">
+    <row r="213" spans="1:27" hidden="1">
       <c r="A213" s="4" t="s">
         <v>319</v>
       </c>
@@ -14385,7 +14476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:27">
+    <row r="214" spans="1:27" hidden="1">
       <c r="A214" s="4" t="s">
         <v>320</v>
       </c>
@@ -14436,7 +14527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:27">
+    <row r="215" spans="1:27" hidden="1">
       <c r="A215" s="4" t="s">
         <v>321</v>
       </c>
@@ -14481,7 +14572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:27">
+    <row r="216" spans="1:27" hidden="1">
       <c r="A216" s="4" t="s">
         <v>322</v>
       </c>
@@ -14526,7 +14617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:27">
+    <row r="217" spans="1:27" hidden="1">
       <c r="A217" s="4" t="s">
         <v>323</v>
       </c>
@@ -14587,6 +14678,9 @@
       <c r="E218" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="G218" s="4">
+        <v>50</v>
+      </c>
       <c r="K218" s="4">
         <v>100</v>
       </c>
@@ -14595,7 +14689,7 @@
       </c>
       <c r="T218" s="4">
         <f t="shared" si="13"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U218" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D218="Nie",E218="Nie"),0,IF(AND(D218="Tak",E218="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -14603,7 +14697,7 @@
       </c>
       <c r="V218" s="4">
         <f t="shared" si="11"/>
-        <v>-230</v>
+        <v>-180</v>
       </c>
       <c r="W218" s="55" t="str">
         <f t="shared" si="12"/>
@@ -14635,6 +14729,9 @@
       <c r="E219" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="G219" s="4">
+        <v>50</v>
+      </c>
       <c r="K219" s="4">
         <v>100</v>
       </c>
@@ -14643,7 +14740,7 @@
       </c>
       <c r="T219" s="4">
         <f t="shared" si="13"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U219" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D219="Nie",E219="Nie"),0,IF(AND(D219="Tak",E219="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -14651,7 +14748,7 @@
       </c>
       <c r="V219" s="4">
         <f t="shared" si="11"/>
-        <v>-230</v>
+        <v>-180</v>
       </c>
       <c r="W219" s="55" t="str">
         <f t="shared" si="12"/>
@@ -14667,7 +14764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:27">
+    <row r="220" spans="1:27" hidden="1">
       <c r="A220" s="4" t="s">
         <v>325</v>
       </c>
@@ -14712,7 +14809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:27">
+    <row r="221" spans="1:27" hidden="1">
       <c r="A221" s="4" t="s">
         <v>327</v>
       </c>
@@ -14757,7 +14854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:27">
+    <row r="222" spans="1:27" hidden="1">
       <c r="A222" s="4" t="s">
         <v>328</v>
       </c>
@@ -14808,7 +14905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:27">
+    <row r="223" spans="1:27" hidden="1">
       <c r="A223" s="4" t="s">
         <v>273</v>
       </c>
@@ -14869,6 +14966,9 @@
       <c r="E224" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G224" s="4">
+        <v>50</v>
+      </c>
       <c r="K224" s="4">
         <v>100</v>
       </c>
@@ -14877,7 +14977,7 @@
       </c>
       <c r="T224" s="4">
         <f t="shared" si="13"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U224" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D224="Nie",E224="Nie"),0,IF(AND(D224="Tak",E224="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -14885,7 +14985,7 @@
       </c>
       <c r="V224" s="4">
         <f t="shared" si="11"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W224" s="55" t="str">
         <f t="shared" si="12"/>
@@ -14901,7 +15001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:27">
+    <row r="225" spans="1:27" hidden="1">
       <c r="A225" s="4" t="s">
         <v>331</v>
       </c>
@@ -14946,7 +15046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:27">
+    <row r="226" spans="1:27" hidden="1">
       <c r="A226" s="4" t="str">
         <f>IF('Ankieta#1_13.04.26'!F225="","",'Ankieta#1_13.04.26'!F225)</f>
         <v>Sawka</v>
@@ -14996,7 +15096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:27">
+    <row r="227" spans="1:27" hidden="1">
       <c r="A227" s="4" t="str">
         <f>IF('Ankieta#1_13.04.26'!F226="","",'Ankieta#1_13.04.26'!F226)</f>
         <v>Olczyk</v>
@@ -15046,7 +15146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:27">
+    <row r="228" spans="1:27" hidden="1">
       <c r="A228" s="4" t="str">
         <f>IF('Ankieta#1_13.04.26'!F227="","",'Ankieta#1_13.04.26'!F227)</f>
         <v xml:space="preserve">Bogacka </v>
@@ -15096,7 +15196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:27">
+    <row r="229" spans="1:27" hidden="1">
       <c r="A229" s="4" t="str">
         <f>IF('Ankieta#1_13.04.26'!F228="","",'Ankieta#1_13.04.26'!F228)</f>
         <v xml:space="preserve">Rajtar </v>
@@ -15167,6 +15267,9 @@
         <f>IF('Ankieta#1_13.04.26'!I229="","",'Ankieta#1_13.04.26'!I229)</f>
         <v>Nie</v>
       </c>
+      <c r="G230" s="4">
+        <v>50</v>
+      </c>
       <c r="K230" s="4">
         <v>100</v>
       </c>
@@ -15175,7 +15278,7 @@
       </c>
       <c r="T230" s="4">
         <f t="shared" si="13"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U230" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D230="Nie",E230="Nie"),0,IF(AND(D230="Tak",E230="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -15183,7 +15286,7 @@
       </c>
       <c r="V230" s="4">
         <f t="shared" si="11"/>
-        <v>-230</v>
+        <v>-180</v>
       </c>
       <c r="W230" s="55" t="str">
         <f t="shared" si="12"/>
@@ -15220,6 +15323,9 @@
         <f>IF('Ankieta#1_13.04.26'!I230="","",'Ankieta#1_13.04.26'!I230)</f>
         <v>Tak</v>
       </c>
+      <c r="G231" s="4">
+        <v>50</v>
+      </c>
       <c r="K231" s="4">
         <v>100</v>
       </c>
@@ -15228,7 +15334,7 @@
       </c>
       <c r="T231" s="4">
         <f t="shared" ref="T231:T235" si="14">SUM(G231:S231)</f>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U231" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D231="Nie",E231="Nie"),0,IF(AND(D231="Tak",E231="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -15236,7 +15342,7 @@
       </c>
       <c r="V231" s="4">
         <f t="shared" si="11"/>
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="W231" s="55" t="str">
         <f t="shared" si="12"/>
@@ -15273,6 +15379,9 @@
         <f>IF('Ankieta#1_13.04.26'!I231="","",'Ankieta#1_13.04.26'!I231)</f>
         <v>Tak</v>
       </c>
+      <c r="G232" s="4">
+        <v>50</v>
+      </c>
       <c r="K232" s="4">
         <v>100</v>
       </c>
@@ -15284,7 +15393,7 @@
       </c>
       <c r="T232" s="4">
         <f t="shared" si="14"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="U232" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D232="Nie",E232="Nie"),0,IF(AND(D232="Tak",E232="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -15292,7 +15401,7 @@
       </c>
       <c r="V232" s="4">
         <f t="shared" si="11"/>
-        <v>-400</v>
+        <v>-350</v>
       </c>
       <c r="W232" s="55" t="str">
         <f t="shared" si="12"/>
@@ -15308,7 +15417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:27">
+    <row r="233" spans="1:27" hidden="1">
       <c r="A233" s="4" t="str">
         <f>IF('Ankieta#1_13.04.26'!F232="","",'Ankieta#1_13.04.26'!F232)</f>
         <v>Kowalczyk</v>
@@ -15358,7 +15467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:27">
+    <row r="234" spans="1:27" hidden="1">
       <c r="A234" s="4" t="str">
         <f>IF('Ankieta#1_13.04.26'!F233="","",'Ankieta#1_13.04.26'!F233)</f>
         <v>Nowak</v>
@@ -15408,7 +15517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:27">
+    <row r="235" spans="1:27" hidden="1">
       <c r="A235" s="4" t="str">
         <f>IF('Ankieta#1_13.04.26'!F234="","",'Ankieta#1_13.04.26'!F234)</f>
         <v>Domański</v>
@@ -18914,21 +19023,21 @@
       </c>
       <c r="D3" s="33">
         <f>Podsumowanie!C12</f>
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E3" s="88">
         <v>270</v>
       </c>
       <c r="F3" s="88">
         <f>Table1[[#This Row],[Ilość]]*Table1[[#This Row],[Cena]]</f>
-        <v>101250</v>
+        <v>100980</v>
       </c>
       <c r="G3" s="88">
         <v>2000</v>
       </c>
       <c r="H3" s="88">
         <f>Table1[[#This Row],[Koszt]]-Table1[[#This Row],[Zaliczka]]</f>
-        <v>99250</v>
+        <v>98980</v>
       </c>
       <c r="I3" s="122" t="s">
         <v>342</v>
@@ -19114,19 +19223,19 @@
       <c r="C10" s="32"/>
       <c r="D10" s="33">
         <f>(D3+D4)*1.1</f>
-        <v>445.50000000000006</v>
+        <v>444.40000000000003</v>
       </c>
       <c r="E10" s="88">
         <v>7.5</v>
       </c>
       <c r="F10" s="88">
         <f>Table1[[#This Row],[Ilość]]*Table1[[#This Row],[Cena]]</f>
-        <v>3341.2500000000005</v>
+        <v>3333.0000000000005</v>
       </c>
       <c r="G10" s="88"/>
       <c r="H10" s="88">
         <f>Table1[[#This Row],[Koszt]]-Table1[[#This Row],[Zaliczka]]</f>
-        <v>3341.2500000000005</v>
+        <v>3333.0000000000005</v>
       </c>
       <c r="I10" s="122"/>
     </row>
@@ -19224,7 +19333,7 @@
       <c r="E14" s="35"/>
       <c r="F14" s="34">
         <f>SUBTOTAL(109,F3:F13)</f>
-        <v>133181.25</v>
+        <v>132903</v>
       </c>
       <c r="G14" s="34">
         <f>SUBTOTAL(109,G3:G13)</f>
@@ -19232,7 +19341,7 @@
       </c>
       <c r="H14" s="34">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>128501.25</v>
+        <v>128223</v>
       </c>
       <c r="I14" s="35"/>
     </row>
@@ -19465,11 +19574,11 @@
       </c>
       <c r="C5" s="40">
         <f>COUNTIFS('Lista uczniów_składki'!E:E,"Tak",'Lista uczniów_składki'!C:C,Podsumowanie!A5)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="38">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="124">
         <v>35</v>
@@ -19489,15 +19598,15 @@
       <c r="I5" s="60"/>
       <c r="J5" s="91">
         <f>SUMIFS('Lista uczniów_składki'!U:U,'Lista uczniów_składki'!C:C,Podsumowanie!A5)</f>
-        <v>21800</v>
+        <v>21530</v>
       </c>
       <c r="K5" s="91">
         <f>SUMIFS('Lista uczniów_składki'!T:T,'Lista uczniów_składki'!C:C,Podsumowanie!A5)</f>
-        <v>6000</v>
+        <v>7750</v>
       </c>
       <c r="L5" s="91">
         <f t="shared" si="2"/>
-        <v>-15800</v>
+        <v>-13780</v>
       </c>
       <c r="T5" s="63"/>
       <c r="U5" s="90"/>
@@ -19651,15 +19760,15 @@
       <c r="E9" s="63"/>
       <c r="J9" s="91">
         <f>SUM(J2:J8)</f>
-        <v>137250</v>
+        <v>136980</v>
       </c>
       <c r="K9" s="91">
         <f t="shared" ref="K9:L9" si="4">SUM(K2:K8)</f>
-        <v>21300</v>
+        <v>23050</v>
       </c>
       <c r="L9" s="91">
         <f t="shared" si="4"/>
-        <v>-115950</v>
+        <v>-113930</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -19679,7 +19788,7 @@
       </c>
       <c r="C12" s="126">
         <f>SUM(B12:B13)</f>
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E12" s="63"/>
     </row>
@@ -19689,7 +19798,7 @@
       </c>
       <c r="B13" s="17">
         <f>SUM(C2:C8)</f>
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C13" s="127"/>
       <c r="E13" s="63"/>
@@ -19733,7 +19842,7 @@
       </c>
       <c r="B15" s="12">
         <f>SUM(Wydatki!F3:F4)</f>
-        <v>101250</v>
+        <v>100980</v>
       </c>
       <c r="E15" s="63"/>
     </row>
@@ -19743,7 +19852,7 @@
       </c>
       <c r="B16" s="13">
         <f>SUM(Wydatki!F5:F13)</f>
-        <v>31931.25</v>
+        <v>31923</v>
       </c>
       <c r="E16" s="63"/>
       <c r="H16" s="61"/>
@@ -19755,7 +19864,7 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B15:B16)</f>
-        <v>133181.25</v>
+        <v>132903</v>
       </c>
       <c r="E17" s="63"/>
       <c r="H17" s="61"/>
@@ -19803,7 +19912,7 @@
       </c>
       <c r="B22" s="11">
         <f>B19*B12+B20*B13</f>
-        <v>137250</v>
+        <v>136980</v>
       </c>
       <c r="E22" s="108"/>
     </row>
@@ -19813,7 +19922,7 @@
       </c>
       <c r="B23" s="12">
         <f>SUM(Table1[Koszt])</f>
-        <v>133181.25</v>
+        <v>132903</v>
       </c>
       <c r="E23" s="63"/>
     </row>
@@ -19823,7 +19932,7 @@
       </c>
       <c r="B24" s="15">
         <f>B22-B23</f>
-        <v>4068.75</v>
+        <v>4077</v>
       </c>
       <c r="E24" s="63"/>
     </row>
@@ -19842,7 +19951,7 @@
       </c>
       <c r="B27" s="18">
         <f>IF(B2=0,"",B$24/SUM($B$3:$B$8)*B2)</f>
-        <v>699.31640625</v>
+        <v>700.734375</v>
       </c>
       <c r="E27" s="63"/>
     </row>
@@ -19852,7 +19961,7 @@
       </c>
       <c r="B28" s="18">
         <f>IF(B3=0,"",B$24/SUM($B$3:$B$8)*B3)</f>
-        <v>508.59375</v>
+        <v>509.625</v>
       </c>
       <c r="E28" s="45"/>
       <c r="H28" s="62"/>
@@ -19864,7 +19973,7 @@
       </c>
       <c r="B29" s="18">
         <f>IF(B4=0,"",B$24/SUM($B$3:$B$8)*B4)</f>
-        <v>741.69921875</v>
+        <v>743.203125</v>
       </c>
       <c r="E29" s="63"/>
     </row>
@@ -19874,7 +19983,7 @@
       </c>
       <c r="B30" s="18">
         <f>IF(B5=0,"",B$24/SUM($B$3:$B$8)*B5)</f>
-        <v>741.69921875</v>
+        <v>743.203125</v>
       </c>
       <c r="E30" s="63"/>
     </row>
@@ -19884,7 +19993,7 @@
       </c>
       <c r="B31" s="18">
         <f>IF(B6=0,"",B$24/SUM($B$3:$B$8)*B6)</f>
-        <v>741.69921875</v>
+        <v>743.203125</v>
       </c>
       <c r="E31" s="63"/>
     </row>
@@ -19894,7 +20003,7 @@
       </c>
       <c r="B32" s="18">
         <f>IF(B7=0,"",B$24/SUM($B$3:$B$8)*B7)</f>
-        <v>720.5078125</v>
+        <v>721.96875</v>
       </c>
       <c r="E32" s="63"/>
     </row>
@@ -19904,7 +20013,7 @@
       </c>
       <c r="B33" s="18">
         <f>IF(B8=0,"",B$24/SUM($B$3:$B$8)*B8)</f>
-        <v>614.55078125</v>
+        <v>615.796875</v>
       </c>
       <c r="E33" s="63"/>
     </row>
@@ -19985,7 +20094,7 @@
       </c>
       <c r="D7" s="68">
         <f>SUM(Podsumowanie!C2:C8)</f>
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -19994,7 +20103,7 @@
       </c>
       <c r="D8" s="68">
         <f>D6+D7</f>
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" customHeight="1">
@@ -20039,7 +20148,7 @@
       </c>
       <c r="D12" s="71">
         <f>Wydatki!F3</f>
-        <v>101250</v>
+        <v>100980</v>
       </c>
       <c r="E12" s="115" t="s">
         <v>342</v>
@@ -20159,7 +20268,7 @@
       </c>
       <c r="D19" s="71">
         <f>Wydatki!F10</f>
-        <v>3341.2500000000005</v>
+        <v>3333.0000000000005</v>
       </c>
       <c r="E19" s="115"/>
     </row>
@@ -20219,7 +20328,7 @@
       </c>
       <c r="D23" s="75">
         <f>Wydatki!F14</f>
-        <v>133181.25</v>
+        <v>132903</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -20333,15 +20442,15 @@
       </c>
       <c r="D36" s="95">
         <f>SUMIFS('Lista uczniów_składki'!U:U,'Lista uczniów_składki'!C:C,'Do wiadomości rodziców'!C36)</f>
-        <v>21800</v>
+        <v>21530</v>
       </c>
       <c r="E36" s="96">
         <f>SUMIFS('Lista uczniów_składki'!T:T,'Lista uczniów_składki'!C:C,'Do wiadomości rodziców'!C36)</f>
-        <v>6000</v>
+        <v>7750</v>
       </c>
       <c r="F36" s="91">
         <f t="shared" si="0"/>
-        <v>-15800</v>
+        <v>-13780</v>
       </c>
     </row>
     <row r="37" spans="3:6">
@@ -20401,15 +20510,15 @@
       </c>
       <c r="D40" s="121">
         <f>SUBTOTAL(109,D33:D39)</f>
-        <v>137250</v>
+        <v>136980</v>
       </c>
       <c r="E40" s="121">
         <f>SUBTOTAL(109,E33:E39)</f>
-        <v>21300</v>
+        <v>23050</v>
       </c>
       <c r="F40" s="121">
         <f>SUBTOTAL(109,Table5[Delta])</f>
-        <v>-115950</v>
+        <v>-113930</v>
       </c>
     </row>
     <row r="41" spans="3:6">
@@ -30267,7 +30376,7 @@
       </c>
       <c r="AD7" s="91">
         <f>Wydatki!F3</f>
-        <v>101250</v>
+        <v>100980</v>
       </c>
       <c r="AE7" s="91">
         <f>Wydatki!G3</f>
@@ -30275,7 +30384,7 @@
       </c>
       <c r="AF7" s="91">
         <f>Wydatki!H3</f>
-        <v>99250</v>
+        <v>98980</v>
       </c>
       <c r="AG7" t="str">
         <f>Wydatki!I3</f>
@@ -30287,7 +30396,7 @@
       </c>
       <c r="AO7" s="91">
         <f>Podsumowanie!B27</f>
-        <v>699.31640625</v>
+        <v>700.734375</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -30367,7 +30476,7 @@
       </c>
       <c r="AO8" s="91">
         <f>Podsumowanie!B28</f>
-        <v>508.59375</v>
+        <v>509.625</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -30453,7 +30562,7 @@
       </c>
       <c r="AO9" s="91">
         <f>Podsumowanie!B29</f>
-        <v>741.69921875</v>
+        <v>743.203125</v>
       </c>
     </row>
     <row r="10" spans="1:41">
@@ -30503,7 +30612,7 @@
       </c>
       <c r="Y10">
         <f>'Do wiadomości rodziców'!D7</f>
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AC10" t="str">
         <f>Wydatki!A6</f>
@@ -30531,7 +30640,7 @@
       </c>
       <c r="AO10" s="91">
         <f>Podsumowanie!B30</f>
-        <v>741.69921875</v>
+        <v>743.203125</v>
       </c>
     </row>
     <row r="11" spans="1:41">
@@ -30545,19 +30654,19 @@
       </c>
       <c r="J11">
         <f>Podsumowanie!C5</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K11" s="91">
         <f>Podsumowanie!J5</f>
-        <v>21800</v>
+        <v>21530</v>
       </c>
       <c r="L11" s="91">
         <f>Podsumowanie!K5</f>
-        <v>6000</v>
+        <v>7750</v>
       </c>
       <c r="M11" s="91">
         <f>Podsumowanie!L5</f>
-        <v>-15800</v>
+        <v>-13780</v>
       </c>
       <c r="P11" t="str">
         <f>'Do wiadomości rodziców'!C35</f>
@@ -30609,7 +30718,7 @@
       </c>
       <c r="AO11" s="91">
         <f>Podsumowanie!B31</f>
-        <v>741.69921875</v>
+        <v>743.203125</v>
       </c>
     </row>
     <row r="12" spans="1:41">
@@ -30643,15 +30752,15 @@
       </c>
       <c r="Q12" s="91">
         <f>'Do wiadomości rodziców'!D36</f>
-        <v>21800</v>
+        <v>21530</v>
       </c>
       <c r="R12" s="91">
         <f>'Do wiadomości rodziców'!E36</f>
-        <v>6000</v>
+        <v>7750</v>
       </c>
       <c r="S12" s="91">
         <f>'Do wiadomości rodziców'!F36</f>
-        <v>-15800</v>
+        <v>-13780</v>
       </c>
       <c r="AC12" t="str">
         <f>Wydatki!A8</f>
@@ -30679,7 +30788,7 @@
       </c>
       <c r="AO12" s="91">
         <f>Podsumowanie!B32</f>
-        <v>720.5078125</v>
+        <v>721.96875</v>
       </c>
     </row>
     <row r="13" spans="1:41">
@@ -30749,7 +30858,7 @@
       </c>
       <c r="AO13" s="91">
         <f>Podsumowanie!B33</f>
-        <v>614.55078125</v>
+        <v>615.796875</v>
       </c>
     </row>
     <row r="14" spans="1:41">
@@ -30799,7 +30908,7 @@
       </c>
       <c r="AD14" s="91">
         <f>Wydatki!F10</f>
-        <v>3341.2500000000005</v>
+        <v>3333.0000000000005</v>
       </c>
       <c r="AE14" s="91">
         <f>Wydatki!G10</f>
@@ -30807,7 +30916,7 @@
       </c>
       <c r="AF14" s="91">
         <f>Wydatki!H10</f>
-        <v>3341.2500000000005</v>
+        <v>3333.0000000000005</v>
       </c>
       <c r="AG14">
         <f>Wydatki!I10</f>
@@ -30859,15 +30968,15 @@
       </c>
       <c r="Q16" s="91">
         <f>'Do wiadomości rodziców'!D40</f>
-        <v>137250</v>
+        <v>136980</v>
       </c>
       <c r="R16" s="91">
         <f>'Do wiadomości rodziców'!E40</f>
-        <v>21300</v>
+        <v>23050</v>
       </c>
       <c r="S16" s="91">
         <f>'Do wiadomości rodziców'!F40</f>
-        <v>-115950</v>
+        <v>-113930</v>
       </c>
       <c r="AC16" t="str">
         <f>Wydatki!A12</f>
@@ -30915,7 +31024,7 @@
     <row r="18" spans="29:33">
       <c r="AD18" s="91">
         <f>Wydatki!F14</f>
-        <v>133181.25</v>
+        <v>132903</v>
       </c>
       <c r="AE18" s="91">
         <f>Wydatki!G14</f>
@@ -30923,7 +31032,7 @@
       </c>
       <c r="AF18" s="91">
         <f>Wydatki!H14</f>
-        <v>128501.25</v>
+        <v>128223</v>
       </c>
     </row>
   </sheetData>

--- a/Studniówka 2027_I LO.xlsx
+++ b/Studniówka 2027_I LO.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DE188DB-5603-4D32-A53E-012A14E135CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48852396-9B25-4163-999F-D280AD919AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2817" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2818" uniqueCount="484">
   <si>
     <t>Nazwisko</t>
   </si>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>Wróblewska</t>
+  </si>
+  <si>
+    <t>zrezygnowała z os. Tow.14.10</t>
   </si>
   <si>
     <t>Owsiana</t>
@@ -2267,6 +2270,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2294,7 +2298,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3788,7 +3791,7 @@
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main">
@@ -3856,13 +3859,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main">
@@ -3988,7 +3991,7 @@
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1">
       <filters>
-        <filter val="3D1"/>
+        <filter val="3C"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3" hiddenButton="1"/>
@@ -4651,7 +4654,7 @@
     <row r="1" spans="1:27">
       <c r="G1" s="4">
         <f>SUBTOTAL(9,G3:G614)</f>
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="H1" s="4">
         <f t="shared" ref="H1:S1" si="0">SUBTOTAL(9,H3:H614)</f>
@@ -4687,11 +4690,11 @@
       </c>
       <c r="P1" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="Q1" s="4">
         <f t="shared" si="0"/>
-        <v>8350</v>
+        <v>5000</v>
       </c>
       <c r="R1" s="4">
         <f t="shared" si="0"/>
@@ -4707,11 +4710,11 @@
       </c>
       <c r="U1" s="4">
         <f>SUBTOTAL(9,U3:U614)</f>
-        <v>18830</v>
+        <v>20180</v>
       </c>
       <c r="V1" s="4">
         <f>SUBTOTAL(9,V3:V614)</f>
-        <v>-8730</v>
+        <v>-10080</v>
       </c>
     </row>
     <row r="2" spans="1:27" s="3" customFormat="1" ht="36.75" customHeight="1">
@@ -4878,7 +4881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" hidden="1">
       <c r="A5" s="4" t="s">
         <v>30</v>
       </c>
@@ -5016,7 +5019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" hidden="1">
       <c r="A8" s="4" t="s">
         <v>38</v>
       </c>
@@ -5109,7 +5112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" hidden="1">
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
@@ -5157,7 +5160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" hidden="1">
       <c r="A11" s="4" t="s">
         <v>43</v>
       </c>
@@ -5250,7 +5253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" hidden="1">
       <c r="A13" s="4" t="s">
         <v>47</v>
       </c>
@@ -5439,7 +5442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" hidden="1">
       <c r="A17" s="4" t="s">
         <v>56</v>
       </c>
@@ -5772,7 +5775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" hidden="1">
       <c r="A24" s="4" t="s">
         <v>69</v>
       </c>
@@ -5868,7 +5871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" hidden="1">
       <c r="A26" s="4" t="s">
         <v>72</v>
       </c>
@@ -5916,7 +5919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" hidden="1">
       <c r="A27" s="4" t="s">
         <v>74</v>
       </c>
@@ -5964,7 +5967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" hidden="1">
       <c r="A28" s="4" t="s">
         <v>75</v>
       </c>
@@ -6012,7 +6015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" hidden="1">
       <c r="A29" s="4" t="s">
         <v>77</v>
       </c>
@@ -6060,7 +6063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" hidden="1">
       <c r="A30" s="4" t="s">
         <v>79</v>
       </c>
@@ -6252,7 +6255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:27" hidden="1">
+    <row r="34" spans="1:27">
       <c r="A34" s="4" t="s">
         <v>86</v>
       </c>
@@ -6274,9 +6277,12 @@
       <c r="P34" s="4">
         <v>100</v>
       </c>
+      <c r="Q34" s="4">
+        <v>200</v>
+      </c>
       <c r="T34" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U34" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D34="Nie",E34="Nie"),0,IF(AND(D34="Tak",E34="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6284,7 +6290,7 @@
       </c>
       <c r="V34" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W34" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6300,7 +6306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:27" hidden="1">
+    <row r="35" spans="1:27">
       <c r="A35" s="4" t="s">
         <v>88</v>
       </c>
@@ -6322,9 +6328,12 @@
       <c r="P35" s="4">
         <v>100</v>
       </c>
+      <c r="Q35" s="4">
+        <v>200</v>
+      </c>
       <c r="T35" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U35" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D35="Nie",E35="Nie"),0,IF(AND(D35="Tak",E35="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6332,7 +6341,7 @@
       </c>
       <c r="V35" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W35" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6348,7 +6357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:27" hidden="1">
+    <row r="36" spans="1:27">
       <c r="A36" s="4" t="s">
         <v>90</v>
       </c>
@@ -6370,9 +6379,12 @@
       <c r="P36" s="4">
         <v>100</v>
       </c>
+      <c r="Q36" s="4">
+        <v>200</v>
+      </c>
       <c r="T36" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U36" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D36="Nie",E36="Nie"),0,IF(AND(D36="Tak",E36="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6380,7 +6392,7 @@
       </c>
       <c r="V36" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W36" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6396,7 +6408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:27" hidden="1">
+    <row r="37" spans="1:27">
       <c r="A37" s="4" t="s">
         <v>91</v>
       </c>
@@ -6418,9 +6430,12 @@
       <c r="P37" s="4">
         <v>100</v>
       </c>
+      <c r="Q37" s="4">
+        <v>100</v>
+      </c>
       <c r="T37" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U37" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D37="Nie",E37="Nie"),0,IF(AND(D37="Tak",E37="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6428,7 +6443,7 @@
       </c>
       <c r="V37" s="4">
         <f t="shared" si="1"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W37" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6444,7 +6459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:27" hidden="1">
+    <row r="38" spans="1:27">
       <c r="A38" s="4" t="s">
         <v>93</v>
       </c>
@@ -6466,9 +6481,12 @@
       <c r="P38" s="4">
         <v>100</v>
       </c>
+      <c r="Q38" s="4">
+        <v>100</v>
+      </c>
       <c r="T38" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U38" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D38="Nie",E38="Nie"),0,IF(AND(D38="Tak",E38="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6476,7 +6494,7 @@
       </c>
       <c r="V38" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-450</v>
       </c>
       <c r="W38" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6492,7 +6510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:27" hidden="1">
+    <row r="39" spans="1:27">
       <c r="A39" s="4" t="s">
         <v>94</v>
       </c>
@@ -6514,9 +6532,12 @@
       <c r="P39" s="4">
         <v>100</v>
       </c>
+      <c r="Q39" s="4">
+        <v>200</v>
+      </c>
       <c r="T39" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U39" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D39="Nie",E39="Nie"),0,IF(AND(D39="Tak",E39="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6524,7 +6545,7 @@
       </c>
       <c r="V39" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W39" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6540,7 +6561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:27" hidden="1">
+    <row r="40" spans="1:27">
       <c r="A40" s="4" t="s">
         <v>96</v>
       </c>
@@ -6562,9 +6583,12 @@
       <c r="P40" s="4">
         <v>100</v>
       </c>
+      <c r="Q40" s="4">
+        <v>200</v>
+      </c>
       <c r="T40" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U40" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D40="Nie",E40="Nie"),0,IF(AND(D40="Tak",E40="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6572,7 +6596,7 @@
       </c>
       <c r="V40" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W40" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6588,7 +6612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:27" hidden="1">
+    <row r="41" spans="1:27">
       <c r="A41" s="4" t="s">
         <v>97</v>
       </c>
@@ -6610,9 +6634,12 @@
       <c r="P41" s="4">
         <v>100</v>
       </c>
+      <c r="Q41" s="4">
+        <v>200</v>
+      </c>
       <c r="T41" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U41" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D41="Nie",E41="Nie"),0,IF(AND(D41="Tak",E41="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6620,7 +6647,7 @@
       </c>
       <c r="V41" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W41" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6636,7 +6663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:27" hidden="1">
+    <row r="42" spans="1:27">
       <c r="A42" s="4" t="s">
         <v>99</v>
       </c>
@@ -6658,9 +6685,12 @@
       <c r="P42" s="4">
         <v>100</v>
       </c>
+      <c r="Q42" s="4">
+        <v>200</v>
+      </c>
       <c r="T42" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U42" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D42="Nie",E42="Nie"),0,IF(AND(D42="Tak",E42="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6668,7 +6698,7 @@
       </c>
       <c r="V42" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W42" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6684,7 +6714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:27" hidden="1">
+    <row r="43" spans="1:27">
       <c r="A43" s="4" t="s">
         <v>101</v>
       </c>
@@ -6706,9 +6736,12 @@
       <c r="P43" s="4">
         <v>100</v>
       </c>
+      <c r="Q43" s="4">
+        <v>200</v>
+      </c>
       <c r="T43" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U43" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D43="Nie",E43="Nie"),0,IF(AND(D43="Tak",E43="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6716,7 +6749,7 @@
       </c>
       <c r="V43" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W43" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6732,7 +6765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:27" hidden="1">
+    <row r="44" spans="1:27">
       <c r="A44" s="4" t="s">
         <v>102</v>
       </c>
@@ -6754,9 +6787,12 @@
       <c r="P44" s="4">
         <v>100</v>
       </c>
+      <c r="Q44" s="4">
+        <v>100</v>
+      </c>
       <c r="T44" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U44" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D44="Nie",E44="Nie"),0,IF(AND(D44="Tak",E44="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6764,7 +6800,7 @@
       </c>
       <c r="V44" s="4">
         <f t="shared" si="1"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W44" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6828,7 +6864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:27" hidden="1">
+    <row r="46" spans="1:27">
       <c r="A46" s="4" t="s">
         <v>102</v>
       </c>
@@ -6850,9 +6886,12 @@
       <c r="P46" s="4">
         <v>100</v>
       </c>
+      <c r="Q46" s="4">
+        <v>200</v>
+      </c>
       <c r="T46" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U46" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D46="Nie",E46="Nie"),0,IF(AND(D46="Tak",E46="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -6860,7 +6899,7 @@
       </c>
       <c r="V46" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W46" s="55" t="str">
         <f t="shared" si="2"/>
@@ -6876,7 +6915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:27" hidden="1">
       <c r="A47" s="4" t="s">
         <v>106</v>
       </c>
@@ -6924,7 +6963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:27" hidden="1">
       <c r="A48" s="4" t="s">
         <v>108</v>
       </c>
@@ -6972,7 +7011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:27" hidden="1">
       <c r="A49" s="4" t="s">
         <v>110</v>
       </c>
@@ -7784,7 +7823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:27" hidden="1">
+    <row r="66" spans="1:27">
       <c r="A66" s="4" t="s">
         <v>148</v>
       </c>
@@ -7798,7 +7837,10 @@
         <v>27</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="G66" s="4">
         <v>50</v>
@@ -7806,17 +7848,20 @@
       <c r="P66" s="4">
         <v>100</v>
       </c>
+      <c r="Q66" s="4">
+        <v>100</v>
+      </c>
       <c r="T66" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U66" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D66="Nie",E66="Nie"),0,IF(AND(D66="Tak",E66="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
-        <v>700</v>
+        <v>430</v>
       </c>
       <c r="V66" s="4">
         <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-180</v>
       </c>
       <c r="W66" s="55" t="str">
         <f t="shared" si="2"/>
@@ -7834,7 +7879,7 @@
     </row>
     <row r="67" spans="1:27" hidden="1">
       <c r="A67" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>29</v>
@@ -7849,7 +7894,7 @@
         <v>27</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G67" s="4">
         <v>50</v>
@@ -7882,10 +7927,10 @@
     </row>
     <row r="68" spans="1:27" hidden="1">
       <c r="A68" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>26</v>
@@ -7927,7 +7972,7 @@
     </row>
     <row r="69" spans="1:27" hidden="1">
       <c r="A69" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>63</v>
@@ -7972,7 +8017,7 @@
     </row>
     <row r="70" spans="1:27" hidden="1">
       <c r="A70" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>63</v>
@@ -7987,7 +8032,7 @@
         <v>27</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G70" s="4">
         <v>50</v>
@@ -8018,9 +8063,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:27" hidden="1">
+    <row r="71" spans="1:27">
       <c r="A71" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>25</v>
@@ -8040,9 +8085,12 @@
       <c r="P71" s="4">
         <v>100</v>
       </c>
+      <c r="Q71" s="4">
+        <v>100</v>
+      </c>
       <c r="T71" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U71" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D71="Nie",E71="Nie"),0,IF(AND(D71="Tak",E71="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8050,7 +8098,7 @@
       </c>
       <c r="V71" s="4">
         <f t="shared" si="4"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W71" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8068,7 +8116,7 @@
     </row>
     <row r="72" spans="1:27" hidden="1">
       <c r="A72" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>100</v>
@@ -8114,9 +8162,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:27" hidden="1">
+    <row r="73" spans="1:27">
       <c r="A73" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>29</v>
@@ -8136,9 +8184,12 @@
       <c r="P73" s="4">
         <v>100</v>
       </c>
+      <c r="Q73" s="4">
+        <v>200</v>
+      </c>
       <c r="T73" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U73" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D73="Nie",E73="Nie"),0,IF(AND(D73="Tak",E73="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8146,7 +8197,7 @@
       </c>
       <c r="V73" s="4">
         <f t="shared" si="4"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W73" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8164,10 +8215,10 @@
     </row>
     <row r="74" spans="1:27" hidden="1">
       <c r="A74" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>113</v>
@@ -8207,9 +8258,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:27" hidden="1">
+    <row r="75" spans="1:27">
       <c r="A75" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>63</v>
@@ -8229,9 +8280,12 @@
       <c r="P75" s="4">
         <v>100</v>
       </c>
+      <c r="Q75" s="4">
+        <v>200</v>
+      </c>
       <c r="T75" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U75" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D75="Nie",E75="Nie"),0,IF(AND(D75="Tak",E75="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8239,7 +8293,7 @@
       </c>
       <c r="V75" s="4">
         <f t="shared" si="4"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W75" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8255,9 +8309,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:27" hidden="1">
+    <row r="76" spans="1:27">
       <c r="A76" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>63</v>
@@ -8277,9 +8331,12 @@
       <c r="P76" s="4">
         <v>100</v>
       </c>
+      <c r="Q76" s="4">
+        <v>100</v>
+      </c>
       <c r="T76" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U76" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D76="Nie",E76="Nie"),0,IF(AND(D76="Tak",E76="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8287,7 +8344,7 @@
       </c>
       <c r="V76" s="4">
         <f t="shared" si="4"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W76" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8303,7 +8360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:27" hidden="1">
+    <row r="77" spans="1:27">
       <c r="A77" s="4" t="s">
         <v>93</v>
       </c>
@@ -8322,9 +8379,12 @@
       <c r="G77" s="4">
         <v>50</v>
       </c>
+      <c r="Q77" s="4">
+        <v>100</v>
+      </c>
       <c r="T77" s="4">
         <f t="shared" si="6"/>
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U77" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D77="Nie",E77="Nie"),0,IF(AND(D77="Tak",E77="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8332,7 +8392,7 @@
       </c>
       <c r="V77" s="4">
         <f t="shared" si="4"/>
-        <v>-650</v>
+        <v>-550</v>
       </c>
       <c r="W77" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8350,10 +8410,10 @@
     </row>
     <row r="78" spans="1:27" hidden="1">
       <c r="A78" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>53</v>
@@ -8393,12 +8453,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:27" hidden="1">
+    <row r="79" spans="1:27">
       <c r="A79" s="4" t="s">
         <v>108</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>87</v>
@@ -8415,9 +8475,12 @@
       <c r="P79" s="4">
         <v>100</v>
       </c>
+      <c r="Q79" s="4">
+        <v>100</v>
+      </c>
       <c r="T79" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U79" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D79="Nie",E79="Nie"),0,IF(AND(D79="Tak",E79="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8425,7 +8488,7 @@
       </c>
       <c r="V79" s="4">
         <f t="shared" si="4"/>
-        <v>-550</v>
+        <v>-450</v>
       </c>
       <c r="W79" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8441,12 +8504,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:27" hidden="1">
+    <row r="80" spans="1:27">
       <c r="A80" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>87</v>
@@ -8463,9 +8526,12 @@
       <c r="P80" s="4">
         <v>100</v>
       </c>
+      <c r="Q80" s="4">
+        <v>100</v>
+      </c>
       <c r="T80" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U80" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D80="Nie",E80="Nie"),0,IF(AND(D80="Tak",E80="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8473,7 +8539,7 @@
       </c>
       <c r="V80" s="4">
         <f t="shared" si="4"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W80" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8489,12 +8555,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:27" hidden="1">
+    <row r="81" spans="1:27">
       <c r="A81" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>87</v>
@@ -8506,7 +8572,7 @@
         <v>33</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G81" s="4">
         <v>50</v>
@@ -8514,9 +8580,12 @@
       <c r="P81" s="4">
         <v>100</v>
       </c>
+      <c r="Q81" s="4">
+        <v>100</v>
+      </c>
       <c r="T81" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U81" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D81="Nie",E81="Nie"),0,IF(AND(D81="Tak",E81="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8524,7 +8593,7 @@
       </c>
       <c r="V81" s="4">
         <f t="shared" si="4"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W81" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8540,12 +8609,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:27" hidden="1">
+    <row r="82" spans="1:27">
       <c r="A82" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>87</v>
@@ -8562,9 +8631,12 @@
       <c r="P82" s="4">
         <v>100</v>
       </c>
+      <c r="Q82" s="4">
+        <v>100</v>
+      </c>
       <c r="T82" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U82" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D82="Nie",E82="Nie"),0,IF(AND(D82="Tak",E82="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -8572,7 +8644,7 @@
       </c>
       <c r="V82" s="4">
         <f t="shared" si="4"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W82" s="55" t="str">
         <f t="shared" si="5"/>
@@ -8590,7 +8662,7 @@
     </row>
     <row r="83" spans="1:27" hidden="1">
       <c r="A83" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>59</v>
@@ -8635,7 +8707,7 @@
     </row>
     <row r="84" spans="1:27" hidden="1">
       <c r="A84" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>65</v>
@@ -8650,7 +8722,7 @@
         <v>27</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G84" s="4">
         <v>50</v>
@@ -8731,13 +8803,13 @@
     </row>
     <row r="86" spans="1:27" hidden="1">
       <c r="A86" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>27</v>
@@ -8788,7 +8860,7 @@
     </row>
     <row r="87" spans="1:27" hidden="1">
       <c r="A87" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>76</v>
@@ -8831,12 +8903,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:27">
+    <row r="88" spans="1:27" hidden="1">
       <c r="A88" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>32</v>
@@ -8881,7 +8953,7 @@
     </row>
     <row r="89" spans="1:27" hidden="1">
       <c r="A89" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>59</v>
@@ -8929,10 +9001,10 @@
     </row>
     <row r="90" spans="1:27" hidden="1">
       <c r="A90" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>53</v>
@@ -8977,10 +9049,10 @@
     </row>
     <row r="91" spans="1:27" hidden="1">
       <c r="A91" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>53</v>
@@ -9025,13 +9097,13 @@
     </row>
     <row r="92" spans="1:27" hidden="1">
       <c r="A92" s="117" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>27</v>
@@ -9082,7 +9154,7 @@
         <v>59</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>27</v>
@@ -9127,13 +9199,13 @@
     </row>
     <row r="94" spans="1:27" hidden="1">
       <c r="A94" s="117" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>27</v>
@@ -9178,13 +9250,13 @@
     </row>
     <row r="95" spans="1:27" hidden="1">
       <c r="A95" s="117" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>27</v>
@@ -9229,13 +9301,13 @@
     </row>
     <row r="96" spans="1:27" hidden="1">
       <c r="A96" s="117" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>27</v>
@@ -9280,13 +9352,13 @@
     </row>
     <row r="97" spans="1:27" hidden="1">
       <c r="A97" s="117" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>27</v>
@@ -9331,13 +9403,13 @@
     </row>
     <row r="98" spans="1:27" hidden="1">
       <c r="A98" s="117" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>27</v>
@@ -9382,13 +9454,13 @@
     </row>
     <row r="99" spans="1:27" hidden="1">
       <c r="A99" s="117" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>27</v>
@@ -9433,13 +9505,13 @@
     </row>
     <row r="100" spans="1:27" hidden="1">
       <c r="A100" s="117" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>27</v>
@@ -9484,13 +9556,13 @@
     </row>
     <row r="101" spans="1:27" hidden="1">
       <c r="A101" s="117" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>27</v>
@@ -9535,13 +9607,13 @@
     </row>
     <row r="102" spans="1:27" hidden="1">
       <c r="A102" s="117" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>27</v>
@@ -9586,13 +9658,13 @@
     </row>
     <row r="103" spans="1:27" hidden="1">
       <c r="A103" s="117" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>27</v>
@@ -9637,13 +9709,13 @@
     </row>
     <row r="104" spans="1:27" hidden="1">
       <c r="A104" s="117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>27</v>
@@ -9691,13 +9763,13 @@
     </row>
     <row r="105" spans="1:27" hidden="1">
       <c r="A105" s="117" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>27</v>
@@ -9742,13 +9814,13 @@
     </row>
     <row r="106" spans="1:27" hidden="1">
       <c r="A106" s="117" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>27</v>
@@ -9793,13 +9865,13 @@
     </row>
     <row r="107" spans="1:27" hidden="1">
       <c r="A107" s="117" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>27</v>
@@ -9844,13 +9916,13 @@
     </row>
     <row r="108" spans="1:27" hidden="1">
       <c r="A108" s="117" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>27</v>
@@ -9895,13 +9967,13 @@
     </row>
     <row r="109" spans="1:27" hidden="1">
       <c r="A109" s="117" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>27</v>
@@ -9946,13 +10018,13 @@
     </row>
     <row r="110" spans="1:27" hidden="1">
       <c r="A110" s="117" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>27</v>
@@ -9997,10 +10069,10 @@
     </row>
     <row r="111" spans="1:27" hidden="1">
       <c r="A111" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>53</v>
@@ -10045,13 +10117,13 @@
     </row>
     <row r="112" spans="1:27" hidden="1">
       <c r="A112" s="117" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>27</v>
@@ -10096,13 +10168,13 @@
     </row>
     <row r="113" spans="1:27" hidden="1">
       <c r="A113" s="117" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>27</v>
@@ -10147,13 +10219,13 @@
     </row>
     <row r="114" spans="1:27" hidden="1">
       <c r="A114" s="117" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>27</v>
@@ -10196,12 +10268,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:27">
+    <row r="115" spans="1:27" hidden="1">
       <c r="A115" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>32</v>
@@ -10244,12 +10316,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:27" hidden="1">
+    <row r="116" spans="1:27">
       <c r="A116" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>87</v>
@@ -10266,9 +10338,12 @@
       <c r="P116" s="4">
         <v>100</v>
       </c>
+      <c r="Q116" s="4">
+        <v>100</v>
+      </c>
       <c r="T116" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U116" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D116="Nie",E116="Nie"),0,IF(AND(D116="Tak",E116="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -10276,7 +10351,7 @@
       </c>
       <c r="V116" s="4">
         <f t="shared" si="4"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W116" s="55" t="str">
         <f t="shared" si="5"/>
@@ -10292,9 +10367,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:27" hidden="1">
+    <row r="117" spans="1:27">
       <c r="A117" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>44</v>
@@ -10314,9 +10389,12 @@
       <c r="P117" s="4">
         <v>100</v>
       </c>
+      <c r="Q117" s="4">
+        <v>100</v>
+      </c>
       <c r="T117" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U117" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D117="Nie",E117="Nie"),0,IF(AND(D117="Tak",E117="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -10324,7 +10402,7 @@
       </c>
       <c r="V117" s="4">
         <f t="shared" si="4"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W117" s="55" t="str">
         <f t="shared" si="5"/>
@@ -10340,12 +10418,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:27" hidden="1">
+    <row r="118" spans="1:27">
       <c r="A118" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>87</v>
@@ -10362,9 +10440,12 @@
       <c r="P118" s="4">
         <v>100</v>
       </c>
+      <c r="Q118" s="4">
+        <v>200</v>
+      </c>
       <c r="T118" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U118" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D118="Nie",E118="Nie"),0,IF(AND(D118="Tak",E118="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -10372,7 +10453,7 @@
       </c>
       <c r="V118" s="4">
         <f t="shared" si="4"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W118" s="55" t="str">
         <f t="shared" si="5"/>
@@ -10388,12 +10469,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:27" hidden="1">
+    <row r="119" spans="1:27">
       <c r="A119" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>87</v>
@@ -10410,9 +10491,12 @@
       <c r="P119" s="4">
         <v>100</v>
       </c>
+      <c r="Q119" s="4">
+        <v>100</v>
+      </c>
       <c r="T119" s="4">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U119" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D119="Nie",E119="Nie"),0,IF(AND(D119="Tak",E119="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -10420,7 +10504,7 @@
       </c>
       <c r="V119" s="4">
         <f t="shared" si="4"/>
-        <v>-550</v>
+        <v>-450</v>
       </c>
       <c r="W119" s="55" t="str">
         <f t="shared" si="5"/>
@@ -10436,9 +10520,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:27">
+    <row r="120" spans="1:27" hidden="1">
       <c r="A120" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>73</v>
@@ -10486,10 +10570,10 @@
     </row>
     <row r="121" spans="1:27" hidden="1">
       <c r="A121" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>113</v>
@@ -10501,7 +10585,7 @@
         <v>27</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G121" s="4">
         <v>50</v>
@@ -10532,9 +10616,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:27">
+    <row r="122" spans="1:27" hidden="1">
       <c r="A122" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>57</v>
@@ -10580,7 +10664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:27">
+    <row r="123" spans="1:27" hidden="1">
       <c r="A123" s="4" t="s">
         <v>148</v>
       </c>
@@ -10597,7 +10681,7 @@
         <v>33</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G123" s="4">
         <v>50</v>
@@ -10631,9 +10715,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:27">
+    <row r="124" spans="1:27" hidden="1">
       <c r="A124" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>59</v>
@@ -10648,7 +10732,7 @@
         <v>33</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G124" s="4">
         <v>50</v>
@@ -10682,9 +10766,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:27">
+    <row r="125" spans="1:27" hidden="1">
       <c r="A125" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>131</v>
@@ -10730,12 +10814,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:27">
+    <row r="126" spans="1:27" hidden="1">
       <c r="A126" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>32</v>
@@ -10747,7 +10831,7 @@
         <v>33</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G126" s="4">
         <v>50</v>
@@ -10783,13 +10867,13 @@
     </row>
     <row r="127" spans="1:27" hidden="1">
       <c r="A127" s="117" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>27</v>
@@ -10834,13 +10918,13 @@
     </row>
     <row r="128" spans="1:27" hidden="1">
       <c r="A128" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>27</v>
@@ -10885,13 +10969,13 @@
     </row>
     <row r="129" spans="1:27" hidden="1">
       <c r="A129" s="117" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>27</v>
@@ -10936,13 +11020,13 @@
     </row>
     <row r="130" spans="1:27" hidden="1">
       <c r="A130" s="117" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>27</v>
@@ -10996,7 +11080,7 @@
         <v>73</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>27</v>
@@ -11039,9 +11123,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:27" hidden="1">
+    <row r="132" spans="1:27">
       <c r="A132" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>46</v>
@@ -11061,9 +11145,12 @@
       <c r="P132" s="4">
         <v>100</v>
       </c>
+      <c r="Q132" s="4">
+        <v>100</v>
+      </c>
       <c r="T132" s="4">
         <f t="shared" ref="T132:T165" si="9">SUM(G132:S132)</f>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U132" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D132="Nie",E132="Nie"),0,IF(AND(D132="Tak",E132="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -11071,7 +11158,7 @@
       </c>
       <c r="V132" s="4">
         <f t="shared" si="7"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W132" s="55" t="str">
         <f t="shared" si="8"/>
@@ -11089,13 +11176,13 @@
     </row>
     <row r="133" spans="1:27" hidden="1">
       <c r="A133" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>27</v>
@@ -11140,13 +11227,13 @@
     </row>
     <row r="134" spans="1:27" hidden="1">
       <c r="A134" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>27</v>
@@ -11188,13 +11275,13 @@
     </row>
     <row r="135" spans="1:27" hidden="1">
       <c r="A135" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>27</v>
@@ -11239,13 +11326,13 @@
     </row>
     <row r="136" spans="1:27" hidden="1">
       <c r="A136" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>27</v>
@@ -11287,13 +11374,13 @@
     </row>
     <row r="137" spans="1:27" hidden="1">
       <c r="A137" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>27</v>
@@ -11335,13 +11422,13 @@
     </row>
     <row r="138" spans="1:27" hidden="1">
       <c r="A138" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>27</v>
@@ -11383,13 +11470,13 @@
     </row>
     <row r="139" spans="1:27" hidden="1">
       <c r="A139" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>27</v>
@@ -11434,13 +11521,13 @@
     </row>
     <row r="140" spans="1:27" hidden="1">
       <c r="A140" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>27</v>
@@ -11485,13 +11572,13 @@
     </row>
     <row r="141" spans="1:27" hidden="1">
       <c r="A141" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>27</v>
@@ -11533,13 +11620,13 @@
     </row>
     <row r="142" spans="1:27" hidden="1">
       <c r="A142" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>27</v>
@@ -11581,13 +11668,13 @@
     </row>
     <row r="143" spans="1:27" hidden="1">
       <c r="A143" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>27</v>
@@ -11630,9 +11717,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:27">
+    <row r="144" spans="1:27" hidden="1">
       <c r="A144" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>31</v>
@@ -11680,13 +11767,13 @@
     </row>
     <row r="145" spans="1:27" hidden="1">
       <c r="A145" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>27</v>
@@ -11728,13 +11815,13 @@
     </row>
     <row r="146" spans="1:27" hidden="1">
       <c r="A146" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>27</v>
@@ -11779,13 +11866,13 @@
     </row>
     <row r="147" spans="1:27" hidden="1">
       <c r="A147" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>27</v>
@@ -11830,13 +11917,13 @@
     </row>
     <row r="148" spans="1:27" hidden="1">
       <c r="A148" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>27</v>
@@ -11881,10 +11968,10 @@
         <v>72</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>27</v>
@@ -11927,9 +12014,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:27">
+    <row r="150" spans="1:27" hidden="1">
       <c r="A150" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>29</v>
@@ -11977,13 +12064,13 @@
     </row>
     <row r="151" spans="1:27" hidden="1">
       <c r="A151" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>27</v>
@@ -12026,12 +12113,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:27" hidden="1">
+    <row r="152" spans="1:27">
       <c r="A152" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>87</v>
@@ -12048,9 +12135,12 @@
       <c r="P152" s="4">
         <v>100</v>
       </c>
+      <c r="Q152" s="4">
+        <v>100</v>
+      </c>
       <c r="T152" s="4">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U152" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D152="Nie",E152="Nie"),0,IF(AND(D152="Tak",E152="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -12058,7 +12148,7 @@
       </c>
       <c r="V152" s="4">
         <f t="shared" si="7"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W152" s="55" t="str">
         <f t="shared" si="8"/>
@@ -12076,10 +12166,10 @@
     </row>
     <row r="153" spans="1:27" hidden="1">
       <c r="A153" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>53</v>
@@ -12124,13 +12214,13 @@
     </row>
     <row r="154" spans="1:27" hidden="1">
       <c r="A154" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>27</v>
@@ -12173,12 +12263,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:27">
+    <row r="155" spans="1:27" hidden="1">
       <c r="A155" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>32</v>
@@ -12223,13 +12313,13 @@
     </row>
     <row r="156" spans="1:27" hidden="1">
       <c r="A156" s="117" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>27</v>
@@ -12274,13 +12364,13 @@
     </row>
     <row r="157" spans="1:27" hidden="1">
       <c r="A157" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>33</v>
@@ -12316,13 +12406,13 @@
     </row>
     <row r="158" spans="1:27" hidden="1">
       <c r="A158" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>27</v>
@@ -12362,12 +12452,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:27" hidden="1">
+    <row r="159" spans="1:27">
       <c r="A159" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>87</v>
@@ -12384,9 +12474,12 @@
       <c r="P159" s="4">
         <v>100</v>
       </c>
+      <c r="Q159" s="4">
+        <v>100</v>
+      </c>
       <c r="T159" s="4">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U159" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D159="Nie",E159="Nie"),0,IF(AND(D159="Tak",E159="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -12394,7 +12487,7 @@
       </c>
       <c r="V159" s="4">
         <f t="shared" si="7"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W159" s="55" t="str">
         <f t="shared" si="8"/>
@@ -12412,7 +12505,7 @@
     </row>
     <row r="160" spans="1:27" hidden="1">
       <c r="A160" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>80</v>
@@ -12457,7 +12550,7 @@
     </row>
     <row r="161" spans="1:27" hidden="1">
       <c r="A161" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>37</v>
@@ -12500,12 +12593,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:27" hidden="1">
+    <row r="162" spans="1:27">
       <c r="A162" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>87</v>
@@ -12522,9 +12615,12 @@
       <c r="P162" s="4">
         <v>100</v>
       </c>
+      <c r="Q162" s="4">
+        <v>200</v>
+      </c>
       <c r="T162" s="4">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U162" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D162="Nie",E162="Nie"),0,IF(AND(D162="Tak",E162="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -12532,7 +12628,7 @@
       </c>
       <c r="V162" s="4">
         <f t="shared" si="7"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W162" s="55" t="str">
         <f t="shared" si="8"/>
@@ -12550,7 +12646,7 @@
     </row>
     <row r="163" spans="1:27" hidden="1">
       <c r="A163" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>73</v>
@@ -12598,7 +12694,7 @@
     </row>
     <row r="164" spans="1:27" hidden="1">
       <c r="A164" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>44</v>
@@ -12613,7 +12709,7 @@
         <v>27</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G164" s="4">
         <v>50</v>
@@ -12646,7 +12742,7 @@
     </row>
     <row r="165" spans="1:27" hidden="1">
       <c r="A165" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>29</v>
@@ -12694,10 +12790,10 @@
     </row>
     <row r="166" spans="1:27" hidden="1">
       <c r="A166" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>53</v>
@@ -12742,7 +12838,7 @@
     </row>
     <row r="167" spans="1:27" hidden="1">
       <c r="A167" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>73</v>
@@ -12790,13 +12886,13 @@
     </row>
     <row r="168" spans="1:27" hidden="1">
       <c r="A168" s="117" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>27</v>
@@ -12841,7 +12937,7 @@
     </row>
     <row r="169" spans="1:27" hidden="1">
       <c r="A169" s="111" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>63</v>
@@ -12889,10 +12985,10 @@
     </row>
     <row r="170" spans="1:27" hidden="1">
       <c r="A170" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>26</v>
@@ -12931,10 +13027,10 @@
     </row>
     <row r="171" spans="1:27" hidden="1">
       <c r="A171" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>26</v>
@@ -12946,7 +13042,7 @@
         <v>33</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G171" s="4">
         <v>50</v>
@@ -12979,7 +13075,7 @@
     </row>
     <row r="172" spans="1:27" hidden="1">
       <c r="A172" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>57</v>
@@ -13024,13 +13120,13 @@
     </row>
     <row r="173" spans="1:27" hidden="1">
       <c r="A173" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>27</v>
@@ -13078,10 +13174,10 @@
     </row>
     <row r="174" spans="1:27" hidden="1">
       <c r="A174" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>53</v>
@@ -13121,9 +13217,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:27" hidden="1">
+    <row r="175" spans="1:27">
       <c r="A175" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>107</v>
@@ -13143,9 +13239,12 @@
       <c r="P175" s="4">
         <v>100</v>
       </c>
+      <c r="Q175" s="4">
+        <v>100</v>
+      </c>
       <c r="T175" s="4">
         <f t="shared" si="10"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U175" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D175="Nie",E175="Nie"),0,IF(AND(D175="Tak",E175="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -13153,7 +13252,7 @@
       </c>
       <c r="V175" s="4">
         <f t="shared" si="7"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W175" s="55" t="str">
         <f t="shared" si="8"/>
@@ -13171,7 +13270,7 @@
     </row>
     <row r="176" spans="1:27" hidden="1">
       <c r="A176" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>107</v>
@@ -13214,12 +13313,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:27" hidden="1">
+    <row r="177" spans="1:27">
       <c r="A177" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>87</v>
@@ -13236,9 +13335,12 @@
       <c r="P177" s="4">
         <v>100</v>
       </c>
+      <c r="Q177" s="4">
+        <v>100</v>
+      </c>
       <c r="T177" s="4">
         <f t="shared" si="10"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U177" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D177="Nie",E177="Nie"),0,IF(AND(D177="Tak",E177="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -13246,7 +13348,7 @@
       </c>
       <c r="V177" s="4">
         <f t="shared" si="7"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W177" s="55" t="str">
         <f t="shared" si="8"/>
@@ -13264,7 +13366,7 @@
     </row>
     <row r="178" spans="1:27" hidden="1">
       <c r="A178" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>65</v>
@@ -13309,7 +13411,7 @@
     </row>
     <row r="179" spans="1:27" hidden="1">
       <c r="A179" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>78</v>
@@ -13354,10 +13456,10 @@
     </row>
     <row r="180" spans="1:27" hidden="1">
       <c r="A180" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>26</v>
@@ -13402,7 +13504,7 @@
         <v>91</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>26</v>
@@ -13444,13 +13546,13 @@
     </row>
     <row r="182" spans="1:27" hidden="1">
       <c r="A182" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>27</v>
@@ -13495,13 +13597,13 @@
     </row>
     <row r="183" spans="1:27" hidden="1">
       <c r="A183" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>33</v>
@@ -13537,13 +13639,13 @@
     </row>
     <row r="184" spans="1:27" hidden="1">
       <c r="A184" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>27</v>
@@ -13588,13 +13690,13 @@
     </row>
     <row r="185" spans="1:27" hidden="1">
       <c r="A185" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>27</v>
@@ -13639,7 +13741,7 @@
         <v>112</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>26</v>
@@ -13681,7 +13783,7 @@
     </row>
     <row r="187" spans="1:27" hidden="1">
       <c r="A187" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>73</v>
@@ -13726,10 +13828,10 @@
     </row>
     <row r="188" spans="1:27" hidden="1">
       <c r="A188" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>26</v>
@@ -13771,7 +13873,7 @@
     </row>
     <row r="189" spans="1:27" hidden="1">
       <c r="A189" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>35</v>
@@ -13816,7 +13918,7 @@
     </row>
     <row r="190" spans="1:27" hidden="1">
       <c r="A190" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>46</v>
@@ -13861,10 +13963,10 @@
     </row>
     <row r="191" spans="1:27" hidden="1">
       <c r="A191" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>26</v>
@@ -13906,7 +14008,7 @@
     </row>
     <row r="192" spans="1:27" hidden="1">
       <c r="A192" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>52</v>
@@ -13954,13 +14056,13 @@
     </row>
     <row r="193" spans="1:27" hidden="1">
       <c r="A193" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>27</v>
@@ -14005,10 +14107,10 @@
     </row>
     <row r="194" spans="1:27" hidden="1">
       <c r="A194" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>26</v>
@@ -14050,10 +14152,10 @@
     </row>
     <row r="195" spans="1:27" hidden="1">
       <c r="A195" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>26</v>
@@ -14095,13 +14197,13 @@
     </row>
     <row r="196" spans="1:27" hidden="1">
       <c r="A196" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>27</v>
@@ -14143,13 +14245,13 @@
     </row>
     <row r="197" spans="1:27" hidden="1">
       <c r="A197" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>27</v>
@@ -14194,7 +14296,7 @@
     </row>
     <row r="198" spans="1:27" hidden="1">
       <c r="A198" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>67</v>
@@ -14239,10 +14341,10 @@
     </row>
     <row r="199" spans="1:27" hidden="1">
       <c r="A199" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>26</v>
@@ -14284,13 +14386,13 @@
     </row>
     <row r="200" spans="1:27" hidden="1">
       <c r="A200" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>27</v>
@@ -14341,7 +14443,7 @@
         <v>78</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>27</v>
@@ -14381,12 +14483,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:27">
+    <row r="202" spans="1:27" hidden="1">
       <c r="A202" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>32</v>
@@ -14429,12 +14531,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:27">
+    <row r="203" spans="1:27" hidden="1">
       <c r="A203" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>32</v>
@@ -14477,12 +14579,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:27">
+    <row r="204" spans="1:27" hidden="1">
       <c r="A204" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>32</v>
@@ -14525,12 +14627,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:27">
+    <row r="205" spans="1:27" hidden="1">
       <c r="A205" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>32</v>
@@ -14573,9 +14675,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:27">
+    <row r="206" spans="1:27" hidden="1">
       <c r="A206" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>127</v>
@@ -14621,9 +14723,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:27">
+    <row r="207" spans="1:27" hidden="1">
       <c r="A207" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>78</v>
@@ -14666,9 +14768,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:27" hidden="1">
+    <row r="208" spans="1:27">
       <c r="A208" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>78</v>
@@ -14683,7 +14785,7 @@
         <v>33</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G208" s="4">
         <v>50</v>
@@ -14691,9 +14793,12 @@
       <c r="P208" s="4">
         <v>100</v>
       </c>
+      <c r="Q208" s="4">
+        <v>100</v>
+      </c>
       <c r="T208" s="4">
         <f t="shared" si="13"/>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U208" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D208="Nie",E208="Nie"),0,IF(AND(D208="Tak",E208="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -14701,7 +14806,7 @@
       </c>
       <c r="V208" s="4">
         <f t="shared" si="11"/>
-        <v>-280</v>
+        <v>-180</v>
       </c>
       <c r="W208" s="55" t="str">
         <f t="shared" si="12"/>
@@ -14717,12 +14822,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:27">
+    <row r="209" spans="1:27" hidden="1">
       <c r="A209" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>32</v>
@@ -14734,7 +14839,7 @@
         <v>33</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G209" s="4">
         <v>50</v>
@@ -14770,7 +14875,7 @@
     </row>
     <row r="210" spans="1:27" hidden="1">
       <c r="A210" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>35</v>
@@ -14815,10 +14920,10 @@
     </row>
     <row r="211" spans="1:27" hidden="1">
       <c r="A211" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>113</v>
@@ -14860,13 +14965,13 @@
     </row>
     <row r="212" spans="1:27" hidden="1">
       <c r="A212" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>27</v>
@@ -14905,13 +15010,13 @@
     </row>
     <row r="213" spans="1:27" hidden="1">
       <c r="A213" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B213" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>27</v>
@@ -14956,13 +15061,13 @@
     </row>
     <row r="214" spans="1:27" hidden="1">
       <c r="A214" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>27</v>
@@ -15007,7 +15112,7 @@
     </row>
     <row r="215" spans="1:27" hidden="1">
       <c r="A215" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>57</v>
@@ -15050,9 +15155,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:27">
+    <row r="216" spans="1:27" hidden="1">
       <c r="A216" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>31</v>
@@ -15098,9 +15203,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:27">
+    <row r="217" spans="1:27" hidden="1">
       <c r="A217" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>80</v>
@@ -15148,13 +15253,13 @@
     </row>
     <row r="218" spans="1:27" hidden="1">
       <c r="A218" s="117" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>27</v>
@@ -15199,13 +15304,13 @@
     </row>
     <row r="219" spans="1:27" hidden="1">
       <c r="A219" s="117" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>27</v>
@@ -15248,12 +15353,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:27" hidden="1">
+    <row r="220" spans="1:27">
       <c r="A220" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>87</v>
@@ -15270,9 +15375,12 @@
       <c r="P220" s="4">
         <v>100</v>
       </c>
+      <c r="Q220" s="4">
+        <v>200</v>
+      </c>
       <c r="T220" s="4">
         <f t="shared" si="13"/>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="U220" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D220="Nie",E220="Nie"),0,IF(AND(D220="Tak",E220="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -15280,7 +15388,7 @@
       </c>
       <c r="V220" s="4">
         <f t="shared" si="11"/>
-        <v>-550</v>
+        <v>-350</v>
       </c>
       <c r="W220" s="55" t="str">
         <f t="shared" si="12"/>
@@ -15296,12 +15404,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:27">
+    <row r="221" spans="1:27" hidden="1">
       <c r="A221" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>32</v>
@@ -15346,13 +15454,13 @@
     </row>
     <row r="222" spans="1:27" hidden="1">
       <c r="A222" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B222" s="4" t="s">
         <v>100</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>27</v>
@@ -15395,12 +15503,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:27" hidden="1">
+    <row r="223" spans="1:27">
       <c r="A223" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>87</v>
@@ -15414,9 +15522,12 @@
       <c r="G223" s="4">
         <v>50</v>
       </c>
+      <c r="Q223" s="4">
+        <v>200</v>
+      </c>
       <c r="T223" s="4">
         <f t="shared" si="13"/>
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="U223" s="36">
         <f>IF(Table2[[#This Row],[Nazwisko]]="","",IF(AND(D223="Nie",E223="Nie"),0,IF(AND(D223="Tak",E223="Nie"),Podsumowanie!$B$19,Podsumowanie!$C$19)))</f>
@@ -15424,7 +15535,7 @@
       </c>
       <c r="V223" s="4">
         <f t="shared" si="11"/>
-        <v>-650</v>
+        <v>-450</v>
       </c>
       <c r="W223" s="55" t="str">
         <f t="shared" si="12"/>
@@ -15442,13 +15553,13 @@
     </row>
     <row r="224" spans="1:27" hidden="1">
       <c r="A224" s="117" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>27</v>
@@ -15491,12 +15602,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:27" hidden="1">
+    <row r="225" spans="1:27">
       <c r="A225" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>87</v>
@@ -19455,88 +19566,88 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="4" spans="2:3">
-      <c r="B4" s="133" t="s">
+      <c r="B4" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="133" t="s">
+      <c r="C4" s="124" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="5" spans="2:3">
-      <c r="B5" s="133" t="s">
+      <c r="B5" s="124" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5" s="124" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" s="124" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="124" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" s="124" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="124" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" s="124" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="124" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9" s="124" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="124" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10" s="124" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" s="124" t="s">
         <v>328</v>
       </c>
-      <c r="C5" s="133" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
-      <c r="B6" s="133" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="133" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3">
-      <c r="B7" s="133" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="133" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="B8" s="133" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="133" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" s="133" t="s">
-        <v>342</v>
-      </c>
-      <c r="C9" s="133" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3">
-      <c r="B10" s="133" t="s">
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11" s="124" t="s">
         <v>326</v>
       </c>
-      <c r="C10" s="133" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="B11" s="133" t="s">
-        <v>325</v>
-      </c>
-      <c r="C11" s="133" t="s">
-        <v>314</v>
+      <c r="C11" s="124" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="2:3">
-      <c r="B12" s="133" t="s">
+      <c r="B12" s="124" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="133" t="s">
+      <c r="C12" s="124" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="13" spans="2:3">
-      <c r="B13" s="133" t="s">
-        <v>219</v>
-      </c>
-      <c r="C13" s="133" t="s">
+      <c r="B13" s="124" t="s">
         <v>220</v>
+      </c>
+      <c r="C13" s="124" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="B14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -19551,10 +19662,10 @@
       </c>
     </row>
     <row r="16" spans="2:3">
-      <c r="B16" s="133" t="s">
-        <v>228</v>
-      </c>
-      <c r="C16" s="133" t="s">
+      <c r="B16" s="124" t="s">
+        <v>229</v>
+      </c>
+      <c r="C16" s="124" t="s">
         <v>73</v>
       </c>
     </row>
@@ -19568,7 +19679,7 @@
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C18" t="s">
         <v>57</v>
@@ -19584,15 +19695,15 @@
     </row>
     <row r="20" spans="2:3">
       <c r="B20" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C21" t="s">
         <v>29</v>
@@ -19608,7 +19719,7 @@
     </row>
     <row r="23" spans="2:3">
       <c r="B23" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C23" t="s">
         <v>78</v>
@@ -19616,15 +19727,15 @@
     </row>
     <row r="24" spans="2:3">
       <c r="B24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="B25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" t="s">
         <v>59</v>
@@ -19632,10 +19743,10 @@
     </row>
     <row r="26" spans="2:3">
       <c r="B26" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C26" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="2:3">
@@ -19648,7 +19759,7 @@
     </row>
     <row r="28" spans="2:3">
       <c r="B28" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C28" t="s">
         <v>80</v>
@@ -19680,15 +19791,15 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C32" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C33" t="s">
         <v>127</v>
@@ -19696,7 +19807,7 @@
     </row>
     <row r="34" spans="2:3">
       <c r="B34" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C34" t="s">
         <v>131</v>
@@ -19712,10 +19823,10 @@
     </row>
     <row r="36" spans="2:3">
       <c r="B36" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C36" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="2:3">
@@ -19775,28 +19886,28 @@
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="29.25">
       <c r="A2" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>23</v>
@@ -19804,7 +19915,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="58" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B3" s="32" t="b">
         <v>1</v>
@@ -19814,29 +19925,29 @@
       </c>
       <c r="D3" s="33">
         <f>Podsumowanie!C12</f>
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E3" s="88">
         <v>270</v>
       </c>
       <c r="F3" s="88">
         <f>Table1[[#This Row],[Ilość]]*Table1[[#This Row],[Cena]]</f>
-        <v>98280</v>
+        <v>98010</v>
       </c>
       <c r="G3" s="88">
         <v>2000</v>
       </c>
       <c r="H3" s="88">
         <f>Table1[[#This Row],[Koszt]]-Table1[[#This Row],[Zaliczka]]</f>
-        <v>96280</v>
+        <v>96010</v>
       </c>
       <c r="I3" s="122" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="43.5">
       <c r="A4" s="44" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B4" s="43" t="b">
         <v>1</v>
@@ -19863,7 +19974,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="58" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B5" s="32" t="b">
         <v>1</v>
@@ -19889,12 +20000,12 @@
         <v>7600</v>
       </c>
       <c r="I5" s="122" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="58" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B6" s="32" t="b">
         <v>1</v>
@@ -19920,12 +20031,12 @@
         <v>10000</v>
       </c>
       <c r="I6" s="122" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="58" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B7" s="32" t="b">
         <v>1</v>
@@ -19951,12 +20062,12 @@
         <v>1300</v>
       </c>
       <c r="I7" s="122" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B8" s="32" t="b">
         <v>0</v>
@@ -19981,7 +20092,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B9" s="32" t="b">
         <v>0</v>
@@ -20006,7 +20117,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B10" s="32" t="b">
         <v>0</v>
@@ -20014,25 +20125,25 @@
       <c r="C10" s="32"/>
       <c r="D10" s="33">
         <f>(D3+D4)*1.1</f>
-        <v>433.40000000000003</v>
+        <v>432.3</v>
       </c>
       <c r="E10" s="88">
         <v>7.5</v>
       </c>
       <c r="F10" s="88">
         <f>Table1[[#This Row],[Ilość]]*Table1[[#This Row],[Cena]]</f>
-        <v>3250.5000000000005</v>
+        <v>3242.25</v>
       </c>
       <c r="G10" s="88"/>
       <c r="H10" s="88">
         <f>Table1[[#This Row],[Koszt]]-Table1[[#This Row],[Zaliczka]]</f>
-        <v>3250.5000000000005</v>
+        <v>3242.25</v>
       </c>
       <c r="I10" s="122"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B11" s="32" t="b">
         <v>0</v>
@@ -20057,7 +20168,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B12" s="32" t="b">
         <v>1</v>
@@ -20083,12 +20194,12 @@
         <v>1620</v>
       </c>
       <c r="I12" s="122" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B13" s="32" t="b">
         <v>0</v>
@@ -20115,12 +20226,12 @@
         <v>2144.15</v>
       </c>
       <c r="I13" s="122" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -20128,7 +20239,7 @@
       <c r="E14" s="35"/>
       <c r="F14" s="34">
         <f>SUBTOTAL(109,F3:F13)</f>
-        <v>130090.5</v>
+        <v>129812.25</v>
       </c>
       <c r="G14" s="34">
         <f>SUBTOTAL(109,G3:G13)</f>
@@ -20136,7 +20247,7 @@
       </c>
       <c r="H14" s="34">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>125334.65</v>
+        <v>125056.4</v>
       </c>
       <c r="I14" s="35"/>
     </row>
@@ -20178,35 +20289,35 @@
   <sheetData>
     <row r="1" spans="1:22" ht="33" customHeight="1">
       <c r="A1" s="22" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1" s="65" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1" s="92" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F1" s="92" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G1" s="92" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1" s="92" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I1" s="92"/>
       <c r="J1" s="93" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K1" s="93" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L1" s="93" t="s">
         <v>21</v>
@@ -20217,7 +20328,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B2" s="38">
         <f>COUNTIFS('Lista uczniów_składki'!D:D,"Tak",'Lista uczniów_składki'!C:C,Podsumowanie!A2)</f>
@@ -20231,7 +20342,7 @@
         <f>SUM(B2:C2)</f>
         <v>62</v>
       </c>
-      <c r="E2" s="124">
+      <c r="E2" s="125">
         <v>35</v>
       </c>
       <c r="F2" s="46">
@@ -20279,7 +20390,7 @@
         <f>SUM(B3:C3)</f>
         <v>40</v>
       </c>
-      <c r="E3" s="124">
+      <c r="E3" s="125">
         <v>25</v>
       </c>
       <c r="F3" s="46">
@@ -20321,13 +20432,13 @@
       </c>
       <c r="C4" s="40">
         <f>COUNTIFS('Lista uczniów_składki'!E:E,"Tak",'Lista uczniów_składki'!C:C,Podsumowanie!A4)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="38">
         <f t="shared" ref="D4:D8" si="3">SUM(B4:C4)</f>
-        <v>55</v>
-      </c>
-      <c r="E4" s="124">
+        <v>54</v>
+      </c>
+      <c r="E4" s="125">
         <v>36</v>
       </c>
       <c r="F4" s="46">
@@ -20345,15 +20456,15 @@
       <c r="I4" s="60"/>
       <c r="J4" s="91">
         <f>SUMIFS('Lista uczniów_składki'!U:U,'Lista uczniów_składki'!C:C,Podsumowanie!A4)</f>
-        <v>20450</v>
+        <v>20180</v>
       </c>
       <c r="K4" s="91">
         <f>SUMIFS('Lista uczniów_składki'!T:T,'Lista uczniów_składki'!C:C,Podsumowanie!A4)</f>
-        <v>5100</v>
+        <v>10100</v>
       </c>
       <c r="L4" s="91">
         <f t="shared" si="2"/>
-        <v>-15350</v>
+        <v>-10080</v>
       </c>
       <c r="T4" s="63"/>
       <c r="U4" s="90"/>
@@ -20361,7 +20472,7 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B5" s="38">
         <f>COUNTIFS('Lista uczniów_składki'!D:D,"Tak",'Lista uczniów_składki'!C:C,Podsumowanie!A5)</f>
@@ -20375,7 +20486,7 @@
         <f t="shared" si="3"/>
         <v>59</v>
       </c>
-      <c r="E5" s="124">
+      <c r="E5" s="125">
         <v>35</v>
       </c>
       <c r="F5" s="46">
@@ -20423,7 +20534,7 @@
         <f t="shared" si="3"/>
         <v>49</v>
       </c>
-      <c r="E6" s="124">
+      <c r="E6" s="125">
         <v>36</v>
       </c>
       <c r="F6" s="46">
@@ -20471,7 +20582,7 @@
         <f t="shared" si="3"/>
         <v>57</v>
       </c>
-      <c r="E7" s="124">
+      <c r="E7" s="125">
         <v>36</v>
       </c>
       <c r="F7" s="46">
@@ -20519,7 +20630,7 @@
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="E8" s="124">
+      <c r="E8" s="125">
         <v>30</v>
       </c>
       <c r="F8" s="46">
@@ -20555,61 +20666,61 @@
       <c r="E9" s="63"/>
       <c r="J9" s="91">
         <f>SUM(J2:J8)</f>
-        <v>133800</v>
+        <v>133530</v>
       </c>
       <c r="K9" s="91">
         <f t="shared" ref="K9:L9" si="4">SUM(K2:K8)</f>
-        <v>40050</v>
+        <v>45050</v>
       </c>
       <c r="L9" s="91">
         <f t="shared" si="4"/>
-        <v>-93750</v>
+        <v>-88480</v>
       </c>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="125" t="s">
-        <v>386</v>
-      </c>
-      <c r="B11" s="125"/>
+      <c r="A11" s="126" t="s">
+        <v>387</v>
+      </c>
+      <c r="B11" s="126"/>
       <c r="E11" s="63"/>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="28" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B12" s="16">
         <f>SUM(B2:B8)</f>
         <v>222</v>
       </c>
-      <c r="C12" s="126">
+      <c r="C12" s="127">
         <f>SUM(B12:B13)</f>
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E12" s="63"/>
     </row>
     <row r="13" spans="1:22" s="8" customFormat="1">
       <c r="A13" s="29" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B13" s="17">
         <f>SUM(C2:C8)</f>
-        <v>142</v>
-      </c>
-      <c r="C13" s="127"/>
+        <v>141</v>
+      </c>
+      <c r="C13" s="128"/>
       <c r="E13" s="63"/>
       <c r="H13" s="61"/>
       <c r="I13" s="61"/>
     </row>
     <row r="14" spans="1:22" s="27" customFormat="1" ht="27.75">
       <c r="A14" s="30" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B14" s="87">
         <f>Wydatki!D4</f>
         <v>30</v>
       </c>
-      <c r="C14" s="124" t="s">
-        <v>390</v>
+      <c r="C14" s="125" t="s">
+        <v>391</v>
       </c>
       <c r="D14" s="63"/>
       <c r="E14" s="63"/>
@@ -20633,21 +20744,21 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="29" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B15" s="12">
         <f>SUM(Wydatki!F3:F4)</f>
-        <v>98280</v>
+        <v>98010</v>
       </c>
       <c r="E15" s="63"/>
     </row>
     <row r="16" spans="1:22" s="8" customFormat="1">
       <c r="A16" s="29" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B16" s="13">
         <f>SUM(Wydatki!F5:F13)</f>
-        <v>31810.5</v>
+        <v>31802.25</v>
       </c>
       <c r="E16" s="63"/>
       <c r="H16" s="61"/>
@@ -20655,11 +20766,11 @@
     </row>
     <row r="17" spans="1:9" s="8" customFormat="1">
       <c r="A17" s="31" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B17" s="14">
         <f>SUM(B15:B16)</f>
-        <v>130090.5</v>
+        <v>129812.25</v>
       </c>
       <c r="E17" s="63"/>
       <c r="H17" s="61"/>
@@ -20674,12 +20785,12 @@
     </row>
     <row r="19" spans="1:9" s="8" customFormat="1">
       <c r="A19" s="109" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B19" s="64">
         <v>430</v>
       </c>
-      <c r="C19" s="128">
+      <c r="C19" s="129">
         <f>B19+B20</f>
         <v>700</v>
       </c>
@@ -20689,13 +20800,13 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="59" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B20" s="110">
         <f>Wydatki!E3</f>
         <v>270</v>
       </c>
-      <c r="C20" s="128"/>
+      <c r="C20" s="129"/>
       <c r="E20" s="63"/>
     </row>
     <row r="21" spans="1:9" ht="6.75" customHeight="1">
@@ -20703,50 +20814,50 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="19" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B22" s="11">
         <f>B19*B12+B20*B13</f>
-        <v>133800</v>
+        <v>133530</v>
       </c>
       <c r="E22" s="108"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="20" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B23" s="12">
         <f>SUM(Table1[Koszt])</f>
-        <v>130090.5</v>
+        <v>129812.25</v>
       </c>
       <c r="E23" s="63"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="21" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B24" s="15">
         <f>B22-B23</f>
-        <v>3709.5</v>
+        <v>3717.75</v>
       </c>
       <c r="E24" s="63"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="22" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E26" s="63"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B27" s="18">
         <f>IF(B2=0,"",B$24/SUM($B$3:$B$8)*B2)</f>
-        <v>647.69047619047615</v>
+        <v>649.13095238095241</v>
       </c>
       <c r="E27" s="63"/>
     </row>
@@ -20756,7 +20867,7 @@
       </c>
       <c r="B28" s="18">
         <f>IF(B3=0,"",B$24/SUM($B$3:$B$8)*B3)</f>
-        <v>471.04761904761904</v>
+        <v>472.09523809523807</v>
       </c>
       <c r="E28" s="45"/>
       <c r="H28" s="62"/>
@@ -20768,17 +20879,17 @@
       </c>
       <c r="B29" s="18">
         <f>IF(B4=0,"",B$24/SUM($B$3:$B$8)*B4)</f>
-        <v>686.94444444444446</v>
+        <v>688.47222222222229</v>
       </c>
       <c r="E29" s="63"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B30" s="18">
         <f>IF(B5=0,"",B$24/SUM($B$3:$B$8)*B5)</f>
-        <v>686.94444444444446</v>
+        <v>688.47222222222229</v>
       </c>
       <c r="E30" s="63"/>
     </row>
@@ -20788,7 +20899,7 @@
       </c>
       <c r="B31" s="18">
         <f>IF(B6=0,"",B$24/SUM($B$3:$B$8)*B6)</f>
-        <v>686.94444444444446</v>
+        <v>688.47222222222229</v>
       </c>
       <c r="E31" s="63"/>
     </row>
@@ -20798,7 +20909,7 @@
       </c>
       <c r="B32" s="18">
         <f>IF(B7=0,"",B$24/SUM($B$3:$B$8)*B7)</f>
-        <v>667.31746031746025</v>
+        <v>668.80158730158735</v>
       </c>
       <c r="E32" s="63"/>
     </row>
@@ -20808,7 +20919,7 @@
       </c>
       <c r="B33" s="18">
         <f>IF(B8=0,"",B$24/SUM($B$3:$B$8)*B8)</f>
-        <v>510.30158730158729</v>
+        <v>511.43650793650795</v>
       </c>
       <c r="E33" s="63"/>
     </row>
@@ -20861,13 +20972,13 @@
   <sheetData>
     <row r="4" spans="1:5">
       <c r="C4" s="85" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D4" s="67"/>
     </row>
     <row r="5" spans="1:5">
       <c r="C5" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D5" s="68">
         <f>SUM(Podsumowanie!E2:E8)</f>
@@ -20876,7 +20987,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="C6" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D6" s="68">
         <f>SUM(Podsumowanie!B2:B8)</f>
@@ -20885,49 +20996,49 @@
     </row>
     <row r="7" spans="1:5">
       <c r="C7" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D7" s="68">
         <f>SUM(Podsumowanie!C2:C8)</f>
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="C8" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D8" s="68">
         <f>D6+D7</f>
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A9" s="130" t="s">
-        <v>405</v>
-      </c>
-      <c r="B9" s="131" t="s">
-        <v>359</v>
+      <c r="A9" s="131" t="s">
+        <v>406</v>
+      </c>
+      <c r="B9" s="132" t="s">
+        <v>360</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D9" s="106">
         <f>Podsumowanie!B14</f>
         <v>30</v>
       </c>
       <c r="E9" s="105" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="130"/>
-      <c r="B10" s="131"/>
+      <c r="A10" s="131"/>
+      <c r="B10" s="132"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
-      <c r="A11" s="130"/>
-      <c r="B11" s="131"/>
+      <c r="A11" s="131"/>
+      <c r="B11" s="132"/>
       <c r="C11" s="85" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D11" s="67"/>
     </row>
@@ -20939,14 +21050,14 @@
         <v>1</v>
       </c>
       <c r="C12" s="70" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D12" s="71">
         <f>Wydatki!F3</f>
-        <v>98280</v>
+        <v>98010</v>
       </c>
       <c r="E12" s="115" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.5">
@@ -20957,7 +21068,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="72" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D13" s="76">
         <f>Wydatki!F4</f>
@@ -20973,14 +21084,14 @@
         <v>1</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D14" s="71">
         <f>Wydatki!F5</f>
         <v>8000</v>
       </c>
       <c r="E14" s="115" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -20991,14 +21102,14 @@
         <v>1</v>
       </c>
       <c r="C15" s="70" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D15" s="71">
         <f>Wydatki!F6</f>
         <v>12000</v>
       </c>
       <c r="E15" s="105" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -21009,14 +21120,14 @@
         <v>1</v>
       </c>
       <c r="C16" s="70" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D16" s="71">
         <f>Wydatki!F7</f>
         <v>1400</v>
       </c>
       <c r="E16" s="115" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -21027,7 +21138,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D17" s="71">
         <f>Wydatki!F8</f>
@@ -21043,7 +21154,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D18" s="71">
         <f>Wydatki!F9</f>
@@ -21059,11 +21170,11 @@
         <v>0</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D19" s="71">
         <f>Wydatki!F10</f>
-        <v>3250.5000000000005</v>
+        <v>3242.25</v>
       </c>
       <c r="E19" s="115"/>
     </row>
@@ -21075,7 +21186,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="73" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D20" s="71">
         <f>Wydatki!F11</f>
@@ -21091,14 +21202,14 @@
         <v>1</v>
       </c>
       <c r="C21" s="73" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D21" s="71">
         <f>Wydatki!F12</f>
         <v>1800</v>
       </c>
       <c r="E21" s="115" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="26.25">
@@ -21109,7 +21220,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="104" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D22" s="107">
         <f>Wydatki!F13</f>
@@ -21119,48 +21230,48 @@
     </row>
     <row r="23" spans="1:6" ht="18.75">
       <c r="C23" s="74" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D23" s="75">
         <f>Wydatki!F14</f>
-        <v>130090.5</v>
+        <v>129812.25</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="C26" s="66" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D26" s="67"/>
     </row>
     <row r="27" spans="1:6" ht="16.5">
       <c r="C27" s="79" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D27" s="78">
         <f>Podsumowanie!B19</f>
         <v>430</v>
       </c>
-      <c r="E27" s="129">
+      <c r="E27" s="130">
         <f>SUM(D27:D28)</f>
         <v>700</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16.5">
       <c r="C28" s="79" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D28" s="78">
         <f>Podsumowanie!B20</f>
         <v>270</v>
       </c>
-      <c r="E28" s="129"/>
+      <c r="E28" s="130"/>
     </row>
     <row r="30" spans="1:6">
       <c r="C30" s="116"/>
     </row>
     <row r="31" spans="1:6">
       <c r="C31" s="102" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D31" s="67"/>
       <c r="E31" s="67"/>
@@ -21171,10 +21282,10 @@
         <v>2</v>
       </c>
       <c r="D32" s="97" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E32" s="97" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F32" s="97" t="s">
         <v>21</v>
@@ -21182,7 +21293,7 @@
     </row>
     <row r="33" spans="3:6">
       <c r="C33" s="99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D33" s="95">
         <f>SUMIFS('Lista uczniów_składki'!U:U,'Lista uczniów_składki'!C:C,'Do wiadomości rodziców'!C33)</f>
@@ -21220,20 +21331,20 @@
       </c>
       <c r="D35" s="95">
         <f>SUMIFS('Lista uczniów_składki'!U:U,'Lista uczniów_składki'!C:C,'Do wiadomości rodziców'!C35)</f>
-        <v>20450</v>
+        <v>20180</v>
       </c>
       <c r="E35" s="96">
         <f>SUMIFS('Lista uczniów_składki'!T:T,'Lista uczniów_składki'!C:C,'Do wiadomości rodziców'!C35)</f>
-        <v>5100</v>
+        <v>10100</v>
       </c>
       <c r="F35" s="91">
         <f t="shared" si="0"/>
-        <v>-15350</v>
+        <v>-10080</v>
       </c>
     </row>
     <row r="36" spans="3:6">
       <c r="C36" s="101" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D36" s="95">
         <f>SUMIFS('Lista uczniów_składki'!U:U,'Lista uczniów_składki'!C:C,'Do wiadomości rodziców'!C36)</f>
@@ -21301,19 +21412,19 @@
     </row>
     <row r="40" spans="3:6">
       <c r="C40" s="103" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D40" s="121">
         <f>SUBTOTAL(109,D33:D39)</f>
-        <v>133800</v>
+        <v>133530</v>
       </c>
       <c r="E40" s="121">
         <f>SUBTOTAL(109,E33:E39)</f>
-        <v>40050</v>
+        <v>45050</v>
       </c>
       <c r="F40" s="121">
         <f>SUBTOTAL(109,Table5[Delta])</f>
-        <v>-93750</v>
+        <v>-88480</v>
       </c>
     </row>
     <row r="41" spans="3:6">
@@ -21329,11 +21440,11 @@
       <c r="F42" s="77"/>
     </row>
     <row r="44" spans="3:6">
-      <c r="C44" s="132" t="s">
-        <v>420</v>
-      </c>
-      <c r="D44" s="132"/>
-      <c r="E44" s="132"/>
+      <c r="C44" s="133" t="s">
+        <v>421</v>
+      </c>
+      <c r="D44" s="133"/>
+      <c r="E44" s="133"/>
       <c r="F44" s="120">
         <f>SUM(F46:F52)</f>
         <v>14420</v>
@@ -21341,21 +21452,21 @@
     </row>
     <row r="45" spans="3:6">
       <c r="C45" s="118" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D45" s="119" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E45" s="119" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F45" s="119" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="46" spans="3:6">
       <c r="C46" s="123" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D46" s="71">
         <v>5750</v>
@@ -21370,7 +21481,7 @@
     </row>
     <row r="47" spans="3:6">
       <c r="C47" s="123" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D47" s="71">
         <v>7350</v>
@@ -21385,7 +21496,7 @@
     </row>
     <row r="48" spans="3:6">
       <c r="C48" s="123" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D48" s="71">
         <v>6000</v>
@@ -21457,27 +21568,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B2" s="114">
         <v>46275</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D2" s="43" t="b">
         <v>1</v>
@@ -21485,13 +21596,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B3" s="114">
         <v>46401</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D3" s="43" t="b">
         <v>0</v>
@@ -21499,13 +21610,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B4" s="114">
         <v>46395</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D4" s="43" t="b">
         <v>0</v>
@@ -21513,13 +21624,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B5" s="114">
         <v>46254</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D5" s="43" t="b">
         <v>0</v>
@@ -21527,13 +21638,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B6" s="114">
         <v>46412</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D6" s="43" t="b">
         <v>0</v>
@@ -21541,13 +21652,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B7" s="114">
         <v>46185</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D7" s="43" t="b">
         <v>1</v>
@@ -21555,13 +21666,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B8" s="114">
         <v>46192</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D8" s="43" t="b">
         <v>1</v>
@@ -21569,13 +21680,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B9" s="114">
         <v>46192</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D9" s="43" t="b">
         <v>0</v>
@@ -21583,13 +21694,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B10" s="114">
         <v>46267</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D10" s="43" t="b">
         <v>0</v>
@@ -21597,13 +21708,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B11" s="114">
         <v>46356</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D11" s="43" t="b">
         <v>0</v>
@@ -21682,24 +21793,24 @@
   <sheetData>
     <row r="3" spans="2:4">
       <c r="B3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C3">
         <v>5750</v>
       </c>
       <c r="D3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C4">
         <v>500</v>
       </c>
       <c r="D4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -21734,53 +21845,53 @@
   <sheetData>
     <row r="5" spans="1:41">
       <c r="AC5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:41">
       <c r="AC6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AD6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AE6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AF6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG6" t="s">
         <v>23</v>
       </c>
       <c r="AN6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
@@ -21795,7 +21906,7 @@
       </c>
       <c r="AD7" s="91">
         <f>Wydatki!F3</f>
-        <v>98280</v>
+        <v>98010</v>
       </c>
       <c r="AE7" s="91">
         <f>Wydatki!G3</f>
@@ -21803,7 +21914,7 @@
       </c>
       <c r="AF7" s="91">
         <f>Wydatki!H3</f>
-        <v>96280</v>
+        <v>96010</v>
       </c>
       <c r="AG7" t="str">
         <f>Wydatki!I3</f>
@@ -21815,7 +21926,7 @@
       </c>
       <c r="AO7" s="91">
         <f>Podsumowanie!B27</f>
-        <v>647.69047619047615</v>
+        <v>649.13095238095241</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -21855,19 +21966,19 @@
         <v>2</v>
       </c>
       <c r="Q8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="R8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="S8" t="s">
         <v>21</v>
       </c>
       <c r="X8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Y8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AC8" t="str">
         <f>Wydatki!A4</f>
@@ -21895,7 +22006,7 @@
       </c>
       <c r="AO8" s="91">
         <f>Podsumowanie!B28</f>
-        <v>471.04761904761904</v>
+        <v>472.09523809523807</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -21981,7 +22092,7 @@
       </c>
       <c r="AO9" s="91">
         <f>Podsumowanie!B29</f>
-        <v>686.94444444444446</v>
+        <v>688.47222222222229</v>
       </c>
     </row>
     <row r="10" spans="1:41">
@@ -21995,19 +22106,19 @@
       </c>
       <c r="J10">
         <f>Podsumowanie!C4</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K10" s="91">
         <f>Podsumowanie!J4</f>
-        <v>20450</v>
+        <v>20180</v>
       </c>
       <c r="L10" s="91">
         <f>Podsumowanie!K4</f>
-        <v>5100</v>
+        <v>10100</v>
       </c>
       <c r="M10" s="91">
         <f>Podsumowanie!L4</f>
-        <v>-15350</v>
+        <v>-10080</v>
       </c>
       <c r="P10" t="str">
         <f>'Do wiadomości rodziców'!C34</f>
@@ -22031,7 +22142,7 @@
       </c>
       <c r="Y10">
         <f>'Do wiadomości rodziców'!D7</f>
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AC10" t="str">
         <f>Wydatki!A6</f>
@@ -22059,7 +22170,7 @@
       </c>
       <c r="AO10" s="91">
         <f>Podsumowanie!B30</f>
-        <v>686.94444444444446</v>
+        <v>688.47222222222229</v>
       </c>
     </row>
     <row r="11" spans="1:41">
@@ -22093,15 +22204,15 @@
       </c>
       <c r="Q11" s="91">
         <f>'Do wiadomości rodziców'!D35</f>
-        <v>20450</v>
+        <v>20180</v>
       </c>
       <c r="R11" s="91">
         <f>'Do wiadomości rodziców'!E35</f>
-        <v>5100</v>
+        <v>10100</v>
       </c>
       <c r="S11" s="91">
         <f>'Do wiadomości rodziców'!F35</f>
-        <v>-15350</v>
+        <v>-10080</v>
       </c>
       <c r="X11" t="str">
         <f>'Do wiadomości rodziców'!C9</f>
@@ -22137,7 +22248,7 @@
       </c>
       <c r="AO11" s="91">
         <f>Podsumowanie!B31</f>
-        <v>686.94444444444446</v>
+        <v>688.47222222222229</v>
       </c>
     </row>
     <row r="12" spans="1:41">
@@ -22207,7 +22318,7 @@
       </c>
       <c r="AO12" s="91">
         <f>Podsumowanie!B32</f>
-        <v>667.31746031746025</v>
+        <v>668.80158730158735</v>
       </c>
     </row>
     <row r="13" spans="1:41">
@@ -22277,7 +22388,7 @@
       </c>
       <c r="AO13" s="91">
         <f>Podsumowanie!B33</f>
-        <v>510.30158730158729</v>
+        <v>511.43650793650795</v>
       </c>
     </row>
     <row r="14" spans="1:41">
@@ -22327,7 +22438,7 @@
       </c>
       <c r="AD14" s="91">
         <f>Wydatki!F10</f>
-        <v>3250.5000000000005</v>
+        <v>3242.25</v>
       </c>
       <c r="AE14" s="91">
         <f>Wydatki!G10</f>
@@ -22335,7 +22446,7 @@
       </c>
       <c r="AF14" s="91">
         <f>Wydatki!H10</f>
-        <v>3250.5000000000005</v>
+        <v>3242.25</v>
       </c>
       <c r="AG14">
         <f>Wydatki!I10</f>
@@ -22387,15 +22498,15 @@
       </c>
       <c r="Q16" s="91">
         <f>'Do wiadomości rodziców'!D40</f>
-        <v>133800</v>
+        <v>133530</v>
       </c>
       <c r="R16" s="91">
         <f>'Do wiadomości rodziców'!E40</f>
-        <v>40050</v>
+        <v>45050</v>
       </c>
       <c r="S16" s="91">
         <f>'Do wiadomości rodziców'!F40</f>
-        <v>-93750</v>
+        <v>-88480</v>
       </c>
       <c r="AC16" t="str">
         <f>Wydatki!A12</f>
@@ -22443,7 +22554,7 @@
     <row r="18" spans="29:33">
       <c r="AD18" s="91">
         <f>Wydatki!F14</f>
-        <v>130090.5</v>
+        <v>129812.25</v>
       </c>
       <c r="AE18" s="91">
         <f>Wydatki!G14</f>
@@ -22451,7 +22562,7 @@
       </c>
       <c r="AF18" s="91">
         <f>Wydatki!H14</f>
-        <v>125334.65</v>
+        <v>125056.4</v>
       </c>
     </row>
   </sheetData>
@@ -22481,16 +22592,16 @@
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="65.25" customHeight="1">
       <c r="A1" s="55" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B1" s="86" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C1" s="86" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D1" s="55" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1" s="55" t="s">
         <v>1</v>
@@ -22502,10 +22613,10 @@
         <v>2</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -22519,7 +22630,7 @@
         <v>46125.645833333336</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>25</v>
@@ -22557,7 +22668,7 @@
         <v>46125.647222222222</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>29</v>
@@ -22595,7 +22706,7 @@
         <v>46125.648611111108</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E4" s="47" t="s">
         <v>31</v>
@@ -22633,7 +22744,7 @@
         <v>46125.65</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E5" s="47" t="s">
         <v>35</v>
@@ -22671,7 +22782,7 @@
         <v>46125.652777777781</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E6" s="47" t="s">
         <v>37</v>
@@ -22709,7 +22820,7 @@
         <v>46125.658333333333</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E7" s="47" t="s">
         <v>39</v>
@@ -22747,7 +22858,7 @@
         <v>46125.67083333333</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E8" s="47" t="s">
         <v>35</v>
@@ -22785,7 +22896,7 @@
         <v>46125.677083333336</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E9" s="47" t="s">
         <v>42</v>
@@ -22823,7 +22934,7 @@
         <v>46125.682638888888</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E10" s="47" t="s">
         <v>44</v>
@@ -22861,7 +22972,7 @@
         <v>46125.697222222225</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E11" s="47" t="s">
         <v>46</v>
@@ -22899,7 +23010,7 @@
         <v>46125.70208333333</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E12" s="47" t="s">
         <v>48</v>
@@ -22937,7 +23048,7 @@
         <v>46125.72152777778</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E13" s="47" t="s">
         <v>50</v>
@@ -22975,7 +23086,7 @@
         <v>46125.762499999997</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E14" s="47" t="s">
         <v>52</v>
@@ -23013,7 +23124,7 @@
         <v>46125.763888888891</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E15" s="47" t="s">
         <v>55</v>
@@ -23051,7 +23162,7 @@
         <v>46125.765277777777</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E16" s="47" t="s">
         <v>57</v>
@@ -23089,7 +23200,7 @@
         <v>46125.767361111109</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E17" s="47" t="s">
         <v>59</v>
@@ -23127,7 +23238,7 @@
         <v>46125.768750000003</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E18" s="47" t="s">
         <v>61</v>
@@ -23165,7 +23276,7 @@
         <v>46125.770138888889</v>
       </c>
       <c r="D19" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E19" s="47" t="s">
         <v>63</v>
@@ -23203,7 +23314,7 @@
         <v>46125.774305555555</v>
       </c>
       <c r="D20" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E20" s="47" t="s">
         <v>65</v>
@@ -23241,7 +23352,7 @@
         <v>46125.777777777781</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E21" s="47" t="s">
         <v>67</v>
@@ -23279,7 +23390,7 @@
         <v>46125.790972222225</v>
       </c>
       <c r="D22" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E22" s="47" t="s">
         <v>25</v>
@@ -23317,7 +23428,7 @@
         <v>46125.84375</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E23" s="47" t="s">
         <v>70</v>
@@ -23355,7 +23466,7 @@
         <v>46125.845138888886</v>
       </c>
       <c r="D24" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E24" s="47" t="s">
         <v>63</v>
@@ -23393,7 +23504,7 @@
         <v>46125.84652777778</v>
       </c>
       <c r="D25" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E25" s="47" t="s">
         <v>73</v>
@@ -23431,7 +23542,7 @@
         <v>46125.866666666669</v>
       </c>
       <c r="D26" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E26" s="47" t="s">
         <v>63</v>
@@ -23469,7 +23580,7 @@
         <v>46125.892361111109</v>
       </c>
       <c r="D27" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E27" s="47" t="s">
         <v>76</v>
@@ -23507,7 +23618,7 @@
         <v>46125.897222222222</v>
       </c>
       <c r="D28" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E28" s="47" t="s">
         <v>78</v>
@@ -23545,7 +23656,7 @@
         <v>46126.37777777778</v>
       </c>
       <c r="D29" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E29" s="47" t="s">
         <v>80</v>
@@ -23583,7 +23694,7 @@
         <v>46126.384027777778</v>
       </c>
       <c r="D30" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E30" s="47" t="s">
         <v>65</v>
@@ -23621,7 +23732,7 @@
         <v>46126.384027777778</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E31" s="47" t="s">
         <v>83</v>
@@ -23659,7 +23770,7 @@
         <v>46126.405555555553</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E32" s="47" t="s">
         <v>85</v>
@@ -23697,7 +23808,7 @@
         <v>46126.522916666669</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E33" s="47" t="s">
         <v>73</v>
@@ -23735,7 +23846,7 @@
         <v>46126.522916666669</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E34" s="47" t="s">
         <v>89</v>
@@ -23773,7 +23884,7 @@
         <v>46126.523611111108</v>
       </c>
       <c r="D35" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E35" s="47" t="s">
         <v>89</v>
@@ -23811,13 +23922,13 @@
         <v>46126.523611111108</v>
       </c>
       <c r="D36" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F36" s="47" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G36" s="47" t="s">
         <v>87</v>
@@ -23849,7 +23960,7 @@
         <v>46126.523611111108</v>
       </c>
       <c r="D37" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E37" s="47" t="s">
         <v>67</v>
@@ -23887,7 +23998,7 @@
         <v>46126.525000000001</v>
       </c>
       <c r="D38" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E38" s="47" t="s">
         <v>95</v>
@@ -23925,7 +24036,7 @@
         <v>46126.525000000001</v>
       </c>
       <c r="D39" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E39" s="47" t="s">
         <v>73</v>
@@ -23963,7 +24074,7 @@
         <v>46126.525000000001</v>
       </c>
       <c r="D40" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E40" s="47" t="s">
         <v>98</v>
@@ -24001,7 +24112,7 @@
         <v>46126.525694444441</v>
       </c>
       <c r="D41" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E41" s="47" t="s">
         <v>100</v>
@@ -24039,7 +24150,7 @@
         <v>46126.525694444441</v>
       </c>
       <c r="D42" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E42" s="47" t="s">
         <v>59</v>
@@ -24077,7 +24188,7 @@
         <v>46126.526388888888</v>
       </c>
       <c r="D43" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>46</v>
@@ -24115,7 +24226,7 @@
         <v>46126.706944444442</v>
       </c>
       <c r="D44" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E44" s="47" t="s">
         <v>73</v>
@@ -24153,7 +24264,7 @@
         <v>46126.915277777778</v>
       </c>
       <c r="D45" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E45" s="47" t="s">
         <v>105</v>
@@ -24191,7 +24302,7 @@
         <v>46127.85</v>
       </c>
       <c r="D46" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E46" s="47" t="s">
         <v>107</v>
@@ -24229,7 +24340,7 @@
         <v>46127.866666666669</v>
       </c>
       <c r="D47" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E47" s="47" t="s">
         <v>109</v>
@@ -24267,7 +24378,7 @@
         <v>46127.992361111108</v>
       </c>
       <c r="D48" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E48" s="47" t="s">
         <v>111</v>
@@ -24305,7 +24416,7 @@
         <v>46128.43472222222</v>
       </c>
       <c r="D49" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E49" s="47" t="s">
         <v>59</v>
@@ -24343,7 +24454,7 @@
         <v>46128.43472222222</v>
       </c>
       <c r="D50" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E50" s="47" t="s">
         <v>116</v>
@@ -24381,7 +24492,7 @@
         <v>46128.43472222222</v>
       </c>
       <c r="D51" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E51" s="47" t="s">
         <v>73</v>
@@ -24419,7 +24530,7 @@
         <v>46128.436805555553</v>
       </c>
       <c r="D52" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E52" s="47" t="s">
         <v>121</v>
@@ -24457,7 +24568,7 @@
         <v>46128.436805555553</v>
       </c>
       <c r="D53" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E53" s="47" t="s">
         <v>37</v>
@@ -24495,7 +24606,7 @@
         <v>46128.436805555553</v>
       </c>
       <c r="D54" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E54" s="47" t="s">
         <v>73</v>
@@ -24533,7 +24644,7 @@
         <v>46128.4375</v>
       </c>
       <c r="D55" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E55" s="47" t="s">
         <v>127</v>
@@ -24571,7 +24682,7 @@
         <v>46128.4375</v>
       </c>
       <c r="D56" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E56" s="47" t="s">
         <v>63</v>
@@ -24609,7 +24720,7 @@
         <v>46128.439583333333</v>
       </c>
       <c r="D57" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E57" s="47" t="s">
         <v>131</v>
@@ -24647,7 +24758,7 @@
         <v>46128.439583333333</v>
       </c>
       <c r="D58" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E58" s="47" t="s">
         <v>46</v>
@@ -24685,7 +24796,7 @@
         <v>46128.439583333333</v>
       </c>
       <c r="D59" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E59" s="47" t="s">
         <v>135</v>
@@ -24723,7 +24834,7 @@
         <v>46128.44027777778</v>
       </c>
       <c r="D60" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E60" s="47" t="s">
         <v>92</v>
@@ -24761,7 +24872,7 @@
         <v>46128.440972222219</v>
       </c>
       <c r="D61" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E61" s="47" t="s">
         <v>139</v>
@@ -24799,13 +24910,13 @@
         <v>46128.440972222219</v>
       </c>
       <c r="D62" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F62" s="47" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G62" s="47" t="s">
         <v>113</v>
@@ -24837,7 +24948,7 @@
         <v>46128.440972222219</v>
       </c>
       <c r="D63" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E63" s="47" t="s">
         <v>52</v>
@@ -24875,7 +24986,7 @@
         <v>46128.440972222219</v>
       </c>
       <c r="D64" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E64" s="47" t="s">
         <v>146</v>
@@ -24913,7 +25024,7 @@
         <v>46128.442361111112</v>
       </c>
       <c r="D65" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E65" s="47" t="s">
         <v>65</v>
@@ -24951,13 +25062,13 @@
         <v>46128.479166666664</v>
       </c>
       <c r="D66" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E66" s="47" t="s">
         <v>29</v>
       </c>
       <c r="F66" s="47" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G66" s="47" t="s">
         <v>113</v>
@@ -24989,13 +25100,13 @@
         <v>46128.693055555559</v>
       </c>
       <c r="D67" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E67" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="F67" s="47" t="s">
         <v>152</v>
-      </c>
-      <c r="F67" s="47" t="s">
-        <v>151</v>
       </c>
       <c r="G67" s="47" t="s">
         <v>26</v>
@@ -25027,13 +25138,13 @@
         <v>46128.724305555559</v>
       </c>
       <c r="D68" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E68" s="47" t="s">
         <v>63</v>
       </c>
       <c r="F68" s="47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G68" s="47" t="s">
         <v>26</v>
@@ -25065,13 +25176,13 @@
         <v>46128.788888888892</v>
       </c>
       <c r="D69" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E69" s="47" t="s">
         <v>63</v>
       </c>
       <c r="F69" s="47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G69" s="47" t="s">
         <v>113</v>
@@ -25103,13 +25214,13 @@
         <v>46128.838194444441</v>
       </c>
       <c r="D70" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>25</v>
       </c>
       <c r="F70" s="47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G70" s="47" t="s">
         <v>87</v>
@@ -25141,13 +25252,13 @@
         <v>46128.85</v>
       </c>
       <c r="D71" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E71" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F71" s="47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G71" s="47" t="s">
         <v>53</v>
@@ -25179,13 +25290,13 @@
         <v>46128.925000000003</v>
       </c>
       <c r="D72" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E72" s="47" t="s">
         <v>29</v>
       </c>
       <c r="F72" s="47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G72" s="47" t="s">
         <v>87</v>
@@ -25217,13 +25328,13 @@
         <v>46129.521527777775</v>
       </c>
       <c r="D73" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E73" s="47" t="s">
+        <v>161</v>
+      </c>
+      <c r="F73" s="47" t="s">
         <v>160</v>
-      </c>
-      <c r="F73" s="47" t="s">
-        <v>159</v>
       </c>
       <c r="G73" s="47" t="s">
         <v>113</v>
@@ -25255,13 +25366,13 @@
         <v>46129.619444444441</v>
       </c>
       <c r="D74" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E74" s="47" t="s">
         <v>63</v>
       </c>
       <c r="F74" s="47" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G74" s="47" t="s">
         <v>87</v>
@@ -25293,13 +25404,13 @@
         <v>46129.661111111112</v>
       </c>
       <c r="D75" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E75" s="47" t="s">
         <v>63</v>
       </c>
       <c r="F75" s="47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G75" s="47" t="s">
         <v>87</v>
@@ -25331,7 +25442,7 @@
         <v>46129.880555555559</v>
       </c>
       <c r="D76" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E76" s="47" t="s">
         <v>59</v>
@@ -25369,13 +25480,13 @@
         <v>46129.929861111108</v>
       </c>
       <c r="D77" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E77" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="F77" s="47" t="s">
         <v>164</v>
-      </c>
-      <c r="F77" s="47" t="s">
-        <v>163</v>
       </c>
       <c r="G77" s="47" t="s">
         <v>53</v>
@@ -25407,10 +25518,10 @@
         <v>46130.60833333333</v>
       </c>
       <c r="D78" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E78" s="47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F78" s="47" t="s">
         <v>108</v>
@@ -25445,13 +25556,13 @@
         <v>46130.65</v>
       </c>
       <c r="D79" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E79" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="F79" s="47" t="s">
         <v>167</v>
-      </c>
-      <c r="F79" s="47" t="s">
-        <v>166</v>
       </c>
       <c r="G79" s="47" t="s">
         <v>87</v>
@@ -25483,13 +25594,13 @@
         <v>46130.883333333331</v>
       </c>
       <c r="D80" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E80" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="F80" s="47" t="s">
         <v>169</v>
-      </c>
-      <c r="F80" s="47" t="s">
-        <v>168</v>
       </c>
       <c r="G80" s="47" t="s">
         <v>87</v>
@@ -25521,13 +25632,13 @@
         <v>46131.617361111108</v>
       </c>
       <c r="D81" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E81" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="F81" s="47" t="s">
         <v>172</v>
-      </c>
-      <c r="F81" s="47" t="s">
-        <v>171</v>
       </c>
       <c r="G81" s="47" t="s">
         <v>87</v>
@@ -25559,13 +25670,13 @@
         <v>46131.762499999997</v>
       </c>
       <c r="D82" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E82" s="47" t="s">
         <v>59</v>
       </c>
       <c r="F82" s="47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G82" s="47" t="s">
         <v>26</v>
@@ -25597,13 +25708,13 @@
         <v>46131.979861111111</v>
       </c>
       <c r="D83" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E83" s="47" t="s">
         <v>65</v>
       </c>
       <c r="F83" s="47" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G83" s="47" t="s">
         <v>113</v>
@@ -25635,7 +25746,7 @@
         <v>46131.979861111111</v>
       </c>
       <c r="D84" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E84" s="47" t="s">
         <v>78</v>
@@ -25673,16 +25784,16 @@
         <v>46133.536111111112</v>
       </c>
       <c r="D85" s="47" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E85" s="47" t="s">
+        <v>178</v>
+      </c>
+      <c r="F85" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F85" s="47" t="s">
-        <v>176</v>
-      </c>
       <c r="G85" s="47" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H85" s="47" t="s">
         <v>27</v>
@@ -25711,13 +25822,13 @@
         <v>46134.777083333334</v>
       </c>
       <c r="D86" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E86" s="49" t="s">
         <v>76</v>
       </c>
       <c r="F86" s="49" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G86" s="49" t="s">
         <v>113</v>
@@ -25749,13 +25860,13 @@
         <v>46134.780555555553</v>
       </c>
       <c r="D87" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E87" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="F87" s="51" t="s">
         <v>181</v>
-      </c>
-      <c r="F87" s="51" t="s">
-        <v>180</v>
       </c>
       <c r="G87" s="51" t="s">
         <v>32</v>
@@ -25787,13 +25898,13 @@
         <v>46134.780555555553</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E88" s="49" t="s">
         <v>59</v>
       </c>
       <c r="F88" s="49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G88" s="49" t="s">
         <v>53</v>
@@ -25825,13 +25936,13 @@
         <v>46135.796527777777</v>
       </c>
       <c r="D89" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E89" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="F89" s="51" t="s">
         <v>184</v>
-      </c>
-      <c r="F89" s="51" t="s">
-        <v>183</v>
       </c>
       <c r="G89" s="51" t="s">
         <v>53</v>
@@ -25863,13 +25974,13 @@
         <v>46135.796527777777</v>
       </c>
       <c r="D90" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E90" s="49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F90" s="49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G90" s="49" t="s">
         <v>53</v>
@@ -25901,16 +26012,16 @@
         <v>46139.715277777781</v>
       </c>
       <c r="D91" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E91" s="49" t="s">
         <v>127</v>
       </c>
       <c r="F91" s="49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G91" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H91" s="49" t="s">
         <v>27</v>
@@ -25939,7 +26050,7 @@
         <v>46139.715277777781</v>
       </c>
       <c r="D92" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E92" s="51" t="s">
         <v>59</v>
@@ -25948,7 +26059,7 @@
         <v>110</v>
       </c>
       <c r="G92" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H92" s="51" t="s">
         <v>27</v>
@@ -25977,16 +26088,16 @@
         <v>46139.715277777781</v>
       </c>
       <c r="D93" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E93" s="49" t="s">
         <v>80</v>
       </c>
       <c r="F93" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="G93" s="49" t="s">
         <v>188</v>
-      </c>
-      <c r="G93" s="49" t="s">
-        <v>187</v>
       </c>
       <c r="H93" s="49" t="s">
         <v>27</v>
@@ -26015,16 +26126,16 @@
         <v>46139.715277777781</v>
       </c>
       <c r="D94" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E94" s="51" t="s">
         <v>42</v>
       </c>
       <c r="F94" s="51" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G94" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H94" s="51" t="s">
         <v>27</v>
@@ -26053,16 +26164,16 @@
         <v>46139.715277777781</v>
       </c>
       <c r="D95" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E95" s="49" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F95" s="49" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G95" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H95" s="49" t="s">
         <v>27</v>
@@ -26091,16 +26202,16 @@
         <v>46139.716666666667</v>
       </c>
       <c r="D96" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E96" s="51" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F96" s="51" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G96" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H96" s="51" t="s">
         <v>27</v>
@@ -26129,16 +26240,16 @@
         <v>46139.722916666666</v>
       </c>
       <c r="D97" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E97" s="51" t="s">
         <v>39</v>
       </c>
       <c r="F97" s="51" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G97" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H97" s="51" t="s">
         <v>27</v>
@@ -26167,16 +26278,16 @@
         <v>46139.753472222219</v>
       </c>
       <c r="D98" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E98" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="F98" s="49" t="s">
         <v>194</v>
       </c>
-      <c r="F98" s="49" t="s">
-        <v>193</v>
-      </c>
       <c r="G98" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H98" s="49" t="s">
         <v>27</v>
@@ -26205,16 +26316,16 @@
         <v>46139.759027777778</v>
       </c>
       <c r="D99" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E99" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="F99" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="F99" s="51" t="s">
-        <v>195</v>
-      </c>
       <c r="G99" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H99" s="51" t="s">
         <v>27</v>
@@ -26243,16 +26354,16 @@
         <v>46139.760416666664</v>
       </c>
       <c r="D100" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E100" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="F100" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="F100" s="49" t="s">
-        <v>197</v>
-      </c>
       <c r="G100" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H100" s="49" t="s">
         <v>27</v>
@@ -26281,16 +26392,16 @@
         <v>46139.803472222222</v>
       </c>
       <c r="D101" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E101" s="51" t="s">
         <v>57</v>
       </c>
       <c r="F101" s="51" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G101" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H101" s="51" t="s">
         <v>27</v>
@@ -26319,16 +26430,16 @@
         <v>46139.808333333334</v>
       </c>
       <c r="D102" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E102" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="F102" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="F102" s="49" t="s">
-        <v>200</v>
-      </c>
       <c r="G102" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H102" s="49" t="s">
         <v>27</v>
@@ -26357,16 +26468,16 @@
         <v>46139.888888888891</v>
       </c>
       <c r="D103" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E103" s="51" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F103" s="51" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G103" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H103" s="51" t="s">
         <v>27</v>
@@ -26395,16 +26506,16 @@
         <v>46140.425000000003</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E104" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="F104" s="49" t="s">
         <v>205</v>
       </c>
-      <c r="F104" s="49" t="s">
-        <v>204</v>
-      </c>
       <c r="G104" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H104" s="49" t="s">
         <v>27</v>
@@ -26433,16 +26544,16 @@
         <v>46140.604861111111</v>
       </c>
       <c r="D105" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E105" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="F105" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="F105" s="49" t="s">
-        <v>206</v>
-      </c>
       <c r="G105" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H105" s="49" t="s">
         <v>27</v>
@@ -26471,16 +26582,16 @@
         <v>46140.616666666669</v>
       </c>
       <c r="D106" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E106" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F106" s="51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G106" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H106" s="51" t="s">
         <v>27</v>
@@ -26509,16 +26620,16 @@
         <v>46140.972222222219</v>
       </c>
       <c r="D107" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E107" s="49" t="s">
         <v>73</v>
       </c>
       <c r="F107" s="49" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G107" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H107" s="49" t="s">
         <v>27</v>
@@ -26547,16 +26658,16 @@
         <v>46140.972222222219</v>
       </c>
       <c r="D108" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E108" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="F108" s="49" t="s">
         <v>211</v>
       </c>
-      <c r="F108" s="49" t="s">
-        <v>210</v>
-      </c>
       <c r="G108" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H108" s="49" t="s">
         <v>27</v>
@@ -26585,16 +26696,16 @@
         <v>46142.597222222219</v>
       </c>
       <c r="D109" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E109" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="F109" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="F109" s="51" t="s">
-        <v>212</v>
-      </c>
       <c r="G109" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H109" s="51" t="s">
         <v>27</v>
@@ -26623,13 +26734,13 @@
         <v>46153.702777777777</v>
       </c>
       <c r="D110" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E110" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="F110" s="49" t="s">
         <v>215</v>
-      </c>
-      <c r="F110" s="49" t="s">
-        <v>214</v>
       </c>
       <c r="G110" s="49" t="s">
         <v>53</v>
@@ -26661,16 +26772,16 @@
         <v>46164.888194444444</v>
       </c>
       <c r="D111" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E111" s="51" t="s">
         <v>63</v>
       </c>
       <c r="F111" s="51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G111" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H111" s="51" t="s">
         <v>27</v>
@@ -26699,16 +26810,16 @@
         <v>46165.59375</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E112" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="F112" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="F112" s="49" t="s">
-        <v>217</v>
-      </c>
       <c r="G112" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H112" s="49" t="s">
         <v>27</v>
@@ -26737,16 +26848,16 @@
         <v>46165.59375</v>
       </c>
       <c r="D113" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E113" s="51" t="s">
         <v>135</v>
       </c>
       <c r="F113" s="51" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G113" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H113" s="51" t="s">
         <v>27</v>
@@ -26775,13 +26886,13 @@
         <v>46167.594444444447</v>
       </c>
       <c r="D114" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E114" s="49" t="s">
+        <v>221</v>
+      </c>
+      <c r="F114" s="49" t="s">
         <v>220</v>
-      </c>
-      <c r="F114" s="49" t="s">
-        <v>219</v>
       </c>
       <c r="G114" s="49" t="s">
         <v>32</v>
@@ -26813,13 +26924,13 @@
         <v>46167.85</v>
       </c>
       <c r="D115" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E115" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="F115" s="51" t="s">
         <v>222</v>
-      </c>
-      <c r="F115" s="51" t="s">
-        <v>221</v>
       </c>
       <c r="G115" s="51" t="s">
         <v>87</v>
@@ -26851,13 +26962,13 @@
         <v>46167.854861111111</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E116" s="49" t="s">
         <v>44</v>
       </c>
       <c r="F116" s="49" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G116" s="49" t="s">
         <v>87</v>
@@ -26889,13 +27000,13 @@
         <v>46167.890972222223</v>
       </c>
       <c r="D117" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E117" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="F117" s="51" t="s">
         <v>225</v>
-      </c>
-      <c r="F117" s="51" t="s">
-        <v>224</v>
       </c>
       <c r="G117" s="51" t="s">
         <v>87</v>
@@ -26927,13 +27038,13 @@
         <v>46167.92291666667</v>
       </c>
       <c r="D118" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E118" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="F118" s="49" t="s">
         <v>227</v>
-      </c>
-      <c r="F118" s="49" t="s">
-        <v>226</v>
       </c>
       <c r="G118" s="49" t="s">
         <v>87</v>
@@ -26965,13 +27076,13 @@
         <v>46167.929166666669</v>
       </c>
       <c r="D119" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E119" s="51" t="s">
         <v>73</v>
       </c>
       <c r="F119" s="51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G119" s="51" t="s">
         <v>32</v>
@@ -27003,13 +27114,13 @@
         <v>46167.933333333334</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E120" s="49" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F120" s="49" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G120" s="49" t="s">
         <v>113</v>
@@ -27041,13 +27152,13 @@
         <v>46168.370833333334</v>
       </c>
       <c r="D121" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E121" s="51" t="s">
         <v>57</v>
       </c>
       <c r="F121" s="51" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G121" s="51" t="s">
         <v>32</v>
@@ -27079,7 +27190,7 @@
         <v>46168.401388888888</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E122" s="49" t="s">
         <v>46</v>
@@ -27117,13 +27228,13 @@
         <v>46168.402118055601</v>
       </c>
       <c r="D123" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E123" s="49" t="s">
         <v>59</v>
       </c>
       <c r="F123" s="49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G123" s="49" t="s">
         <v>32</v>
@@ -27155,13 +27266,13 @@
         <v>46168.406145833302</v>
       </c>
       <c r="D124" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E124" s="51" t="s">
         <v>131</v>
       </c>
       <c r="F124" s="51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G124" s="51" t="s">
         <v>32</v>
@@ -27193,13 +27304,13 @@
         <v>46168.429502314801</v>
       </c>
       <c r="D125" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E125" s="49" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F125" s="49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G125" s="49" t="s">
         <v>32</v>
@@ -27231,16 +27342,16 @@
         <v>46168.470891203702</v>
       </c>
       <c r="D126" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E126" s="51" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F126" s="51" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G126" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H126" s="51" t="s">
         <v>27</v>
@@ -27269,16 +27380,16 @@
         <v>46168.472280092603</v>
       </c>
       <c r="D127" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E127" s="51" t="s">
         <v>83</v>
       </c>
       <c r="F127" s="51" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G127" s="51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H127" s="51" t="s">
         <v>27</v>
@@ -27307,16 +27418,16 @@
         <v>46168.472476851799</v>
       </c>
       <c r="D128" s="51" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E128" s="51" t="s">
         <v>63</v>
       </c>
       <c r="F128" s="51" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G128" s="51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H128" s="51" t="s">
         <v>27</v>
@@ -27345,16 +27456,16 @@
         <v>46168.477511574099</v>
       </c>
       <c r="D129" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E129" s="49" t="s">
         <v>73</v>
       </c>
       <c r="F129" s="49" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G129" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H129" s="49" t="s">
         <v>27</v>
@@ -27383,7 +27494,7 @@
         <v>46168.484293981499</v>
       </c>
       <c r="D130" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E130" s="53" t="s">
         <v>73</v>
@@ -27392,7 +27503,7 @@
         <v>34</v>
       </c>
       <c r="G130" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H130" s="53" t="s">
         <v>27</v>
@@ -27421,13 +27532,13 @@
         <v>46168.519641203697</v>
       </c>
       <c r="D131" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E131" s="53" t="s">
         <v>46</v>
       </c>
       <c r="F131" s="53" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G131" s="53" t="s">
         <v>87</v>
@@ -27459,16 +27570,16 @@
         <v>46168.583449074104</v>
       </c>
       <c r="D132" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E132" s="53" t="s">
         <v>37</v>
       </c>
       <c r="F132" s="53" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G132" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H132" s="53" t="s">
         <v>27</v>
@@ -27497,16 +27608,16 @@
         <v>46168.583541666703</v>
       </c>
       <c r="D133" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E133" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="F133" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="F133" s="53" t="s">
-        <v>242</v>
-      </c>
       <c r="G133" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H133" s="53" t="s">
         <v>27</v>
@@ -27535,16 +27646,16 @@
         <v>46168.5835532407</v>
       </c>
       <c r="D134" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E134" s="53" t="s">
         <v>46</v>
       </c>
       <c r="F134" s="53" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G134" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H134" s="53" t="s">
         <v>27</v>
@@ -27573,16 +27684,16 @@
         <v>46168.583564814799</v>
       </c>
       <c r="D135" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E135" s="53" t="s">
         <v>29</v>
       </c>
       <c r="F135" s="53" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G135" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H135" s="53" t="s">
         <v>27</v>
@@ -27611,16 +27722,16 @@
         <v>46168.583634259303</v>
       </c>
       <c r="D136" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E136" s="53" t="s">
         <v>65</v>
       </c>
       <c r="F136" s="53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G136" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H136" s="53" t="s">
         <v>27</v>
@@ -27649,16 +27760,16 @@
         <v>46168.584340277797</v>
       </c>
       <c r="D137" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E137" s="53" t="s">
+        <v>248</v>
+      </c>
+      <c r="F137" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="F137" s="53" t="s">
-        <v>246</v>
-      </c>
       <c r="G137" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H137" s="53" t="s">
         <v>27</v>
@@ -27687,16 +27798,16 @@
         <v>46168.5844560185</v>
       </c>
       <c r="D138" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E138" s="53" t="s">
         <v>63</v>
       </c>
       <c r="F138" s="53" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G138" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H138" s="53" t="s">
         <v>27</v>
@@ -27725,16 +27836,16 @@
         <v>46168.586053240702</v>
       </c>
       <c r="D139" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E139" s="53" t="s">
         <v>59</v>
       </c>
       <c r="F139" s="53" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G139" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H139" s="53" t="s">
         <v>27</v>
@@ -27763,16 +27874,16 @@
         <v>46168.586192129602</v>
       </c>
       <c r="D140" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E140" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F140" s="53" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G140" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H140" s="53" t="s">
         <v>27</v>
@@ -27801,16 +27912,16 @@
         <v>46168.588125000002</v>
       </c>
       <c r="D141" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E141" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F141" s="53" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G141" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H141" s="53" t="s">
         <v>27</v>
@@ -27839,16 +27950,16 @@
         <v>46168.589942129598</v>
       </c>
       <c r="D142" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E142" s="53" t="s">
         <v>35</v>
       </c>
       <c r="F142" s="53" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G142" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H142" s="53" t="s">
         <v>27</v>
@@ -27877,13 +27988,13 @@
         <v>46168.593043981498</v>
       </c>
       <c r="D143" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E143" s="53" t="s">
         <v>31</v>
       </c>
       <c r="F143" s="53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G143" s="53" t="s">
         <v>32</v>
@@ -27915,16 +28026,16 @@
         <v>46168.595381944397</v>
       </c>
       <c r="D144" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E144" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F144" s="53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G144" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H144" s="53" t="s">
         <v>27</v>
@@ -27953,16 +28064,16 @@
         <v>46168.607453703698</v>
       </c>
       <c r="D145" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E145" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="F145" s="53" t="s">
         <v>256</v>
       </c>
-      <c r="F145" s="53" t="s">
-        <v>255</v>
-      </c>
       <c r="G145" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H145" s="53" t="s">
         <v>27</v>
@@ -27991,16 +28102,16 @@
         <v>46168.629259259302</v>
       </c>
       <c r="D146" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E146" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F146" s="53" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G146" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H146" s="53" t="s">
         <v>27</v>
@@ -28029,16 +28140,16 @@
         <v>46168.648854166699</v>
       </c>
       <c r="D147" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E147" s="53" t="s">
         <v>35</v>
       </c>
       <c r="F147" s="53" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G147" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H147" s="53" t="s">
         <v>27</v>
@@ -28067,16 +28178,16 @@
         <v>46168.650486111103</v>
       </c>
       <c r="D148" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E148" s="53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F148" s="53" t="s">
         <v>72</v>
       </c>
       <c r="G148" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H148" s="53" t="s">
         <v>27</v>
@@ -28105,13 +28216,13 @@
         <v>46168.655462962997</v>
       </c>
       <c r="D149" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E149" s="53" t="s">
         <v>29</v>
       </c>
       <c r="F149" s="53" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G149" s="53" t="s">
         <v>32</v>
@@ -28143,16 +28254,16 @@
         <v>46168.668182870402</v>
       </c>
       <c r="D150" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E150" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="F150" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="F150" s="53" t="s">
-        <v>260</v>
-      </c>
       <c r="G150" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H150" s="53" t="s">
         <v>27</v>
@@ -28181,10 +28292,10 @@
         <v>46168.689687500002</v>
       </c>
       <c r="D151" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E151" s="53" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F151" s="53" t="s">
         <v>86</v>
@@ -28219,13 +28330,13 @@
         <v>46168.709189814799</v>
       </c>
       <c r="D152" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E152" s="53" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F152" s="53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G152" s="53" t="s">
         <v>53</v>
@@ -28257,16 +28368,16 @@
         <v>46168.742303240702</v>
       </c>
       <c r="D153" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E153" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="F153" s="53" t="s">
         <v>265</v>
       </c>
-      <c r="F153" s="53" t="s">
-        <v>264</v>
-      </c>
       <c r="G153" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H153" s="53" t="s">
         <v>27</v>
@@ -28295,13 +28406,13 @@
         <v>46168.772951388899</v>
       </c>
       <c r="D154" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E154" s="53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F154" s="53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G154" s="53" t="s">
         <v>32</v>
@@ -28333,16 +28444,16 @@
         <v>46168.792337963001</v>
       </c>
       <c r="D155" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E155" s="53" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F155" s="53" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G155" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H155" s="53" t="s">
         <v>27</v>
@@ -28371,16 +28482,16 @@
         <v>46168.795405092598</v>
       </c>
       <c r="D156" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E156" s="53" t="s">
         <v>67</v>
       </c>
       <c r="F156" s="53" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G156" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H156" s="53" t="s">
         <v>33</v>
@@ -28409,16 +28520,16 @@
         <v>46168.804918981499</v>
       </c>
       <c r="D157" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E157" s="53" t="s">
         <v>29</v>
       </c>
       <c r="F157" s="53" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G157" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H157" s="53" t="s">
         <v>27</v>
@@ -28447,13 +28558,13 @@
         <v>46169.368923611102</v>
       </c>
       <c r="D158" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E158" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="F158" s="53" t="s">
         <v>271</v>
-      </c>
-      <c r="F158" s="53" t="s">
-        <v>270</v>
       </c>
       <c r="G158" s="53" t="s">
         <v>87</v>
@@ -28485,13 +28596,13 @@
         <v>46169.369375000002</v>
       </c>
       <c r="D159" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E159" s="53" t="s">
         <v>80</v>
       </c>
       <c r="F159" s="53" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G159" s="53" t="s">
         <v>113</v>
@@ -28523,13 +28634,13 @@
         <v>46169.369444444397</v>
       </c>
       <c r="D160" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E160" s="53" t="s">
         <v>37</v>
       </c>
       <c r="F160" s="53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G160" s="53" t="s">
         <v>113</v>
@@ -28561,10 +28672,10 @@
         <v>46169.371342592603</v>
       </c>
       <c r="D161" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E161" s="53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F161" s="53" t="s">
         <v>86</v>
@@ -28599,13 +28710,13 @@
         <v>46169.3975347222</v>
       </c>
       <c r="D162" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E162" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F162" s="53" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G162" s="53" t="s">
         <v>113</v>
@@ -28637,13 +28748,13 @@
         <v>46169.402523148201</v>
       </c>
       <c r="D163" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E163" s="53" t="s">
         <v>44</v>
       </c>
       <c r="F163" s="53" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G163" s="53" t="s">
         <v>113</v>
@@ -28675,13 +28786,13 @@
         <v>46169.409618055601</v>
       </c>
       <c r="D164" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E164" s="53" t="s">
         <v>29</v>
       </c>
       <c r="F164" s="53" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G164" s="53" t="s">
         <v>53</v>
@@ -28713,13 +28824,13 @@
         <v>46169.410289351901</v>
       </c>
       <c r="D165" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E165" s="53" t="s">
+        <v>279</v>
+      </c>
+      <c r="F165" s="53" t="s">
         <v>278</v>
-      </c>
-      <c r="F165" s="53" t="s">
-        <v>277</v>
       </c>
       <c r="G165" s="53" t="s">
         <v>53</v>
@@ -28751,13 +28862,13 @@
         <v>46169.499108796299</v>
       </c>
       <c r="D166" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E166" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F166" s="53" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G166" s="53" t="s">
         <v>53</v>
@@ -28789,16 +28900,16 @@
         <v>46169.5080787037</v>
       </c>
       <c r="D167" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E167" s="53" t="s">
         <v>39</v>
       </c>
       <c r="F167" s="53" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G167" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H167" s="53" t="s">
         <v>27</v>
@@ -28827,13 +28938,13 @@
         <v>46169.574502314797</v>
       </c>
       <c r="D168" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E168" s="53" t="s">
         <v>63</v>
       </c>
       <c r="F168" s="53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G168" s="53" t="s">
         <v>113</v>
@@ -28865,13 +28976,13 @@
         <v>46169.6722800926</v>
       </c>
       <c r="D169" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E169" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="F169" s="53" t="s">
         <v>283</v>
-      </c>
-      <c r="F169" s="53" t="s">
-        <v>282</v>
       </c>
       <c r="G169" s="53" t="s">
         <v>26</v>
@@ -28903,13 +29014,13 @@
         <v>46169.674780092602</v>
       </c>
       <c r="D170" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E170" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="F170" s="53" t="s">
         <v>285</v>
-      </c>
-      <c r="F170" s="53" t="s">
-        <v>284</v>
       </c>
       <c r="G170" s="53" t="s">
         <v>26</v>
@@ -28941,13 +29052,13 @@
         <v>46169.682210648098</v>
       </c>
       <c r="D171" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E171" s="53" t="s">
         <v>57</v>
       </c>
       <c r="F171" s="53" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G171" s="53" t="s">
         <v>26</v>
@@ -28979,16 +29090,16 @@
         <v>46169.924351851798</v>
       </c>
       <c r="D172" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E172" s="53" t="s">
+        <v>290</v>
+      </c>
+      <c r="F172" s="53" t="s">
         <v>289</v>
       </c>
-      <c r="F172" s="53" t="s">
-        <v>288</v>
-      </c>
       <c r="G172" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H172" s="53" t="s">
         <v>27</v>
@@ -29017,13 +29128,13 @@
         <v>46169.931226851899</v>
       </c>
       <c r="D173" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E173" s="53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F173" s="53" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G173" s="53" t="s">
         <v>53</v>
@@ -29055,13 +29166,13 @@
         <v>46169.945590277799</v>
       </c>
       <c r="D174" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E174" s="53" t="s">
         <v>107</v>
       </c>
       <c r="F174" s="53" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G174" s="53" t="s">
         <v>87</v>
@@ -29093,13 +29204,13 @@
         <v>46170.293969907398</v>
       </c>
       <c r="D175" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E175" s="53" t="s">
         <v>107</v>
       </c>
       <c r="F175" s="53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G175" s="53" t="s">
         <v>26</v>
@@ -29131,13 +29242,13 @@
         <v>46170.312013888899</v>
       </c>
       <c r="D176" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E176" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="F176" s="53" t="s">
         <v>294</v>
-      </c>
-      <c r="F176" s="53" t="s">
-        <v>293</v>
       </c>
       <c r="G176" s="53" t="s">
         <v>87</v>
@@ -29169,13 +29280,13 @@
         <v>46170.318321759303</v>
       </c>
       <c r="D177" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E177" s="53" t="s">
         <v>65</v>
       </c>
       <c r="F177" s="53" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G177" s="53" t="s">
         <v>26</v>
@@ -29207,13 +29318,13 @@
         <v>46170.320960648103</v>
       </c>
       <c r="D178" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E178" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F178" s="53" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G178" s="53" t="s">
         <v>26</v>
@@ -29245,13 +29356,13 @@
         <v>46170.3214814815</v>
       </c>
       <c r="D179" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E179" s="53" t="s">
+        <v>298</v>
+      </c>
+      <c r="F179" s="53" t="s">
         <v>297</v>
-      </c>
-      <c r="F179" s="53" t="s">
-        <v>296</v>
       </c>
       <c r="G179" s="53" t="s">
         <v>26</v>
@@ -29283,10 +29394,10 @@
         <v>46170.334490740701</v>
       </c>
       <c r="D180" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E180" s="53" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F180" s="53" t="s">
         <v>91</v>
@@ -29321,16 +29432,16 @@
         <v>46170.343738425901</v>
       </c>
       <c r="D181" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E181" s="53" t="s">
         <v>46</v>
       </c>
       <c r="F181" s="53" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G181" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H181" s="53" t="s">
         <v>27</v>
@@ -29359,16 +29470,16 @@
         <v>46170.344351851803</v>
       </c>
       <c r="D182" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E182" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="F182" s="53" t="s">
         <v>301</v>
       </c>
-      <c r="F182" s="53" t="s">
-        <v>300</v>
-      </c>
       <c r="G182" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H182" s="53" t="s">
         <v>33</v>
@@ -29397,16 +29508,16 @@
         <v>46170.350277777798</v>
       </c>
       <c r="D183" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E183" s="53" t="s">
         <v>35</v>
       </c>
       <c r="F183" s="53" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G183" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H183" s="53" t="s">
         <v>27</v>
@@ -29435,16 +29546,16 @@
         <v>46170.362974536998</v>
       </c>
       <c r="D184" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E184" s="53" t="s">
         <v>52</v>
       </c>
       <c r="F184" s="53" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G184" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H184" s="53" t="s">
         <v>27</v>
@@ -29473,10 +29584,10 @@
         <v>46170.3669212963</v>
       </c>
       <c r="D185" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E185" s="53" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F185" s="53" t="s">
         <v>112</v>
@@ -29511,13 +29622,13 @@
         <v>46170.367071759298</v>
       </c>
       <c r="D186" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E186" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F186" s="53" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G186" s="53" t="s">
         <v>26</v>
@@ -29549,13 +29660,13 @@
         <v>46170.3670949074</v>
       </c>
       <c r="D187" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E187" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="F187" s="53" t="s">
         <v>307</v>
-      </c>
-      <c r="F187" s="53" t="s">
-        <v>306</v>
       </c>
       <c r="G187" s="53" t="s">
         <v>26</v>
@@ -29587,13 +29698,13 @@
         <v>46170.367152777799</v>
       </c>
       <c r="D188" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E188" s="53" t="s">
         <v>35</v>
       </c>
       <c r="F188" s="53" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G188" s="53" t="s">
         <v>26</v>
@@ -29625,13 +29736,13 @@
         <v>46170.367199074099</v>
       </c>
       <c r="D189" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E189" s="53" t="s">
         <v>46</v>
       </c>
       <c r="F189" s="53" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G189" s="53" t="s">
         <v>26</v>
@@ -29663,13 +29774,13 @@
         <v>46170.3676388889</v>
       </c>
       <c r="D190" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E190" s="53" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F190" s="53" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G190" s="53" t="s">
         <v>26</v>
@@ -29701,13 +29812,13 @@
         <v>46170.3727546296</v>
       </c>
       <c r="D191" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E191" s="53" t="s">
         <v>52</v>
       </c>
       <c r="F191" s="53" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G191" s="53" t="s">
         <v>53</v>
@@ -29739,16 +29850,16 @@
         <v>46170.3760763889</v>
       </c>
       <c r="D192" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E192" s="53" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F192" s="53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G192" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H192" s="53" t="s">
         <v>27</v>
@@ -29777,13 +29888,13 @@
         <v>46170.382662037002</v>
       </c>
       <c r="D193" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E193" s="53" t="s">
+        <v>315</v>
+      </c>
+      <c r="F193" s="53" t="s">
         <v>314</v>
-      </c>
-      <c r="F193" s="53" t="s">
-        <v>313</v>
       </c>
       <c r="G193" s="53" t="s">
         <v>26</v>
@@ -29815,13 +29926,13 @@
         <v>46170.410659722198</v>
       </c>
       <c r="D194" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E194" s="53" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F194" s="53" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G194" s="53" t="s">
         <v>26</v>
@@ -29853,16 +29964,16 @@
         <v>46170.426134259302</v>
       </c>
       <c r="D195" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E195" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F195" s="53" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G195" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H195" s="53" t="s">
         <v>27</v>
@@ -29891,16 +30002,16 @@
         <v>46170.4313078704</v>
       </c>
       <c r="D196" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E196" s="53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F196" s="53" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G196" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H196" s="53" t="s">
         <v>27</v>
@@ -29929,13 +30040,13 @@
         <v>46170.440532407403</v>
       </c>
       <c r="D197" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E197" s="53" t="s">
         <v>67</v>
       </c>
       <c r="F197" s="53" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G197" s="53" t="s">
         <v>26</v>
@@ -29967,13 +30078,13 @@
         <v>46170.442349536999</v>
       </c>
       <c r="D198" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E198" s="53" t="s">
+        <v>322</v>
+      </c>
+      <c r="F198" s="53" t="s">
         <v>321</v>
-      </c>
-      <c r="F198" s="53" t="s">
-        <v>320</v>
       </c>
       <c r="G198" s="53" t="s">
         <v>26</v>
@@ -30005,16 +30116,16 @@
         <v>46170.463715277801</v>
       </c>
       <c r="D199" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E199" s="53" t="s">
+        <v>324</v>
+      </c>
+      <c r="F199" s="53" t="s">
         <v>323</v>
       </c>
-      <c r="F199" s="53" t="s">
-        <v>322</v>
-      </c>
       <c r="G199" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H199" s="53" t="s">
         <v>27</v>
@@ -30043,7 +30154,7 @@
         <v>46170.494340277801</v>
       </c>
       <c r="D200" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E200" s="53" t="s">
         <v>78</v>
@@ -30052,7 +30163,7 @@
         <v>56</v>
       </c>
       <c r="G200" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H200" s="53" t="s">
         <v>27</v>
@@ -30081,13 +30192,13 @@
         <v>46170.540069444403</v>
       </c>
       <c r="D201" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E201" s="53" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F201" s="53" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G201" s="53" t="s">
         <v>32</v>
@@ -30119,13 +30230,13 @@
         <v>46170.540439814802</v>
       </c>
       <c r="D202" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E202" s="53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F202" s="53" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G202" s="53" t="s">
         <v>32</v>
@@ -30157,13 +30268,13 @@
         <v>46170.5406365741</v>
       </c>
       <c r="D203" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E203" s="53" t="s">
+        <v>328</v>
+      </c>
+      <c r="F203" s="53" t="s">
         <v>327</v>
-      </c>
-      <c r="F203" s="53" t="s">
-        <v>326</v>
       </c>
       <c r="G203" s="53" t="s">
         <v>32</v>
@@ -30195,13 +30306,13 @@
         <v>46170.541828703703</v>
       </c>
       <c r="D204" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E204" s="53" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F204" s="53" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G204" s="53" t="s">
         <v>32</v>
@@ -30233,13 +30344,13 @@
         <v>46170.555706018502</v>
       </c>
       <c r="D205" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E205" s="53" t="s">
         <v>127</v>
       </c>
       <c r="F205" s="53" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G205" s="53" t="s">
         <v>32</v>
@@ -30271,13 +30382,13 @@
         <v>46170.5613310185</v>
       </c>
       <c r="D206" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E206" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F206" s="53" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G206" s="53" t="s">
         <v>32</v>
@@ -30309,13 +30420,13 @@
         <v>46170.6018287037</v>
       </c>
       <c r="D207" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E207" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F207" s="53" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G207" s="53" t="s">
         <v>87</v>
@@ -30347,13 +30458,13 @@
         <v>46170.6551736111</v>
       </c>
       <c r="D208" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E208" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="F208" s="53" t="s">
         <v>333</v>
-      </c>
-      <c r="F208" s="53" t="s">
-        <v>332</v>
       </c>
       <c r="G208" s="53" t="s">
         <v>32</v>
@@ -30385,13 +30496,13 @@
         <v>46170.798148148097</v>
       </c>
       <c r="D209" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E209" s="53" t="s">
         <v>35</v>
       </c>
       <c r="F209" s="53" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G209" s="53" t="s">
         <v>113</v>
@@ -30423,13 +30534,13 @@
         <v>46171.3684027778</v>
       </c>
       <c r="D210" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E210" s="53" t="s">
+        <v>338</v>
+      </c>
+      <c r="F210" s="53" t="s">
         <v>337</v>
-      </c>
-      <c r="F210" s="53" t="s">
-        <v>336</v>
       </c>
       <c r="G210" s="53" t="s">
         <v>113</v>
@@ -30461,16 +30572,16 @@
         <v>46171.409490740698</v>
       </c>
       <c r="D211" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E211" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F211" s="53" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G211" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H211" s="53" t="s">
         <v>27</v>
@@ -30499,16 +30610,16 @@
         <v>46171.410208333298</v>
       </c>
       <c r="D212" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E212" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F212" s="53" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G212" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H212" s="53" t="s">
         <v>27</v>
@@ -30537,16 +30648,16 @@
         <v>46171.411041666703</v>
       </c>
       <c r="D213" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E213" s="53" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F213" s="53" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G213" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H213" s="53" t="s">
         <v>27</v>
@@ -30575,13 +30686,13 @@
         <v>46171.423634259299</v>
       </c>
       <c r="D214" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E214" s="53" t="s">
         <v>57</v>
       </c>
       <c r="F214" s="53" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G214" s="53" t="s">
         <v>26</v>
@@ -30613,13 +30724,13 @@
         <v>46171.646597222199</v>
       </c>
       <c r="D215" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E215" s="53" t="s">
         <v>31</v>
       </c>
       <c r="F215" s="53" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G215" s="53" t="s">
         <v>32</v>
@@ -30651,13 +30762,13 @@
         <v>46171.646608796298</v>
       </c>
       <c r="D216" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E216" s="53" t="s">
         <v>80</v>
       </c>
       <c r="F216" s="53" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G216" s="53" t="s">
         <v>32</v>
@@ -30689,16 +30800,16 @@
         <v>46171.668287036999</v>
       </c>
       <c r="D217" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E217" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F217" s="53" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G217" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H217" s="53" t="s">
         <v>27</v>
@@ -30727,16 +30838,16 @@
         <v>46171.704421296301</v>
       </c>
       <c r="D218" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E218" s="53" t="s">
         <v>52</v>
       </c>
       <c r="F218" s="53" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G218" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H218" s="53" t="s">
         <v>27</v>
@@ -30765,13 +30876,13 @@
         <v>46171.726331018501</v>
       </c>
       <c r="D219" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E219" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="F219" s="53" t="s">
         <v>346</v>
-      </c>
-      <c r="F219" s="53" t="s">
-        <v>345</v>
       </c>
       <c r="G219" s="53" t="s">
         <v>87</v>
@@ -30803,13 +30914,13 @@
         <v>46171.7492824074</v>
       </c>
       <c r="D220" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E220" s="53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F220" s="53" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G220" s="53" t="s">
         <v>32</v>
@@ -30841,16 +30952,16 @@
         <v>46171.882743055598</v>
       </c>
       <c r="D221" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E221" s="53" t="s">
         <v>100</v>
       </c>
       <c r="F221" s="53" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G221" s="53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H221" s="53" t="s">
         <v>27</v>
@@ -30879,13 +30990,13 @@
         <v>46172.437511574099</v>
       </c>
       <c r="D222" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E222" s="53" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F222" s="53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G222" s="53" t="s">
         <v>87</v>
@@ -30917,16 +31028,16 @@
         <v>46172.486087963</v>
       </c>
       <c r="D223" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E223" s="53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F223" s="53" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G223" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H223" s="53" t="s">
         <v>27</v>
@@ -30955,13 +31066,13 @@
         <v>46172.724467592598</v>
       </c>
       <c r="D224" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E224" s="53" t="s">
+        <v>353</v>
+      </c>
+      <c r="F224" s="53" t="s">
         <v>352</v>
-      </c>
-      <c r="F224" s="53" t="s">
-        <v>351</v>
       </c>
       <c r="G224" s="53" t="s">
         <v>87</v>
@@ -30993,13 +31104,13 @@
         <v>46174.4089930556</v>
       </c>
       <c r="D225" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E225" s="53" t="s">
         <v>57</v>
       </c>
       <c r="F225" s="53" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G225" s="53" t="s">
         <v>26</v>
@@ -31031,13 +31142,13 @@
         <v>46174.409849536998</v>
       </c>
       <c r="D226" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E226" s="53" t="s">
         <v>59</v>
       </c>
       <c r="F226" s="53" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G226" s="53" t="s">
         <v>26</v>
@@ -31069,13 +31180,13 @@
         <v>46174.452615740702</v>
       </c>
       <c r="D227" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E227" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F227" s="53" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G227" s="53" t="s">
         <v>26</v>
@@ -31107,13 +31218,13 @@
         <v>46174.645057870403</v>
       </c>
       <c r="D228" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E228" s="53" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F228" s="53" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G228" s="53" t="s">
         <v>26</v>
@@ -31145,16 +31256,16 @@
         <v>46174.820590277799</v>
       </c>
       <c r="D229" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E229" s="53" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F229" s="53" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G229" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H229" s="53" t="s">
         <v>27</v>
@@ -31183,16 +31294,16 @@
         <v>46174.909942129598</v>
       </c>
       <c r="D230" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E230" s="53" t="s">
         <v>73</v>
       </c>
       <c r="F230" s="53" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G230" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H230" s="53" t="s">
         <v>27</v>
@@ -31221,16 +31332,16 @@
         <v>46174.910532407397</v>
       </c>
       <c r="D231" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E231" s="53" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F231" s="53" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G231" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H231" s="53" t="s">
         <v>27</v>
@@ -31259,7 +31370,7 @@
         <v>46175.453402777799</v>
       </c>
       <c r="D232" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E232" s="53" t="s">
         <v>73</v>
@@ -31297,13 +31408,13 @@
         <v>46175.4539814815</v>
       </c>
       <c r="D233" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E233" s="53" t="s">
         <v>78</v>
       </c>
       <c r="F233" s="53" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G233" s="53" t="s">
         <v>26</v>
@@ -31335,13 +31446,13 @@
         <v>46175.876828703702</v>
       </c>
       <c r="D234" s="54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E234" s="53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F234" s="53" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G234" s="53" t="s">
         <v>26</v>
